--- a/research/traditional_assets/database/data/south_africa/south_africa_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_shipbuilding_marine.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="jse_gnd" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.17</v>
+        <v>1.063</v>
       </c>
       <c r="G2">
-        <v>-0.09933283914010378</v>
+        <v>0.1754578754578754</v>
       </c>
       <c r="H2">
-        <v>-0.09933283914010378</v>
+        <v>0.1754578754578754</v>
       </c>
       <c r="I2">
-        <v>-0.09933283914010378</v>
+        <v>0.1406593406593407</v>
       </c>
       <c r="J2">
-        <v>-0.09933283914010378</v>
+        <v>0.1406593406593407</v>
       </c>
       <c r="K2">
-        <v>-38.9</v>
+        <v>63.1</v>
       </c>
       <c r="L2">
-        <v>-0.1441808747220163</v>
+        <v>0.2311355311355311</v>
       </c>
       <c r="M2">
-        <v>13.37</v>
+        <v>6.44</v>
       </c>
       <c r="N2">
-        <v>0.06418626980316849</v>
+        <v>0.01778023191606847</v>
       </c>
       <c r="O2">
-        <v>-0.3437017994858612</v>
+        <v>0.1020602218700475</v>
       </c>
       <c r="P2">
-        <v>11.2</v>
+        <v>4.82</v>
       </c>
       <c r="Q2">
-        <v>0.05376860297647623</v>
+        <v>0.01330756488128106</v>
       </c>
       <c r="R2">
-        <v>-0.2879177377892031</v>
+        <v>0.07638668779714738</v>
       </c>
       <c r="S2">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="T2">
-        <v>0.162303664921466</v>
+        <v>0.2515527950310559</v>
       </c>
       <c r="U2">
-        <v>129.4</v>
+        <v>140.3</v>
       </c>
       <c r="V2">
-        <v>0.6212193951032166</v>
+        <v>0.387355052457206</v>
       </c>
       <c r="W2">
-        <v>-0.07335470488402791</v>
+        <v>0.1182977127859018</v>
       </c>
       <c r="X2">
-        <v>0.1619115370444741</v>
+        <v>0.2147676941115188</v>
       </c>
       <c r="Y2">
-        <v>-0.235266241928502</v>
+        <v>-0.09646998132561706</v>
       </c>
       <c r="Z2">
-        <v>0.503828197945845</v>
+        <v>0.3727471327143638</v>
       </c>
       <c r="AA2">
-        <v>-0.05004668534080299</v>
+        <v>0.05243036592026215</v>
       </c>
       <c r="AB2">
-        <v>0.08438659973305605</v>
+        <v>0.1521988006211771</v>
       </c>
       <c r="AC2">
-        <v>-0.134433285073859</v>
+        <v>-0.09976843470091498</v>
       </c>
       <c r="AD2">
-        <v>328.4</v>
+        <v>249.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>328.4</v>
+        <v>249.6</v>
       </c>
       <c r="AG2">
-        <v>199</v>
+        <v>109.3</v>
       </c>
       <c r="AH2">
-        <v>0.6118874604061859</v>
+        <v>0.4079764628963714</v>
       </c>
       <c r="AI2">
-        <v>0.3818160678990815</v>
+        <v>0.3133709981167608</v>
       </c>
       <c r="AJ2">
-        <v>0.4885833537932728</v>
+        <v>0.231813361611877</v>
       </c>
       <c r="AK2">
-        <v>0.2723415902559189</v>
+        <v>0.1665650716245047</v>
       </c>
       <c r="AL2">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="AM2">
-        <v>10.73</v>
+        <v>4.73</v>
       </c>
       <c r="AN2">
-        <v>-21.4640522875817</v>
+        <v>5.957040572792363</v>
       </c>
       <c r="AO2">
-        <v>-1.614457831325301</v>
+        <v>3.2</v>
       </c>
       <c r="AP2">
-        <v>-13.00653594771242</v>
+        <v>2.608591885441527</v>
       </c>
       <c r="AQ2">
-        <v>-2.49767008387698</v>
+        <v>8.118393234672304</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +721,8830 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.17</v>
+        <v>1.063</v>
       </c>
       <c r="G3">
-        <v>-0.09933283914010378</v>
+        <v>0.1754578754578754</v>
       </c>
       <c r="H3">
-        <v>-0.09933283914010378</v>
+        <v>0.1754578754578754</v>
       </c>
       <c r="I3">
-        <v>-0.09933283914010378</v>
+        <v>0.1406593406593407</v>
       </c>
       <c r="J3">
-        <v>-0.09933283914010378</v>
+        <v>0.1406593406593407</v>
       </c>
       <c r="K3">
-        <v>-38.9</v>
+        <v>63.1</v>
       </c>
       <c r="L3">
-        <v>-0.1441808747220163</v>
+        <v>0.2311355311355311</v>
       </c>
       <c r="M3">
-        <v>13.37</v>
+        <v>6.44</v>
       </c>
       <c r="N3">
-        <v>0.06418626980316849</v>
+        <v>0.01778023191606847</v>
       </c>
       <c r="O3">
-        <v>-0.3437017994858612</v>
+        <v>0.1020602218700475</v>
       </c>
       <c r="P3">
-        <v>11.2</v>
+        <v>4.82</v>
       </c>
       <c r="Q3">
-        <v>0.05376860297647623</v>
+        <v>0.01330756488128106</v>
       </c>
       <c r="R3">
-        <v>-0.2879177377892031</v>
+        <v>0.07638668779714738</v>
       </c>
       <c r="S3">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="T3">
-        <v>0.162303664921466</v>
+        <v>0.2515527950310559</v>
       </c>
       <c r="U3">
-        <v>129.4</v>
+        <v>140.3</v>
       </c>
       <c r="V3">
-        <v>0.6212193951032166</v>
+        <v>0.387355052457206</v>
       </c>
       <c r="W3">
-        <v>-0.07335470488402791</v>
+        <v>0.1182977127859018</v>
       </c>
       <c r="X3">
-        <v>0.1619115370444741</v>
+        <v>0.2147676941115188</v>
       </c>
       <c r="Y3">
-        <v>-0.235266241928502</v>
+        <v>-0.09646998132561706</v>
       </c>
       <c r="Z3">
-        <v>0.503828197945845</v>
+        <v>0.3727471327143638</v>
       </c>
       <c r="AA3">
-        <v>-0.05004668534080299</v>
+        <v>0.05243036592026215</v>
       </c>
       <c r="AB3">
-        <v>0.08438659973305605</v>
+        <v>0.1521988006211771</v>
       </c>
       <c r="AC3">
-        <v>-0.134433285073859</v>
+        <v>-0.09976843470091498</v>
       </c>
       <c r="AD3">
-        <v>328.4</v>
+        <v>249.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>328.4</v>
+        <v>249.6</v>
       </c>
       <c r="AG3">
-        <v>199</v>
+        <v>109.3</v>
       </c>
       <c r="AH3">
-        <v>0.6118874604061859</v>
+        <v>0.4079764628963714</v>
       </c>
       <c r="AI3">
-        <v>0.3818160678990815</v>
+        <v>0.3133709981167608</v>
       </c>
       <c r="AJ3">
-        <v>0.4885833537932728</v>
+        <v>0.231813361611877</v>
       </c>
       <c r="AK3">
-        <v>0.2723415902559189</v>
+        <v>0.1665650716245047</v>
       </c>
       <c r="AL3">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="AM3">
-        <v>10.73</v>
+        <v>4.73</v>
       </c>
       <c r="AN3">
-        <v>-21.4640522875817</v>
+        <v>5.957040572792363</v>
       </c>
       <c r="AO3">
-        <v>-1.614457831325301</v>
+        <v>3.2</v>
       </c>
       <c r="AP3">
-        <v>-13.00653594771242</v>
+        <v>2.608591885441527</v>
       </c>
       <c r="AQ3">
-        <v>-2.49767008387698</v>
+        <v>8.118393234672304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Grindrod Limited (JSE:GND)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JSE:GND</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shipbuilding &amp; Marine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.407976462896371</v>
+      </c>
+      <c r="F2">
+        <v>0.08</v>
+      </c>
+      <c r="G2">
+        <v>362.2</v>
+      </c>
+      <c r="H2">
+        <v>557.701225420802</v>
+      </c>
+      <c r="I2">
+        <v>471.5</v>
+      </c>
+      <c r="J2">
+        <v>466.345225420802</v>
+      </c>
+      <c r="K2">
+        <v>249.6</v>
+      </c>
+      <c r="L2">
+        <v>48.944</v>
+      </c>
+      <c r="M2">
+        <v>0.152198800621177</v>
+      </c>
+      <c r="N2">
+        <v>0.153452260982492</v>
+      </c>
+      <c r="O2">
+        <v>0.0614037155963303</v>
+      </c>
+      <c r="P2">
+        <v>0.04015</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.214767694111519</v>
+      </c>
+      <c r="T2">
+        <v>0.163304631502709</v>
+      </c>
+      <c r="U2">
+        <v>1.58423703084909</v>
+      </c>
+      <c r="V2">
+        <v>1.1209151130537</v>
+      </c>
+      <c r="W2">
+        <v>4.643525810573866</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>362.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.1110740947755822</v>
+      </c>
+      <c r="AC2">
+        <v>0.08411467889908257</v>
+      </c>
+      <c r="AD2">
+        <v>0.27</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>41.9</v>
+      </c>
+      <c r="AH2">
+        <v>29.4</v>
+      </c>
+      <c r="AI2">
+        <v>19.2</v>
+      </c>
+      <c r="AJ2">
+        <v>249.6</v>
+      </c>
+      <c r="AK2">
+        <v>249.6</v>
+      </c>
+      <c r="AL2">
+        <v>12</v>
+      </c>
+      <c r="AM2">
+        <v>249.6</v>
+      </c>
+      <c r="AN2">
+        <v>140.3</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1558730386166113</v>
+      </c>
+      <c r="C2">
+        <v>597.0023725076408</v>
+      </c>
+      <c r="D2">
+        <v>456.7023725076407</v>
+      </c>
+      <c r="E2">
+        <v>-249.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>140.3</v>
+      </c>
+      <c r="H2">
+        <v>362.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>41.9</v>
+      </c>
+      <c r="K2">
+        <v>29.4</v>
+      </c>
+      <c r="L2">
+        <v>12.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.5</v>
+      </c>
+      <c r="O2">
+        <v>3.375</v>
+      </c>
+      <c r="P2">
+        <v>9.125</v>
+      </c>
+      <c r="Q2">
+        <v>38.525</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1558730386166113</v>
+      </c>
+      <c r="T2">
+        <v>1.05400848733586</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.27</v>
+      </c>
+      <c r="W2">
+        <v>0.033361</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1555025514123465</v>
+      </c>
+      <c r="C3">
+        <v>592.3342327131269</v>
+      </c>
+      <c r="D3">
+        <v>458.1522327131269</v>
+      </c>
+      <c r="E3">
+        <v>-243.482</v>
+      </c>
+      <c r="F3">
+        <v>6.117999999999999</v>
+      </c>
+      <c r="G3">
+        <v>140.3</v>
+      </c>
+      <c r="H3">
+        <v>362.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>41.9</v>
+      </c>
+      <c r="K3">
+        <v>29.4</v>
+      </c>
+      <c r="L3">
+        <v>12.5</v>
+      </c>
+      <c r="M3">
+        <v>0.2795926</v>
+      </c>
+      <c r="N3">
+        <v>12.2204074</v>
+      </c>
+      <c r="O3">
+        <v>3.299509998</v>
+      </c>
+      <c r="P3">
+        <v>8.920897402</v>
+      </c>
+      <c r="Q3">
+        <v>38.320897402</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1567363044569156</v>
+      </c>
+      <c r="T3">
+        <v>1.061780469111165</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.27</v>
+      </c>
+      <c r="W3">
+        <v>0.033361</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>44.70790714775712</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1551320642080816</v>
+      </c>
+      <c r="C4">
+        <v>587.6753277698604</v>
+      </c>
+      <c r="D4">
+        <v>459.6113277698603</v>
+      </c>
+      <c r="E4">
+        <v>-237.364</v>
+      </c>
+      <c r="F4">
+        <v>12.236</v>
+      </c>
+      <c r="G4">
+        <v>140.3</v>
+      </c>
+      <c r="H4">
+        <v>362.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>41.9</v>
+      </c>
+      <c r="K4">
+        <v>29.4</v>
+      </c>
+      <c r="L4">
+        <v>12.5</v>
+      </c>
+      <c r="M4">
+        <v>0.5591852</v>
+      </c>
+      <c r="N4">
+        <v>11.9408148</v>
+      </c>
+      <c r="O4">
+        <v>3.224019996</v>
+      </c>
+      <c r="P4">
+        <v>8.716794803999999</v>
+      </c>
+      <c r="Q4">
+        <v>38.11679480399999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1576171879674302</v>
+      </c>
+      <c r="T4">
+        <v>1.069711062759435</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.27</v>
+      </c>
+      <c r="W4">
+        <v>0.033361</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>22.35395357387856</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1547615770038167</v>
+      </c>
+      <c r="C5">
+        <v>583.0257461914923</v>
+      </c>
+      <c r="D5">
+        <v>461.0797461914923</v>
+      </c>
+      <c r="E5">
+        <v>-231.246</v>
+      </c>
+      <c r="F5">
+        <v>18.354</v>
+      </c>
+      <c r="G5">
+        <v>140.3</v>
+      </c>
+      <c r="H5">
+        <v>362.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>41.9</v>
+      </c>
+      <c r="K5">
+        <v>29.4</v>
+      </c>
+      <c r="L5">
+        <v>12.5</v>
+      </c>
+      <c r="M5">
+        <v>0.8387778</v>
+      </c>
+      <c r="N5">
+        <v>11.6612222</v>
+      </c>
+      <c r="O5">
+        <v>3.148529994</v>
+      </c>
+      <c r="P5">
+        <v>8.512692205999999</v>
+      </c>
+      <c r="Q5">
+        <v>37.912692206</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1585162340245533</v>
+      </c>
+      <c r="T5">
+        <v>1.077805173802515</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.27</v>
+      </c>
+      <c r="W5">
+        <v>0.033361</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.90263571591904</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1544378097995519</v>
+      </c>
+      <c r="C6">
+        <v>578.1986950656221</v>
+      </c>
+      <c r="D6">
+        <v>462.3706950656222</v>
+      </c>
+      <c r="E6">
+        <v>-225.128</v>
+      </c>
+      <c r="F6">
+        <v>24.472</v>
+      </c>
+      <c r="G6">
+        <v>140.3</v>
+      </c>
+      <c r="H6">
+        <v>362.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>41.9</v>
+      </c>
+      <c r="K6">
+        <v>29.4</v>
+      </c>
+      <c r="L6">
+        <v>12.5</v>
+      </c>
+      <c r="M6">
+        <v>1.1575256</v>
+      </c>
+      <c r="N6">
+        <v>11.3424744</v>
+      </c>
+      <c r="O6">
+        <v>3.062468088</v>
+      </c>
+      <c r="P6">
+        <v>8.280006312000001</v>
+      </c>
+      <c r="Q6">
+        <v>37.680006312</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1594340102078665</v>
+      </c>
+      <c r="T6">
+        <v>1.086067912158992</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.27</v>
+      </c>
+      <c r="W6">
+        <v>0.034529</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.79889723389271</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.154217702595287</v>
+      </c>
+      <c r="C7">
+        <v>572.9624585970083</v>
+      </c>
+      <c r="D7">
+        <v>463.2524585970083</v>
+      </c>
+      <c r="E7">
+        <v>-219.01</v>
+      </c>
+      <c r="F7">
+        <v>30.59</v>
+      </c>
+      <c r="G7">
+        <v>140.3</v>
+      </c>
+      <c r="H7">
+        <v>362.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>41.9</v>
+      </c>
+      <c r="K7">
+        <v>29.4</v>
+      </c>
+      <c r="L7">
+        <v>12.5</v>
+      </c>
+      <c r="M7">
+        <v>1.563149</v>
+      </c>
+      <c r="N7">
+        <v>10.936851</v>
+      </c>
+      <c r="O7">
+        <v>2.95294977</v>
+      </c>
+      <c r="P7">
+        <v>7.983901230000001</v>
+      </c>
+      <c r="Q7">
+        <v>37.38390123</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.160371107995039</v>
+      </c>
+      <c r="T7">
+        <v>1.094504602901922</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.27</v>
+      </c>
+      <c r="W7">
+        <v>0.037303</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>7.996678499618399</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1539698553910222</v>
+      </c>
+      <c r="C8">
+        <v>567.8413846271944</v>
+      </c>
+      <c r="D8">
+        <v>464.2493846271944</v>
+      </c>
+      <c r="E8">
+        <v>-212.892</v>
+      </c>
+      <c r="F8">
+        <v>36.708</v>
+      </c>
+      <c r="G8">
+        <v>140.3</v>
+      </c>
+      <c r="H8">
+        <v>362.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>41.9</v>
+      </c>
+      <c r="K8">
+        <v>29.4</v>
+      </c>
+      <c r="L8">
+        <v>12.5</v>
+      </c>
+      <c r="M8">
+        <v>1.945524</v>
+      </c>
+      <c r="N8">
+        <v>10.554476</v>
+      </c>
+      <c r="O8">
+        <v>2.84970852</v>
+      </c>
+      <c r="P8">
+        <v>7.704767479999999</v>
+      </c>
+      <c r="Q8">
+        <v>37.10476748</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1613281440330023</v>
+      </c>
+      <c r="T8">
+        <v>1.103120797703212</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.27</v>
+      </c>
+      <c r="W8">
+        <v>0.03869</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.425004266202833</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1537548581867573</v>
+      </c>
+      <c r="C9">
+        <v>562.5916586727712</v>
+      </c>
+      <c r="D9">
+        <v>465.1176586727713</v>
+      </c>
+      <c r="E9">
+        <v>-206.774</v>
+      </c>
+      <c r="F9">
+        <v>42.826</v>
+      </c>
+      <c r="G9">
+        <v>140.3</v>
+      </c>
+      <c r="H9">
+        <v>362.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>41.9</v>
+      </c>
+      <c r="K9">
+        <v>29.4</v>
+      </c>
+      <c r="L9">
+        <v>12.5</v>
+      </c>
+      <c r="M9">
+        <v>2.35543</v>
+      </c>
+      <c r="N9">
+        <v>10.14457</v>
+      </c>
+      <c r="O9">
+        <v>2.7390339</v>
+      </c>
+      <c r="P9">
+        <v>7.405536099999999</v>
+      </c>
+      <c r="Q9">
+        <v>36.8055361</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1623057614911369</v>
+      </c>
+      <c r="T9">
+        <v>1.111922287016357</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.27</v>
+      </c>
+      <c r="W9">
+        <v>0.04015</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.306886640655846</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1534522609824925</v>
+      </c>
+      <c r="C10">
+        <v>557.7012254208016</v>
+      </c>
+      <c r="D10">
+        <v>466.3452254208015</v>
+      </c>
+      <c r="E10">
+        <v>-200.656</v>
+      </c>
+      <c r="F10">
+        <v>48.944</v>
+      </c>
+      <c r="G10">
+        <v>140.3</v>
+      </c>
+      <c r="H10">
+        <v>362.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>41.9</v>
+      </c>
+      <c r="K10">
+        <v>29.4</v>
+      </c>
+      <c r="L10">
+        <v>12.5</v>
+      </c>
+      <c r="M10">
+        <v>2.69192</v>
+      </c>
+      <c r="N10">
+        <v>9.80808</v>
+      </c>
+      <c r="O10">
+        <v>2.6481816</v>
+      </c>
+      <c r="P10">
+        <v>7.159898399999999</v>
+      </c>
+      <c r="Q10">
+        <v>36.55989839999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1633046315027092</v>
+      </c>
+      <c r="T10">
+        <v>1.120915113053701</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.27</v>
+      </c>
+      <c r="W10">
+        <v>0.04015</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.643525810573866</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1536752637782277</v>
+      </c>
+      <c r="C11">
+        <v>550.6779279213557</v>
+      </c>
+      <c r="D11">
+        <v>465.4399279213558</v>
+      </c>
+      <c r="E11">
+        <v>-194.538</v>
+      </c>
+      <c r="F11">
+        <v>55.06199999999999</v>
+      </c>
+      <c r="G11">
+        <v>140.3</v>
+      </c>
+      <c r="H11">
+        <v>362.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>41.9</v>
+      </c>
+      <c r="K11">
+        <v>29.4</v>
+      </c>
+      <c r="L11">
+        <v>12.5</v>
+      </c>
+      <c r="M11">
+        <v>3.468906</v>
+      </c>
+      <c r="N11">
+        <v>9.031094</v>
+      </c>
+      <c r="O11">
+        <v>2.43839538</v>
+      </c>
+      <c r="P11">
+        <v>6.592698619999999</v>
+      </c>
+      <c r="Q11">
+        <v>35.99269862</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.164325454701349</v>
+      </c>
+      <c r="T11">
+        <v>1.130105583619339</v>
+      </c>
+      <c r="U11">
+        <v>0.063</v>
+      </c>
+      <c r="V11">
+        <v>0.27</v>
+      </c>
+      <c r="W11">
+        <v>0.04599</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>3.60344154612434</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1555042665739628</v>
+      </c>
+      <c r="C12">
+        <v>537.2654994106775</v>
+      </c>
+      <c r="D12">
+        <v>458.1454994106775</v>
+      </c>
+      <c r="E12">
+        <v>-188.42</v>
+      </c>
+      <c r="F12">
+        <v>61.18</v>
+      </c>
+      <c r="G12">
+        <v>140.3</v>
+      </c>
+      <c r="H12">
+        <v>362.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>41.9</v>
+      </c>
+      <c r="K12">
+        <v>29.4</v>
+      </c>
+      <c r="L12">
+        <v>12.5</v>
+      </c>
+      <c r="M12">
+        <v>5.591852</v>
+      </c>
+      <c r="N12">
+        <v>6.908148</v>
+      </c>
+      <c r="O12">
+        <v>1.86519996</v>
+      </c>
+      <c r="P12">
+        <v>5.04294804</v>
+      </c>
+      <c r="Q12">
+        <v>34.44294804</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1653689628599586</v>
+      </c>
+      <c r="T12">
+        <v>1.139500286864213</v>
+      </c>
+      <c r="U12">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.27</v>
+      </c>
+      <c r="W12">
+        <v>0.066722</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.235395357387857</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.155467389369698</v>
+      </c>
+      <c r="C13">
+        <v>531.2923138721656</v>
+      </c>
+      <c r="D13">
+        <v>458.2903138721655</v>
+      </c>
+      <c r="E13">
+        <v>-182.302</v>
+      </c>
+      <c r="F13">
+        <v>67.298</v>
+      </c>
+      <c r="G13">
+        <v>140.3</v>
+      </c>
+      <c r="H13">
+        <v>362.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>41.9</v>
+      </c>
+      <c r="K13">
+        <v>29.4</v>
+      </c>
+      <c r="L13">
+        <v>12.5</v>
+      </c>
+      <c r="M13">
+        <v>6.151037200000001</v>
+      </c>
+      <c r="N13">
+        <v>6.348962799999999</v>
+      </c>
+      <c r="O13">
+        <v>1.714219956</v>
+      </c>
+      <c r="P13">
+        <v>4.634742843999999</v>
+      </c>
+      <c r="Q13">
+        <v>34.034742844</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.16643592064011</v>
+      </c>
+      <c r="T13">
+        <v>1.149106107035938</v>
+      </c>
+      <c r="U13">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.27</v>
+      </c>
+      <c r="W13">
+        <v>0.066722</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.032177597625324</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1572788721654331</v>
+      </c>
+      <c r="C14">
+        <v>518.1672838096893</v>
+      </c>
+      <c r="D14">
+        <v>451.2832838096891</v>
+      </c>
+      <c r="E14">
+        <v>-176.184</v>
+      </c>
+      <c r="F14">
+        <v>73.416</v>
+      </c>
+      <c r="G14">
+        <v>140.3</v>
+      </c>
+      <c r="H14">
+        <v>362.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>41.9</v>
+      </c>
+      <c r="K14">
+        <v>29.4</v>
+      </c>
+      <c r="L14">
+        <v>12.5</v>
+      </c>
+      <c r="M14">
+        <v>8.2593</v>
+      </c>
+      <c r="N14">
+        <v>4.2407</v>
+      </c>
+      <c r="O14">
+        <v>1.144989</v>
+      </c>
+      <c r="P14">
+        <v>3.095711</v>
+      </c>
+      <c r="Q14">
+        <v>32.495711</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1675271274607194</v>
+      </c>
+      <c r="T14">
+        <v>1.158930241302475</v>
+      </c>
+      <c r="U14">
+        <v>0.1125</v>
+      </c>
+      <c r="V14">
+        <v>0.27</v>
+      </c>
+      <c r="W14">
+        <v>0.082125</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>1.513445449372223</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1700857889259237</v>
+      </c>
+      <c r="C15">
+        <v>468.0266405484861</v>
+      </c>
+      <c r="D15">
+        <v>407.260640548486</v>
+      </c>
+      <c r="E15">
+        <v>-170.066</v>
+      </c>
+      <c r="F15">
+        <v>79.53399999999999</v>
+      </c>
+      <c r="G15">
+        <v>140.3</v>
+      </c>
+      <c r="H15">
+        <v>362.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>41.9</v>
+      </c>
+      <c r="K15">
+        <v>29.4</v>
+      </c>
+      <c r="L15">
+        <v>12.5</v>
+      </c>
+      <c r="M15">
+        <v>17.0043692</v>
+      </c>
+      <c r="N15">
+        <v>-4.504369199999996</v>
+      </c>
+      <c r="O15">
+        <v>-1.216179683999999</v>
+      </c>
+      <c r="P15">
+        <v>-3.288189515999997</v>
+      </c>
+      <c r="Q15">
+        <v>26.111810484</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1698945949297533</v>
+      </c>
+      <c r="T15">
+        <v>1.180244549321975</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1984784004807424</v>
+      </c>
+      <c r="W15">
+        <v>0.1713653179772173</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.7351051869657125</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1718357889259236</v>
+      </c>
+      <c r="C16">
+        <v>456.5513894906022</v>
+      </c>
+      <c r="D16">
+        <v>401.9033894906021</v>
+      </c>
+      <c r="E16">
+        <v>-163.948</v>
+      </c>
+      <c r="F16">
+        <v>85.652</v>
+      </c>
+      <c r="G16">
+        <v>140.3</v>
+      </c>
+      <c r="H16">
+        <v>362.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>41.9</v>
+      </c>
+      <c r="K16">
+        <v>29.4</v>
+      </c>
+      <c r="L16">
+        <v>12.5</v>
+      </c>
+      <c r="M16">
+        <v>18.3123976</v>
+      </c>
+      <c r="N16">
+        <v>-5.812397600000001</v>
+      </c>
+      <c r="O16">
+        <v>-1.569347352</v>
+      </c>
+      <c r="P16">
+        <v>-4.243050248</v>
+      </c>
+      <c r="Q16">
+        <v>25.156949752</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1714189506847505</v>
+      </c>
+      <c r="T16">
+        <v>1.193968323151301</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.184301371874975</v>
+      </c>
+      <c r="W16">
+        <v>0.1743963666931303</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6825976736110186</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1735857889259236</v>
+      </c>
+      <c r="C17">
+        <v>445.2152508632792</v>
+      </c>
+      <c r="D17">
+        <v>396.6852508632792</v>
+      </c>
+      <c r="E17">
+        <v>-157.83</v>
+      </c>
+      <c r="F17">
+        <v>91.77</v>
+      </c>
+      <c r="G17">
+        <v>140.3</v>
+      </c>
+      <c r="H17">
+        <v>362.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>41.9</v>
+      </c>
+      <c r="K17">
+        <v>29.4</v>
+      </c>
+      <c r="L17">
+        <v>12.5</v>
+      </c>
+      <c r="M17">
+        <v>19.620426</v>
+      </c>
+      <c r="N17">
+        <v>-7.120425999999998</v>
+      </c>
+      <c r="O17">
+        <v>-1.92251502</v>
+      </c>
+      <c r="P17">
+        <v>-5.197910979999999</v>
+      </c>
+      <c r="Q17">
+        <v>24.20208902</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1729791736339828</v>
+      </c>
+      <c r="T17">
+        <v>1.208015009306022</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1720146137499767</v>
+      </c>
+      <c r="W17">
+        <v>0.177023275580255</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.6370911620369507</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1753357889259236</v>
+      </c>
+      <c r="C18">
+        <v>434.0128755908927</v>
+      </c>
+      <c r="D18">
+        <v>391.6008755908927</v>
+      </c>
+      <c r="E18">
+        <v>-151.712</v>
+      </c>
+      <c r="F18">
+        <v>97.88799999999999</v>
+      </c>
+      <c r="G18">
+        <v>140.3</v>
+      </c>
+      <c r="H18">
+        <v>362.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>41.9</v>
+      </c>
+      <c r="K18">
+        <v>29.4</v>
+      </c>
+      <c r="L18">
+        <v>12.5</v>
+      </c>
+      <c r="M18">
+        <v>20.9284544</v>
+      </c>
+      <c r="N18">
+        <v>-8.428454399999996</v>
+      </c>
+      <c r="O18">
+        <v>-2.275682687999999</v>
+      </c>
+      <c r="P18">
+        <v>-6.152771711999997</v>
+      </c>
+      <c r="Q18">
+        <v>23.247228288</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1745765447486731</v>
+      </c>
+      <c r="T18">
+        <v>1.222396140369189</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1612637003906032</v>
+      </c>
+      <c r="W18">
+        <v>0.179321820856489</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5972729644096414</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1770857889259236</v>
+      </c>
+      <c r="C19">
+        <v>422.939185366996</v>
+      </c>
+      <c r="D19">
+        <v>386.6451853669959</v>
+      </c>
+      <c r="E19">
+        <v>-145.594</v>
+      </c>
+      <c r="F19">
+        <v>104.006</v>
+      </c>
+      <c r="G19">
+        <v>140.3</v>
+      </c>
+      <c r="H19">
+        <v>362.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>41.9</v>
+      </c>
+      <c r="K19">
+        <v>29.4</v>
+      </c>
+      <c r="L19">
+        <v>12.5</v>
+      </c>
+      <c r="M19">
+        <v>22.2364828</v>
+      </c>
+      <c r="N19">
+        <v>-9.736482799999997</v>
+      </c>
+      <c r="O19">
+        <v>-2.628850356</v>
+      </c>
+      <c r="P19">
+        <v>-7.107632443999998</v>
+      </c>
+      <c r="Q19">
+        <v>22.292367556</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1762124067335969</v>
+      </c>
+      <c r="T19">
+        <v>1.237123804710986</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1517776003676265</v>
+      </c>
+      <c r="W19">
+        <v>0.1813499490414014</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5621392606208389</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1788357889259237</v>
+      </c>
+      <c r="C20">
+        <v>411.9893557355709</v>
+      </c>
+      <c r="D20">
+        <v>381.8133557355709</v>
+      </c>
+      <c r="E20">
+        <v>-139.476</v>
+      </c>
+      <c r="F20">
+        <v>110.124</v>
+      </c>
+      <c r="G20">
+        <v>140.3</v>
+      </c>
+      <c r="H20">
+        <v>362.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>41.9</v>
+      </c>
+      <c r="K20">
+        <v>29.4</v>
+      </c>
+      <c r="L20">
+        <v>12.5</v>
+      </c>
+      <c r="M20">
+        <v>23.5445112</v>
+      </c>
+      <c r="N20">
+        <v>-11.0445112</v>
+      </c>
+      <c r="O20">
+        <v>-2.982018023999999</v>
+      </c>
+      <c r="P20">
+        <v>-8.062493175999997</v>
+      </c>
+      <c r="Q20">
+        <v>21.337506824</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1778881677913237</v>
+      </c>
+      <c r="T20">
+        <v>1.252210680378193</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1433455114583139</v>
+      </c>
+      <c r="W20">
+        <v>0.1831527296502125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.530909301697459</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1805857889259237</v>
+      </c>
+      <c r="C21">
+        <v>401.1588004252053</v>
+      </c>
+      <c r="D21">
+        <v>377.1008004252052</v>
+      </c>
+      <c r="E21">
+        <v>-133.358</v>
+      </c>
+      <c r="F21">
+        <v>116.242</v>
+      </c>
+      <c r="G21">
+        <v>140.3</v>
+      </c>
+      <c r="H21">
+        <v>362.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>41.9</v>
+      </c>
+      <c r="K21">
+        <v>29.4</v>
+      </c>
+      <c r="L21">
+        <v>12.5</v>
+      </c>
+      <c r="M21">
+        <v>24.8525396</v>
+      </c>
+      <c r="N21">
+        <v>-12.3525396</v>
+      </c>
+      <c r="O21">
+        <v>-3.335185691999999</v>
+      </c>
+      <c r="P21">
+        <v>-9.017353907999997</v>
+      </c>
+      <c r="Q21">
+        <v>20.382646092</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1796053056652906</v>
+      </c>
+      <c r="T21">
+        <v>1.267670071493973</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1358010108552448</v>
+      </c>
+      <c r="W21">
+        <v>0.1847657438791487</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5029667068712769</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.187652030658307</v>
+      </c>
+      <c r="C22">
+        <v>377.1392279609598</v>
+      </c>
+      <c r="D22">
+        <v>359.1992279609598</v>
+      </c>
+      <c r="E22">
+        <v>-127.24</v>
+      </c>
+      <c r="F22">
+        <v>122.36</v>
+      </c>
+      <c r="G22">
+        <v>140.3</v>
+      </c>
+      <c r="H22">
+        <v>362.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>41.9</v>
+      </c>
+      <c r="K22">
+        <v>29.4</v>
+      </c>
+      <c r="L22">
+        <v>12.5</v>
+      </c>
+      <c r="M22">
+        <v>29.219568</v>
+      </c>
+      <c r="N22">
+        <v>-16.719568</v>
+      </c>
+      <c r="O22">
+        <v>-4.514283360000001</v>
+      </c>
+      <c r="P22">
+        <v>-12.20528464</v>
+      </c>
+      <c r="Q22">
+        <v>17.19471536</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.181760674151586</v>
+      </c>
+      <c r="T22">
+        <v>1.287074852515598</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.1155047877504554</v>
+      </c>
+      <c r="W22">
+        <v>0.2112174566851912</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.427795510186872</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.189652030658307</v>
+      </c>
+      <c r="C23">
+        <v>366.2589556018351</v>
+      </c>
+      <c r="D23">
+        <v>354.436955601835</v>
+      </c>
+      <c r="E23">
+        <v>-121.122</v>
+      </c>
+      <c r="F23">
+        <v>128.478</v>
+      </c>
+      <c r="G23">
+        <v>140.3</v>
+      </c>
+      <c r="H23">
+        <v>362.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>41.9</v>
+      </c>
+      <c r="K23">
+        <v>29.4</v>
+      </c>
+      <c r="L23">
+        <v>12.5</v>
+      </c>
+      <c r="M23">
+        <v>30.6805464</v>
+      </c>
+      <c r="N23">
+        <v>-18.1805464</v>
+      </c>
+      <c r="O23">
+        <v>-4.908747527999999</v>
+      </c>
+      <c r="P23">
+        <v>-13.271798872</v>
+      </c>
+      <c r="Q23">
+        <v>16.128201128</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1835703029383149</v>
+      </c>
+      <c r="T23">
+        <v>1.303366939256302</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.1100045597623385</v>
+      </c>
+      <c r="W23">
+        <v>0.2125309111287536</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.4074242954160686</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.191652030658307</v>
+      </c>
+      <c r="C24">
+        <v>355.5033076219509</v>
+      </c>
+      <c r="D24">
+        <v>349.7993076219509</v>
+      </c>
+      <c r="E24">
+        <v>-115.004</v>
+      </c>
+      <c r="F24">
+        <v>134.596</v>
+      </c>
+      <c r="G24">
+        <v>140.3</v>
+      </c>
+      <c r="H24">
+        <v>362.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>41.9</v>
+      </c>
+      <c r="K24">
+        <v>29.4</v>
+      </c>
+      <c r="L24">
+        <v>12.5</v>
+      </c>
+      <c r="M24">
+        <v>32.1415248</v>
+      </c>
+      <c r="N24">
+        <v>-19.6415248</v>
+      </c>
+      <c r="O24">
+        <v>-5.303211696</v>
+      </c>
+      <c r="P24">
+        <v>-14.338313104</v>
+      </c>
+      <c r="Q24">
+        <v>15.061686896</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1854263324631651</v>
+      </c>
+      <c r="T24">
+        <v>1.320076771810869</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1050043525004141</v>
+      </c>
+      <c r="W24">
+        <v>0.2137249606229011</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3889050092607927</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.193652030658307</v>
+      </c>
+      <c r="C25">
+        <v>344.8674552420385</v>
+      </c>
+      <c r="D25">
+        <v>345.2814552420385</v>
+      </c>
+      <c r="E25">
+        <v>-108.886</v>
+      </c>
+      <c r="F25">
+        <v>140.714</v>
+      </c>
+      <c r="G25">
+        <v>140.3</v>
+      </c>
+      <c r="H25">
+        <v>362.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>41.9</v>
+      </c>
+      <c r="K25">
+        <v>29.4</v>
+      </c>
+      <c r="L25">
+        <v>12.5</v>
+      </c>
+      <c r="M25">
+        <v>33.6025032</v>
+      </c>
+      <c r="N25">
+        <v>-21.1025032</v>
+      </c>
+      <c r="O25">
+        <v>-5.697675864000001</v>
+      </c>
+      <c r="P25">
+        <v>-15.404827336</v>
+      </c>
+      <c r="Q25">
+        <v>13.995172664</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1873305705471023</v>
+      </c>
+      <c r="T25">
+        <v>1.337220625990232</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.1004389458699613</v>
+      </c>
+      <c r="W25">
+        <v>0.2148151797262532</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3719960958146713</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.195652030658307</v>
+      </c>
+      <c r="C26">
+        <v>334.3468159673936</v>
+      </c>
+      <c r="D26">
+        <v>340.8788159673936</v>
+      </c>
+      <c r="E26">
+        <v>-102.768</v>
+      </c>
+      <c r="F26">
+        <v>146.832</v>
+      </c>
+      <c r="G26">
+        <v>140.3</v>
+      </c>
+      <c r="H26">
+        <v>362.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>41.9</v>
+      </c>
+      <c r="K26">
+        <v>29.4</v>
+      </c>
+      <c r="L26">
+        <v>12.5</v>
+      </c>
+      <c r="M26">
+        <v>35.0634816</v>
+      </c>
+      <c r="N26">
+        <v>-22.5634816</v>
+      </c>
+      <c r="O26">
+        <v>-6.092140032000001</v>
+      </c>
+      <c r="P26">
+        <v>-16.471341568</v>
+      </c>
+      <c r="Q26">
+        <v>12.928658432</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1892849201595642</v>
+      </c>
+      <c r="T26">
+        <v>1.354815634226945</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.0962539897920462</v>
+      </c>
+      <c r="W26">
+        <v>0.2158145472376594</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.35649625848906</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.197652030658307</v>
+      </c>
+      <c r="C27">
+        <v>323.9370380838532</v>
+      </c>
+      <c r="D27">
+        <v>336.5870380838532</v>
+      </c>
+      <c r="E27">
+        <v>-96.65000000000001</v>
+      </c>
+      <c r="F27">
+        <v>152.95</v>
+      </c>
+      <c r="G27">
+        <v>140.3</v>
+      </c>
+      <c r="H27">
+        <v>362.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>41.9</v>
+      </c>
+      <c r="K27">
+        <v>29.4</v>
+      </c>
+      <c r="L27">
+        <v>12.5</v>
+      </c>
+      <c r="M27">
+        <v>36.52446</v>
+      </c>
+      <c r="N27">
+        <v>-24.02446</v>
+      </c>
+      <c r="O27">
+        <v>-6.486604199999999</v>
+      </c>
+      <c r="P27">
+        <v>-17.5378558</v>
+      </c>
+      <c r="Q27">
+        <v>11.8621442</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1912913857616917</v>
+      </c>
+      <c r="T27">
+        <v>1.372879842683304</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.09240383020036437</v>
+      </c>
+      <c r="W27">
+        <v>0.216733965348153</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3422364081494976</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.199652030658307</v>
+      </c>
+      <c r="C28">
+        <v>313.6339863104149</v>
+      </c>
+      <c r="D28">
+        <v>332.4019863104149</v>
+      </c>
+      <c r="E28">
+        <v>-90.53200000000001</v>
+      </c>
+      <c r="F28">
+        <v>159.068</v>
+      </c>
+      <c r="G28">
+        <v>140.3</v>
+      </c>
+      <c r="H28">
+        <v>362.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>41.9</v>
+      </c>
+      <c r="K28">
+        <v>29.4</v>
+      </c>
+      <c r="L28">
+        <v>12.5</v>
+      </c>
+      <c r="M28">
+        <v>37.9854384</v>
+      </c>
+      <c r="N28">
+        <v>-25.4854384</v>
+      </c>
+      <c r="O28">
+        <v>-6.881068368</v>
+      </c>
+      <c r="P28">
+        <v>-18.604370032</v>
+      </c>
+      <c r="Q28">
+        <v>10.795629968</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1933520801638767</v>
+      </c>
+      <c r="T28">
+        <v>1.391432272989835</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.08884983673111957</v>
+      </c>
+      <c r="W28">
+        <v>0.2175826589886087</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.329073469374517</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2016520306583071</v>
+      </c>
+      <c r="C29">
+        <v>303.4337285090633</v>
+      </c>
+      <c r="D29">
+        <v>328.3197285090632</v>
+      </c>
+      <c r="E29">
+        <v>-84.41399999999999</v>
+      </c>
+      <c r="F29">
+        <v>165.186</v>
+      </c>
+      <c r="G29">
+        <v>140.3</v>
+      </c>
+      <c r="H29">
+        <v>362.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>41.9</v>
+      </c>
+      <c r="K29">
+        <v>29.4</v>
+      </c>
+      <c r="L29">
+        <v>12.5</v>
+      </c>
+      <c r="M29">
+        <v>39.4464168</v>
+      </c>
+      <c r="N29">
+        <v>-26.9464168</v>
+      </c>
+      <c r="O29">
+        <v>-7.275532536000001</v>
+      </c>
+      <c r="P29">
+        <v>-19.670884264</v>
+      </c>
+      <c r="Q29">
+        <v>9.729115735999997</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1954692319469435</v>
+      </c>
+      <c r="T29">
+        <v>1.41049298905819</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.08555910203737441</v>
+      </c>
+      <c r="W29">
+        <v>0.218368486433475</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3168855631013867</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.203652030658307</v>
+      </c>
+      <c r="C30">
+        <v>293.3325233620235</v>
+      </c>
+      <c r="D30">
+        <v>324.3365233620235</v>
+      </c>
+      <c r="E30">
+        <v>-78.29599999999999</v>
+      </c>
+      <c r="F30">
+        <v>171.304</v>
+      </c>
+      <c r="G30">
+        <v>140.3</v>
+      </c>
+      <c r="H30">
+        <v>362.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>41.9</v>
+      </c>
+      <c r="K30">
+        <v>29.4</v>
+      </c>
+      <c r="L30">
+        <v>12.5</v>
+      </c>
+      <c r="M30">
+        <v>40.9073952</v>
+      </c>
+      <c r="N30">
+        <v>-28.4073952</v>
+      </c>
+      <c r="O30">
+        <v>-7.669996704000002</v>
+      </c>
+      <c r="P30">
+        <v>-20.737398496</v>
+      </c>
+      <c r="Q30">
+        <v>8.662601503999998</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1976451935017622</v>
+      </c>
+      <c r="T30">
+        <v>1.430083169461775</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.0825034198217539</v>
+      </c>
+      <c r="W30">
+        <v>0.2190981833465652</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3055682215620514</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.205652030658307</v>
+      </c>
+      <c r="C31">
+        <v>283.3268089352663</v>
+      </c>
+      <c r="D31">
+        <v>320.4488089352663</v>
+      </c>
+      <c r="E31">
+        <v>-72.17800000000003</v>
+      </c>
+      <c r="F31">
+        <v>177.422</v>
+      </c>
+      <c r="G31">
+        <v>140.3</v>
+      </c>
+      <c r="H31">
+        <v>362.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>41.9</v>
+      </c>
+      <c r="K31">
+        <v>29.4</v>
+      </c>
+      <c r="L31">
+        <v>12.5</v>
+      </c>
+      <c r="M31">
+        <v>42.3683736</v>
+      </c>
+      <c r="N31">
+        <v>-29.8683736</v>
+      </c>
+      <c r="O31">
+        <v>-8.064460872</v>
+      </c>
+      <c r="P31">
+        <v>-21.803912728</v>
+      </c>
+      <c r="Q31">
+        <v>7.596087271999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1998824497482659</v>
+      </c>
+      <c r="T31">
+        <v>1.450225185933068</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.07965847431065894</v>
+      </c>
+      <c r="W31">
+        <v>0.2197775563346147</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2950313863357739</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.207652030658307</v>
+      </c>
+      <c r="C32">
+        <v>273.4131920547832</v>
+      </c>
+      <c r="D32">
+        <v>316.6531920547831</v>
+      </c>
+      <c r="E32">
+        <v>-66.06</v>
+      </c>
+      <c r="F32">
+        <v>183.54</v>
+      </c>
+      <c r="G32">
+        <v>140.3</v>
+      </c>
+      <c r="H32">
+        <v>362.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>41.9</v>
+      </c>
+      <c r="K32">
+        <v>29.4</v>
+      </c>
+      <c r="L32">
+        <v>12.5</v>
+      </c>
+      <c r="M32">
+        <v>43.829352</v>
+      </c>
+      <c r="N32">
+        <v>-31.329352</v>
+      </c>
+      <c r="O32">
+        <v>-8.45892504</v>
+      </c>
+      <c r="P32">
+        <v>-22.87042696</v>
+      </c>
+      <c r="Q32">
+        <v>6.529573039999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2021836276018125</v>
+      </c>
+      <c r="T32">
+        <v>1.470942688589255</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.07700319183363698</v>
+      </c>
+      <c r="W32">
+        <v>0.2204116377901275</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.285197006791248</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.209652030658307</v>
+      </c>
+      <c r="C33">
+        <v>263.5884384290323</v>
+      </c>
+      <c r="D33">
+        <v>312.9464384290323</v>
+      </c>
+      <c r="E33">
+        <v>-59.94200000000001</v>
+      </c>
+      <c r="F33">
+        <v>189.658</v>
+      </c>
+      <c r="G33">
+        <v>140.3</v>
+      </c>
+      <c r="H33">
+        <v>362.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>41.9</v>
+      </c>
+      <c r="K33">
+        <v>29.4</v>
+      </c>
+      <c r="L33">
+        <v>12.5</v>
+      </c>
+      <c r="M33">
+        <v>45.2903304</v>
+      </c>
+      <c r="N33">
+        <v>-32.7903304</v>
+      </c>
+      <c r="O33">
+        <v>-8.853389208000001</v>
+      </c>
+      <c r="P33">
+        <v>-23.936941192</v>
+      </c>
+      <c r="Q33">
+        <v>5.463058808</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2045515062627083</v>
+      </c>
+      <c r="T33">
+        <v>1.492260698568809</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07451921790351965</v>
+      </c>
+      <c r="W33">
+        <v>0.2210048107646395</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2759971033463691</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.211652030658307</v>
+      </c>
+      <c r="C34">
+        <v>253.8494634571194</v>
+      </c>
+      <c r="D34">
+        <v>309.3254634571193</v>
+      </c>
+      <c r="E34">
+        <v>-53.82400000000001</v>
+      </c>
+      <c r="F34">
+        <v>195.776</v>
+      </c>
+      <c r="G34">
+        <v>140.3</v>
+      </c>
+      <c r="H34">
+        <v>362.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>41.9</v>
+      </c>
+      <c r="K34">
+        <v>29.4</v>
+      </c>
+      <c r="L34">
+        <v>12.5</v>
+      </c>
+      <c r="M34">
+        <v>46.7513088</v>
+      </c>
+      <c r="N34">
+        <v>-34.2513088</v>
+      </c>
+      <c r="O34">
+        <v>-9.247853376</v>
+      </c>
+      <c r="P34">
+        <v>-25.00345542399999</v>
+      </c>
+      <c r="Q34">
+        <v>4.396544576000004</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2069890284136305</v>
+      </c>
+      <c r="T34">
+        <v>1.51420570884188</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07219049234403467</v>
+      </c>
+      <c r="W34">
+        <v>0.2215609104282446</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.267372193866795</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.213652030658307</v>
+      </c>
+      <c r="C35">
+        <v>244.1933236678069</v>
+      </c>
+      <c r="D35">
+        <v>305.7873236678068</v>
+      </c>
+      <c r="E35">
+        <v>-47.70599999999999</v>
+      </c>
+      <c r="F35">
+        <v>201.894</v>
+      </c>
+      <c r="G35">
+        <v>140.3</v>
+      </c>
+      <c r="H35">
+        <v>362.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>41.9</v>
+      </c>
+      <c r="K35">
+        <v>29.4</v>
+      </c>
+      <c r="L35">
+        <v>12.5</v>
+      </c>
+      <c r="M35">
+        <v>48.21228720000001</v>
+      </c>
+      <c r="N35">
+        <v>-35.71228720000001</v>
+      </c>
+      <c r="O35">
+        <v>-9.642317544000003</v>
+      </c>
+      <c r="P35">
+        <v>-26.069969656</v>
+      </c>
+      <c r="Q35">
+        <v>3.330030343999994</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2094993124198042</v>
+      </c>
+      <c r="T35">
+        <v>1.536805794048475</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07000290166694269</v>
+      </c>
+      <c r="W35">
+        <v>0.2220833070819341</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2592700061738618</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.215652030658307</v>
+      </c>
+      <c r="C36">
+        <v>234.6172087394166</v>
+      </c>
+      <c r="D36">
+        <v>302.3292087394166</v>
+      </c>
+      <c r="E36">
+        <v>-41.58799999999999</v>
+      </c>
+      <c r="F36">
+        <v>208.012</v>
+      </c>
+      <c r="G36">
+        <v>140.3</v>
+      </c>
+      <c r="H36">
+        <v>362.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>41.9</v>
+      </c>
+      <c r="K36">
+        <v>29.4</v>
+      </c>
+      <c r="L36">
+        <v>12.5</v>
+      </c>
+      <c r="M36">
+        <v>49.6732656</v>
+      </c>
+      <c r="N36">
+        <v>-37.1732656</v>
+      </c>
+      <c r="O36">
+        <v>-10.036781712</v>
+      </c>
+      <c r="P36">
+        <v>-27.136483888</v>
+      </c>
+      <c r="Q36">
+        <v>2.263516111999998</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.212085665638286</v>
+      </c>
+      <c r="T36">
+        <v>1.560090730321937</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.06794399279438557</v>
+      </c>
+      <c r="W36">
+        <v>0.2225749745207007</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2516444177569835</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.217652030658307</v>
+      </c>
+      <c r="C37">
+        <v>225.1184340551525</v>
+      </c>
+      <c r="D37">
+        <v>298.9484340551525</v>
+      </c>
+      <c r="E37">
+        <v>-35.47</v>
+      </c>
+      <c r="F37">
+        <v>214.13</v>
+      </c>
+      <c r="G37">
+        <v>140.3</v>
+      </c>
+      <c r="H37">
+        <v>362.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>41.9</v>
+      </c>
+      <c r="K37">
+        <v>29.4</v>
+      </c>
+      <c r="L37">
+        <v>12.5</v>
+      </c>
+      <c r="M37">
+        <v>51.134244</v>
+      </c>
+      <c r="N37">
+        <v>-38.634244</v>
+      </c>
+      <c r="O37">
+        <v>-10.43124588</v>
+      </c>
+      <c r="P37">
+        <v>-28.20299812</v>
+      </c>
+      <c r="Q37">
+        <v>1.197001879999995</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2147515989557981</v>
+      </c>
+      <c r="T37">
+        <v>1.584092126173044</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06600273585740311</v>
+      </c>
+      <c r="W37">
+        <v>0.2230385466772521</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2444545772496411</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.219652030658307</v>
+      </c>
+      <c r="C38">
+        <v>215.6944337523971</v>
+      </c>
+      <c r="D38">
+        <v>295.642433752397</v>
+      </c>
+      <c r="E38">
+        <v>-29.35200000000003</v>
+      </c>
+      <c r="F38">
+        <v>220.248</v>
+      </c>
+      <c r="G38">
+        <v>140.3</v>
+      </c>
+      <c r="H38">
+        <v>362.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>41.9</v>
+      </c>
+      <c r="K38">
+        <v>29.4</v>
+      </c>
+      <c r="L38">
+        <v>12.5</v>
+      </c>
+      <c r="M38">
+        <v>52.59522239999999</v>
+      </c>
+      <c r="N38">
+        <v>-40.09522239999999</v>
+      </c>
+      <c r="O38">
+        <v>-10.825710048</v>
+      </c>
+      <c r="P38">
+        <v>-29.26951235199999</v>
+      </c>
+      <c r="Q38">
+        <v>0.1304876480000061</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2175008426894824</v>
+      </c>
+      <c r="T38">
+        <v>1.608843565644497</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06416932652803083</v>
+      </c>
+      <c r="W38">
+        <v>0.2234763648251062</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2376641723260401</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.221652030658307</v>
+      </c>
+      <c r="C39">
+        <v>206.3427542281608</v>
+      </c>
+      <c r="D39">
+        <v>292.4087542281608</v>
+      </c>
+      <c r="E39">
+        <v>-23.23400000000001</v>
+      </c>
+      <c r="F39">
+        <v>226.366</v>
+      </c>
+      <c r="G39">
+        <v>140.3</v>
+      </c>
+      <c r="H39">
+        <v>362.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>41.9</v>
+      </c>
+      <c r="K39">
+        <v>29.4</v>
+      </c>
+      <c r="L39">
+        <v>12.5</v>
+      </c>
+      <c r="M39">
+        <v>54.0562008</v>
+      </c>
+      <c r="N39">
+        <v>-41.5562008</v>
+      </c>
+      <c r="O39">
+        <v>-11.220174216</v>
+      </c>
+      <c r="P39">
+        <v>-30.336026584</v>
+      </c>
+      <c r="Q39">
+        <v>-0.9360265840000004</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2203373640020139</v>
+      </c>
+      <c r="T39">
+        <v>1.634380765099172</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0624350204056516</v>
+      </c>
+      <c r="W39">
+        <v>0.2238905171271304</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2312408163172281</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.223652030658307</v>
+      </c>
+      <c r="C40">
+        <v>197.0610480661368</v>
+      </c>
+      <c r="D40">
+        <v>289.2450480661368</v>
+      </c>
+      <c r="E40">
+        <v>-17.11600000000001</v>
+      </c>
+      <c r="F40">
+        <v>232.484</v>
+      </c>
+      <c r="G40">
+        <v>140.3</v>
+      </c>
+      <c r="H40">
+        <v>362.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>41.9</v>
+      </c>
+      <c r="K40">
+        <v>29.4</v>
+      </c>
+      <c r="L40">
+        <v>12.5</v>
+      </c>
+      <c r="M40">
+        <v>55.5171792</v>
+      </c>
+      <c r="N40">
+        <v>-43.0171792</v>
+      </c>
+      <c r="O40">
+        <v>-11.614638384</v>
+      </c>
+      <c r="P40">
+        <v>-31.402540816</v>
+      </c>
+      <c r="Q40">
+        <v>-2.002540816</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2232653860020464</v>
+      </c>
+      <c r="T40">
+        <v>1.660741745181417</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06079199355287129</v>
+      </c>
+      <c r="W40">
+        <v>0.2242828719395743</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2251555316773011</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.225652030658307</v>
+      </c>
+      <c r="C41">
+        <v>187.8470683537721</v>
+      </c>
+      <c r="D41">
+        <v>286.1490683537721</v>
+      </c>
+      <c r="E41">
+        <v>-10.99799999999999</v>
+      </c>
+      <c r="F41">
+        <v>238.602</v>
+      </c>
+      <c r="G41">
+        <v>140.3</v>
+      </c>
+      <c r="H41">
+        <v>362.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>41.9</v>
+      </c>
+      <c r="K41">
+        <v>29.4</v>
+      </c>
+      <c r="L41">
+        <v>12.5</v>
+      </c>
+      <c r="M41">
+        <v>56.9781576</v>
+      </c>
+      <c r="N41">
+        <v>-44.4781576</v>
+      </c>
+      <c r="O41">
+        <v>-12.009102552</v>
+      </c>
+      <c r="P41">
+        <v>-32.469055048</v>
+      </c>
+      <c r="Q41">
+        <v>-3.069055048000003</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2262894087233914</v>
+      </c>
+      <c r="T41">
+        <v>1.687967019692587</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.05923322448741305</v>
+      </c>
+      <c r="W41">
+        <v>0.2246551059924058</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2193823129163446</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.227652030658307</v>
+      </c>
+      <c r="C42">
+        <v>178.6986633604415</v>
+      </c>
+      <c r="D42">
+        <v>283.1186633604415</v>
+      </c>
+      <c r="E42">
+        <v>-4.879999999999995</v>
+      </c>
+      <c r="F42">
+        <v>244.72</v>
+      </c>
+      <c r="G42">
+        <v>140.3</v>
+      </c>
+      <c r="H42">
+        <v>362.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>41.9</v>
+      </c>
+      <c r="K42">
+        <v>29.4</v>
+      </c>
+      <c r="L42">
+        <v>12.5</v>
+      </c>
+      <c r="M42">
+        <v>58.439136</v>
+      </c>
+      <c r="N42">
+        <v>-45.939136</v>
+      </c>
+      <c r="O42">
+        <v>-12.40356672</v>
+      </c>
+      <c r="P42">
+        <v>-33.53556928</v>
+      </c>
+      <c r="Q42">
+        <v>-4.135569280000006</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2294142322021146</v>
+      </c>
+      <c r="T42">
+        <v>1.716099803354131</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.05775239387522772</v>
+      </c>
+      <c r="W42">
+        <v>0.2250087283425956</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.213897755093436</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.229652030658307</v>
+      </c>
+      <c r="C43">
+        <v>169.6137715502378</v>
+      </c>
+      <c r="D43">
+        <v>280.1517715502378</v>
+      </c>
+      <c r="E43">
+        <v>1.238</v>
+      </c>
+      <c r="F43">
+        <v>250.838</v>
+      </c>
+      <c r="G43">
+        <v>140.3</v>
+      </c>
+      <c r="H43">
+        <v>362.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>41.9</v>
+      </c>
+      <c r="K43">
+        <v>29.4</v>
+      </c>
+      <c r="L43">
+        <v>12.5</v>
+      </c>
+      <c r="M43">
+        <v>59.9001144</v>
+      </c>
+      <c r="N43">
+        <v>-47.4001144</v>
+      </c>
+      <c r="O43">
+        <v>-12.798030888</v>
+      </c>
+      <c r="P43">
+        <v>-34.602083512</v>
+      </c>
+      <c r="Q43">
+        <v>-5.202083512000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2326449819004555</v>
+      </c>
+      <c r="T43">
+        <v>1.745186240699116</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0563437989026612</v>
+      </c>
+      <c r="W43">
+        <v>0.2253451008220445</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.208680736676523</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.231652030658307</v>
+      </c>
+      <c r="C44">
+        <v>160.590416905084</v>
+      </c>
+      <c r="D44">
+        <v>277.2464169050839</v>
+      </c>
+      <c r="E44">
+        <v>7.355999999999966</v>
+      </c>
+      <c r="F44">
+        <v>256.956</v>
+      </c>
+      <c r="G44">
+        <v>140.3</v>
+      </c>
+      <c r="H44">
+        <v>362.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>41.9</v>
+      </c>
+      <c r="K44">
+        <v>29.4</v>
+      </c>
+      <c r="L44">
+        <v>12.5</v>
+      </c>
+      <c r="M44">
+        <v>61.36109279999999</v>
+      </c>
+      <c r="N44">
+        <v>-48.86109279999999</v>
+      </c>
+      <c r="O44">
+        <v>-13.192495056</v>
+      </c>
+      <c r="P44">
+        <v>-35.668597744</v>
+      </c>
+      <c r="Q44">
+        <v>-6.268597743999997</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2359871367608082</v>
+      </c>
+      <c r="T44">
+        <v>1.775275658642204</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05500227988116926</v>
+      </c>
+      <c r="W44">
+        <v>0.2256654555643768</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2037121477080344</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.233652030658307</v>
+      </c>
+      <c r="C45">
+        <v>151.6267045358733</v>
+      </c>
+      <c r="D45">
+        <v>274.4007045358732</v>
+      </c>
+      <c r="E45">
+        <v>13.47399999999996</v>
+      </c>
+      <c r="F45">
+        <v>263.074</v>
+      </c>
+      <c r="G45">
+        <v>140.3</v>
+      </c>
+      <c r="H45">
+        <v>362.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>41.9</v>
+      </c>
+      <c r="K45">
+        <v>29.4</v>
+      </c>
+      <c r="L45">
+        <v>12.5</v>
+      </c>
+      <c r="M45">
+        <v>62.82207119999999</v>
+      </c>
+      <c r="N45">
+        <v>-50.32207119999999</v>
+      </c>
+      <c r="O45">
+        <v>-13.586959224</v>
+      </c>
+      <c r="P45">
+        <v>-36.73511197599999</v>
+      </c>
+      <c r="Q45">
+        <v>-7.335111975999993</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2394465602127522</v>
+      </c>
+      <c r="T45">
+        <v>1.806420845635927</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.0537231570932351</v>
+      </c>
+      <c r="W45">
+        <v>0.2259709100861355</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1989746559008707</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2356520306583071</v>
+      </c>
+      <c r="C46">
+        <v>142.7208165611519</v>
+      </c>
+      <c r="D46">
+        <v>271.6128165611519</v>
+      </c>
+      <c r="E46">
+        <v>19.59200000000001</v>
+      </c>
+      <c r="F46">
+        <v>269.192</v>
+      </c>
+      <c r="G46">
+        <v>140.3</v>
+      </c>
+      <c r="H46">
+        <v>362.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>41.9</v>
+      </c>
+      <c r="K46">
+        <v>29.4</v>
+      </c>
+      <c r="L46">
+        <v>12.5</v>
+      </c>
+      <c r="M46">
+        <v>64.2830496</v>
+      </c>
+      <c r="N46">
+        <v>-51.7830496</v>
+      </c>
+      <c r="O46">
+        <v>-13.981423392</v>
+      </c>
+      <c r="P46">
+        <v>-37.801626208</v>
+      </c>
+      <c r="Q46">
+        <v>-8.401626208000003</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2430295345022657</v>
+      </c>
+      <c r="T46">
+        <v>1.838678360736569</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05250217625020703</v>
+      </c>
+      <c r="W46">
+        <v>0.2262624803114506</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1944525046303964</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.237652030658307</v>
+      </c>
+      <c r="C47">
+        <v>133.8710082345086</v>
+      </c>
+      <c r="D47">
+        <v>268.8810082345086</v>
+      </c>
+      <c r="E47">
+        <v>25.71000000000001</v>
+      </c>
+      <c r="F47">
+        <v>275.31</v>
+      </c>
+      <c r="G47">
+        <v>140.3</v>
+      </c>
+      <c r="H47">
+        <v>362.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>41.9</v>
+      </c>
+      <c r="K47">
+        <v>29.4</v>
+      </c>
+      <c r="L47">
+        <v>12.5</v>
+      </c>
+      <c r="M47">
+        <v>65.744028</v>
+      </c>
+      <c r="N47">
+        <v>-53.244028</v>
+      </c>
+      <c r="O47">
+        <v>-14.37588756</v>
+      </c>
+      <c r="P47">
+        <v>-38.86814044</v>
+      </c>
+      <c r="Q47">
+        <v>-9.468140439999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2467427987659432</v>
+      </c>
+      <c r="T47">
+        <v>1.872108876386324</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05133546122242464</v>
+      </c>
+      <c r="W47">
+        <v>0.226541091860085</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.190131337860832</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.239652030658307</v>
+      </c>
+      <c r="C48">
+        <v>125.0756043033337</v>
+      </c>
+      <c r="D48">
+        <v>266.2036043033337</v>
+      </c>
+      <c r="E48">
+        <v>31.828</v>
+      </c>
+      <c r="F48">
+        <v>281.428</v>
+      </c>
+      <c r="G48">
+        <v>140.3</v>
+      </c>
+      <c r="H48">
+        <v>362.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>41.9</v>
+      </c>
+      <c r="K48">
+        <v>29.4</v>
+      </c>
+      <c r="L48">
+        <v>12.5</v>
+      </c>
+      <c r="M48">
+        <v>67.2050064</v>
+      </c>
+      <c r="N48">
+        <v>-54.7050064</v>
+      </c>
+      <c r="O48">
+        <v>-14.770351728</v>
+      </c>
+      <c r="P48">
+        <v>-39.934654672</v>
+      </c>
+      <c r="Q48">
+        <v>-10.534654672</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2505935913356829</v>
+      </c>
+      <c r="T48">
+        <v>1.906777559282367</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05021947293498063</v>
+      </c>
+      <c r="W48">
+        <v>0.2268075898631266</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1859980479073357</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.241652030658307</v>
+      </c>
+      <c r="C49">
+        <v>116.3329955829828</v>
+      </c>
+      <c r="D49">
+        <v>263.5789955829828</v>
+      </c>
+      <c r="E49">
+        <v>37.946</v>
+      </c>
+      <c r="F49">
+        <v>287.546</v>
+      </c>
+      <c r="G49">
+        <v>140.3</v>
+      </c>
+      <c r="H49">
+        <v>362.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>41.9</v>
+      </c>
+      <c r="K49">
+        <v>29.4</v>
+      </c>
+      <c r="L49">
+        <v>12.5</v>
+      </c>
+      <c r="M49">
+        <v>68.6659848</v>
+      </c>
+      <c r="N49">
+        <v>-56.1659848</v>
+      </c>
+      <c r="O49">
+        <v>-15.164815896</v>
+      </c>
+      <c r="P49">
+        <v>-41.001168904</v>
+      </c>
+      <c r="Q49">
+        <v>-11.601168904</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2545896968325826</v>
+      </c>
+      <c r="T49">
+        <v>1.942754494363167</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04915097351083211</v>
+      </c>
+      <c r="W49">
+        <v>0.2270627475256133</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1820406426327115</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.243652030658307</v>
+      </c>
+      <c r="C50">
+        <v>107.6416357316214</v>
+      </c>
+      <c r="D50">
+        <v>261.0056357316214</v>
+      </c>
+      <c r="E50">
+        <v>44.06399999999999</v>
+      </c>
+      <c r="F50">
+        <v>293.664</v>
+      </c>
+      <c r="G50">
+        <v>140.3</v>
+      </c>
+      <c r="H50">
+        <v>362.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>41.9</v>
+      </c>
+      <c r="K50">
+        <v>29.4</v>
+      </c>
+      <c r="L50">
+        <v>12.5</v>
+      </c>
+      <c r="M50">
+        <v>70.12696320000001</v>
+      </c>
+      <c r="N50">
+        <v>-57.62696320000001</v>
+      </c>
+      <c r="O50">
+        <v>-15.559280064</v>
+      </c>
+      <c r="P50">
+        <v>-42.067683136</v>
+      </c>
+      <c r="Q50">
+        <v>-12.667683136</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2587394986947476</v>
+      </c>
+      <c r="T50">
+        <v>1.980115157716304</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0481269948960231</v>
+      </c>
+      <c r="W50">
+        <v>0.2273072736188297</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.17824812924453</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.245652030658307</v>
+      </c>
+      <c r="C51">
+        <v>99.00003821216785</v>
+      </c>
+      <c r="D51">
+        <v>258.4820382121678</v>
+      </c>
+      <c r="E51">
+        <v>50.18199999999999</v>
+      </c>
+      <c r="F51">
+        <v>299.782</v>
+      </c>
+      <c r="G51">
+        <v>140.3</v>
+      </c>
+      <c r="H51">
+        <v>362.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>41.9</v>
+      </c>
+      <c r="K51">
+        <v>29.4</v>
+      </c>
+      <c r="L51">
+        <v>12.5</v>
+      </c>
+      <c r="M51">
+        <v>71.58794159999999</v>
+      </c>
+      <c r="N51">
+        <v>-59.08794159999999</v>
+      </c>
+      <c r="O51">
+        <v>-15.953744232</v>
+      </c>
+      <c r="P51">
+        <v>-43.134197368</v>
+      </c>
+      <c r="Q51">
+        <v>-13.734197368</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2630520378848407</v>
+      </c>
+      <c r="T51">
+        <v>2.018940945122506</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04714481132671652</v>
+      </c>
+      <c r="W51">
+        <v>0.2275418190551801</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1746104123211722</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.247652030658307</v>
+      </c>
+      <c r="C52">
+        <v>90.4067734287953</v>
+      </c>
+      <c r="D52">
+        <v>256.0067734287953</v>
+      </c>
+      <c r="E52">
+        <v>56.29999999999998</v>
+      </c>
+      <c r="F52">
+        <v>305.9</v>
+      </c>
+      <c r="G52">
+        <v>140.3</v>
+      </c>
+      <c r="H52">
+        <v>362.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>41.9</v>
+      </c>
+      <c r="K52">
+        <v>29.4</v>
+      </c>
+      <c r="L52">
+        <v>12.5</v>
+      </c>
+      <c r="M52">
+        <v>73.04892</v>
+      </c>
+      <c r="N52">
+        <v>-60.54892</v>
+      </c>
+      <c r="O52">
+        <v>-16.3482084</v>
+      </c>
+      <c r="P52">
+        <v>-44.20071159999999</v>
+      </c>
+      <c r="Q52">
+        <v>-14.80071159999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2675370786425375</v>
+      </c>
+      <c r="T52">
+        <v>2.059319764024957</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04620191510018219</v>
+      </c>
+      <c r="W52">
+        <v>0.2277669826740765</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1711182040747489</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.249652030658307</v>
+      </c>
+      <c r="C53">
+        <v>81.86046602640027</v>
+      </c>
+      <c r="D53">
+        <v>253.5784660264003</v>
+      </c>
+      <c r="E53">
+        <v>62.41799999999998</v>
+      </c>
+      <c r="F53">
+        <v>312.018</v>
+      </c>
+      <c r="G53">
+        <v>140.3</v>
+      </c>
+      <c r="H53">
+        <v>362.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>41.9</v>
+      </c>
+      <c r="K53">
+        <v>29.4</v>
+      </c>
+      <c r="L53">
+        <v>12.5</v>
+      </c>
+      <c r="M53">
+        <v>74.5098984</v>
+      </c>
+      <c r="N53">
+        <v>-62.0098984</v>
+      </c>
+      <c r="O53">
+        <v>-16.742672568</v>
+      </c>
+      <c r="P53">
+        <v>-45.26722583199999</v>
+      </c>
+      <c r="Q53">
+        <v>-15.867225832</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2722051822883036</v>
+      </c>
+      <c r="T53">
+        <v>2.10134669798465</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04529599519625704</v>
+      </c>
+      <c r="W53">
+        <v>0.2279833163471338</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1677629451713224</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.251652030658307</v>
+      </c>
+      <c r="C54">
+        <v>73.35979234231911</v>
+      </c>
+      <c r="D54">
+        <v>251.1957923423191</v>
+      </c>
+      <c r="E54">
+        <v>68.53599999999997</v>
+      </c>
+      <c r="F54">
+        <v>318.136</v>
+      </c>
+      <c r="G54">
+        <v>140.3</v>
+      </c>
+      <c r="H54">
+        <v>362.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>41.9</v>
+      </c>
+      <c r="K54">
+        <v>29.4</v>
+      </c>
+      <c r="L54">
+        <v>12.5</v>
+      </c>
+      <c r="M54">
+        <v>75.9708768</v>
+      </c>
+      <c r="N54">
+        <v>-63.4708768</v>
+      </c>
+      <c r="O54">
+        <v>-17.137136736</v>
+      </c>
+      <c r="P54">
+        <v>-46.333740064</v>
+      </c>
+      <c r="Q54">
+        <v>-16.933740064</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2770677902526433</v>
+      </c>
+      <c r="T54">
+        <v>2.145124754192663</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04442491836555978</v>
+      </c>
+      <c r="W54">
+        <v>0.2281913294943043</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1645367346872585</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.253652030658307</v>
+      </c>
+      <c r="C55">
+        <v>64.9034780003725</v>
+      </c>
+      <c r="D55">
+        <v>248.8574780003725</v>
+      </c>
+      <c r="E55">
+        <v>74.65400000000002</v>
+      </c>
+      <c r="F55">
+        <v>324.254</v>
+      </c>
+      <c r="G55">
+        <v>140.3</v>
+      </c>
+      <c r="H55">
+        <v>362.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>41.9</v>
+      </c>
+      <c r="K55">
+        <v>29.4</v>
+      </c>
+      <c r="L55">
+        <v>12.5</v>
+      </c>
+      <c r="M55">
+        <v>77.43185520000002</v>
+      </c>
+      <c r="N55">
+        <v>-64.93185520000002</v>
+      </c>
+      <c r="O55">
+        <v>-17.531600904</v>
+      </c>
+      <c r="P55">
+        <v>-47.40025429600001</v>
+      </c>
+      <c r="Q55">
+        <v>-18.00025429600002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2821373177048272</v>
+      </c>
+      <c r="T55">
+        <v>2.190765706409529</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04358671235866243</v>
+      </c>
+      <c r="W55">
+        <v>0.2283914930887514</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1614322679950461</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.255652030658307</v>
+      </c>
+      <c r="C56">
+        <v>56.49029563805016</v>
+      </c>
+      <c r="D56">
+        <v>246.5622956380502</v>
+      </c>
+      <c r="E56">
+        <v>80.77200000000002</v>
+      </c>
+      <c r="F56">
+        <v>330.372</v>
+      </c>
+      <c r="G56">
+        <v>140.3</v>
+      </c>
+      <c r="H56">
+        <v>362.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>41.9</v>
+      </c>
+      <c r="K56">
+        <v>29.4</v>
+      </c>
+      <c r="L56">
+        <v>12.5</v>
+      </c>
+      <c r="M56">
+        <v>78.8928336</v>
+      </c>
+      <c r="N56">
+        <v>-66.3928336</v>
+      </c>
+      <c r="O56">
+        <v>-17.926065072</v>
+      </c>
+      <c r="P56">
+        <v>-48.466768528</v>
+      </c>
+      <c r="Q56">
+        <v>-19.066768528</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2874272593940626</v>
+      </c>
+      <c r="T56">
+        <v>2.238391047853214</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0427795510186872</v>
+      </c>
+      <c r="W56">
+        <v>0.2285842432167375</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1584427815506934</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.257652030658307</v>
+      </c>
+      <c r="C57">
+        <v>48.11906275831507</v>
+      </c>
+      <c r="D57">
+        <v>244.309062758315</v>
+      </c>
+      <c r="E57">
+        <v>86.89000000000001</v>
+      </c>
+      <c r="F57">
+        <v>336.49</v>
+      </c>
+      <c r="G57">
+        <v>140.3</v>
+      </c>
+      <c r="H57">
+        <v>362.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>41.9</v>
+      </c>
+      <c r="K57">
+        <v>29.4</v>
+      </c>
+      <c r="L57">
+        <v>12.5</v>
+      </c>
+      <c r="M57">
+        <v>80.353812</v>
+      </c>
+      <c r="N57">
+        <v>-67.853812</v>
+      </c>
+      <c r="O57">
+        <v>-18.32052924</v>
+      </c>
+      <c r="P57">
+        <v>-49.53328276000001</v>
+      </c>
+      <c r="Q57">
+        <v>-20.13328276000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2929523096028195</v>
+      </c>
+      <c r="T57">
+        <v>2.288133071138841</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04200174100016561</v>
+      </c>
+      <c r="W57">
+        <v>0.2287699842491605</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1555620037043171</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.259652030658307</v>
+      </c>
+      <c r="C58">
+        <v>39.78863969813227</v>
+      </c>
+      <c r="D58">
+        <v>242.0966396981323</v>
+      </c>
+      <c r="E58">
+        <v>93.00800000000001</v>
+      </c>
+      <c r="F58">
+        <v>342.608</v>
+      </c>
+      <c r="G58">
+        <v>140.3</v>
+      </c>
+      <c r="H58">
+        <v>362.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>41.9</v>
+      </c>
+      <c r="K58">
+        <v>29.4</v>
+      </c>
+      <c r="L58">
+        <v>12.5</v>
+      </c>
+      <c r="M58">
+        <v>81.81479040000001</v>
+      </c>
+      <c r="N58">
+        <v>-69.31479040000001</v>
+      </c>
+      <c r="O58">
+        <v>-18.714993408</v>
+      </c>
+      <c r="P58">
+        <v>-50.59979699200001</v>
+      </c>
+      <c r="Q58">
+        <v>-21.19979699200001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.298728498457429</v>
+      </c>
+      <c r="T58">
+        <v>2.340136095482905</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04125170991087695</v>
+      </c>
+      <c r="W58">
+        <v>0.2289490916732826</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1527841107810257</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2616520306583071</v>
+      </c>
+      <c r="C59">
+        <v>31.49792770638612</v>
+      </c>
+      <c r="D59">
+        <v>239.9239277063861</v>
+      </c>
+      <c r="E59">
+        <v>99.126</v>
+      </c>
+      <c r="F59">
+        <v>348.726</v>
+      </c>
+      <c r="G59">
+        <v>140.3</v>
+      </c>
+      <c r="H59">
+        <v>362.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>41.9</v>
+      </c>
+      <c r="K59">
+        <v>29.4</v>
+      </c>
+      <c r="L59">
+        <v>12.5</v>
+      </c>
+      <c r="M59">
+        <v>83.27576880000001</v>
+      </c>
+      <c r="N59">
+        <v>-70.77576880000001</v>
+      </c>
+      <c r="O59">
+        <v>-19.109457576</v>
+      </c>
+      <c r="P59">
+        <v>-51.666311224</v>
+      </c>
+      <c r="Q59">
+        <v>-22.26631122400001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3047733472587646</v>
+      </c>
+      <c r="T59">
+        <v>2.394557865145299</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04052799570191419</v>
+      </c>
+      <c r="W59">
+        <v>0.2291219146263829</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1501036877848674</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.263652030658307</v>
+      </c>
+      <c r="C60">
+        <v>23.24586712437639</v>
+      </c>
+      <c r="D60">
+        <v>237.7898671243763</v>
+      </c>
+      <c r="E60">
+        <v>105.2439999999999</v>
+      </c>
+      <c r="F60">
+        <v>354.8439999999999</v>
+      </c>
+      <c r="G60">
+        <v>140.3</v>
+      </c>
+      <c r="H60">
+        <v>362.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>41.9</v>
+      </c>
+      <c r="K60">
+        <v>29.4</v>
+      </c>
+      <c r="L60">
+        <v>12.5</v>
+      </c>
+      <c r="M60">
+        <v>84.7367472</v>
+      </c>
+      <c r="N60">
+        <v>-72.2367472</v>
+      </c>
+      <c r="O60">
+        <v>-19.503921744</v>
+      </c>
+      <c r="P60">
+        <v>-52.732825456</v>
+      </c>
+      <c r="Q60">
+        <v>-23.332825456</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3111060460030208</v>
+      </c>
+      <c r="T60">
+        <v>2.451571147648758</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03982923715532947</v>
+      </c>
+      <c r="W60">
+        <v>0.2292887781673073</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1475156931678869</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.265652030658307</v>
+      </c>
+      <c r="C61">
+        <v>15.03143566256114</v>
+      </c>
+      <c r="D61">
+        <v>235.6934356625611</v>
+      </c>
+      <c r="E61">
+        <v>111.3619999999999</v>
+      </c>
+      <c r="F61">
+        <v>360.9619999999999</v>
+      </c>
+      <c r="G61">
+        <v>140.3</v>
+      </c>
+      <c r="H61">
+        <v>362.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>41.9</v>
+      </c>
+      <c r="K61">
+        <v>29.4</v>
+      </c>
+      <c r="L61">
+        <v>12.5</v>
+      </c>
+      <c r="M61">
+        <v>86.19772559999998</v>
+      </c>
+      <c r="N61">
+        <v>-73.69772559999998</v>
+      </c>
+      <c r="O61">
+        <v>-19.898385912</v>
+      </c>
+      <c r="P61">
+        <v>-53.79933968799999</v>
+      </c>
+      <c r="Q61">
+        <v>-24.39933968799999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3177476568811433</v>
+      </c>
+      <c r="T61">
+        <v>2.511365565884093</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03915416533913745</v>
+      </c>
+      <c r="W61">
+        <v>0.229449985317014</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1450154271819906</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.267652030658307</v>
+      </c>
+      <c r="C62">
+        <v>6.853646767661814</v>
+      </c>
+      <c r="D62">
+        <v>233.6336467676618</v>
+      </c>
+      <c r="E62">
+        <v>117.48</v>
+      </c>
+      <c r="F62">
+        <v>367.08</v>
+      </c>
+      <c r="G62">
+        <v>140.3</v>
+      </c>
+      <c r="H62">
+        <v>362.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>41.9</v>
+      </c>
+      <c r="K62">
+        <v>29.4</v>
+      </c>
+      <c r="L62">
+        <v>12.5</v>
+      </c>
+      <c r="M62">
+        <v>87.658704</v>
+      </c>
+      <c r="N62">
+        <v>-75.158704</v>
+      </c>
+      <c r="O62">
+        <v>-20.29285008</v>
+      </c>
+      <c r="P62">
+        <v>-54.86585392</v>
+      </c>
+      <c r="Q62">
+        <v>-25.46585392</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.324721348303172</v>
+      </c>
+      <c r="T62">
+        <v>2.574149705031196</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03850159591681849</v>
+      </c>
+      <c r="W62">
+        <v>0.2296058188950638</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.142598503395624</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.269652030658307</v>
+      </c>
+      <c r="C63">
+        <v>-1.288451925353058</v>
+      </c>
+      <c r="D63">
+        <v>231.6095480746469</v>
+      </c>
+      <c r="E63">
+        <v>123.598</v>
+      </c>
+      <c r="F63">
+        <v>373.198</v>
+      </c>
+      <c r="G63">
+        <v>140.3</v>
+      </c>
+      <c r="H63">
+        <v>362.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>41.9</v>
+      </c>
+      <c r="K63">
+        <v>29.4</v>
+      </c>
+      <c r="L63">
+        <v>12.5</v>
+      </c>
+      <c r="M63">
+        <v>89.1196824</v>
+      </c>
+      <c r="N63">
+        <v>-76.6196824</v>
+      </c>
+      <c r="O63">
+        <v>-20.687314248</v>
+      </c>
+      <c r="P63">
+        <v>-55.932368152</v>
+      </c>
+      <c r="Q63">
+        <v>-26.532368152</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3320526649263302</v>
+      </c>
+      <c r="T63">
+        <v>2.640153543621739</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03787042221326409</v>
+      </c>
+      <c r="W63">
+        <v>0.2297565431754726</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1402608230120892</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.271652030658307</v>
+      </c>
+      <c r="C64">
+        <v>-9.395780061507651</v>
+      </c>
+      <c r="D64">
+        <v>229.6202199384923</v>
+      </c>
+      <c r="E64">
+        <v>129.716</v>
+      </c>
+      <c r="F64">
+        <v>379.316</v>
+      </c>
+      <c r="G64">
+        <v>140.3</v>
+      </c>
+      <c r="H64">
+        <v>362.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>41.9</v>
+      </c>
+      <c r="K64">
+        <v>29.4</v>
+      </c>
+      <c r="L64">
+        <v>12.5</v>
+      </c>
+      <c r="M64">
+        <v>90.5806608</v>
+      </c>
+      <c r="N64">
+        <v>-78.0806608</v>
+      </c>
+      <c r="O64">
+        <v>-21.081778416</v>
+      </c>
+      <c r="P64">
+        <v>-56.998882384</v>
+      </c>
+      <c r="Q64">
+        <v>-27.598882384</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3397698403191283</v>
+      </c>
+      <c r="T64">
+        <v>2.70963126845389</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03725960895175982</v>
+      </c>
+      <c r="W64">
+        <v>0.2299024053823198</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1379985516731845</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.273652030658307</v>
+      </c>
+      <c r="C65">
+        <v>-17.46922595903601</v>
+      </c>
+      <c r="D65">
+        <v>227.6647740409639</v>
+      </c>
+      <c r="E65">
+        <v>135.834</v>
+      </c>
+      <c r="F65">
+        <v>385.434</v>
+      </c>
+      <c r="G65">
+        <v>140.3</v>
+      </c>
+      <c r="H65">
+        <v>362.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>41.9</v>
+      </c>
+      <c r="K65">
+        <v>29.4</v>
+      </c>
+      <c r="L65">
+        <v>12.5</v>
+      </c>
+      <c r="M65">
+        <v>92.04163919999999</v>
+      </c>
+      <c r="N65">
+        <v>-79.54163919999999</v>
+      </c>
+      <c r="O65">
+        <v>-21.476242584</v>
+      </c>
+      <c r="P65">
+        <v>-58.06539661599999</v>
+      </c>
+      <c r="Q65">
+        <v>-28.665396616</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3479041603277534</v>
+      </c>
+      <c r="T65">
+        <v>2.782864545979671</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03666818658744618</v>
+      </c>
+      <c r="W65">
+        <v>0.2300436370429179</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1358080984720229</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.275652030658307</v>
+      </c>
+      <c r="C66">
+        <v>-25.50964793201371</v>
+      </c>
+      <c r="D66">
+        <v>225.7423520679862</v>
+      </c>
+      <c r="E66">
+        <v>141.952</v>
+      </c>
+      <c r="F66">
+        <v>391.552</v>
+      </c>
+      <c r="G66">
+        <v>140.3</v>
+      </c>
+      <c r="H66">
+        <v>362.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>41.9</v>
+      </c>
+      <c r="K66">
+        <v>29.4</v>
+      </c>
+      <c r="L66">
+        <v>12.5</v>
+      </c>
+      <c r="M66">
+        <v>93.50261759999999</v>
+      </c>
+      <c r="N66">
+        <v>-81.00261759999999</v>
+      </c>
+      <c r="O66">
+        <v>-21.870706752</v>
+      </c>
+      <c r="P66">
+        <v>-59.13191084799999</v>
+      </c>
+      <c r="Q66">
+        <v>-29.73191084799999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3564903870035244</v>
+      </c>
+      <c r="T66">
+        <v>2.860166338923551</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03609524617201734</v>
+      </c>
+      <c r="W66">
+        <v>0.2301804552141223</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1336860969333975</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.277652030658307</v>
+      </c>
+      <c r="C67">
+        <v>-33.51787554653987</v>
+      </c>
+      <c r="D67">
+        <v>223.8521244534601</v>
+      </c>
+      <c r="E67">
+        <v>148.07</v>
+      </c>
+      <c r="F67">
+        <v>397.67</v>
+      </c>
+      <c r="G67">
+        <v>140.3</v>
+      </c>
+      <c r="H67">
+        <v>362.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>41.9</v>
+      </c>
+      <c r="K67">
+        <v>29.4</v>
+      </c>
+      <c r="L67">
+        <v>12.5</v>
+      </c>
+      <c r="M67">
+        <v>94.963596</v>
+      </c>
+      <c r="N67">
+        <v>-82.463596</v>
+      </c>
+      <c r="O67">
+        <v>-22.26517092</v>
+      </c>
+      <c r="P67">
+        <v>-60.19842507999999</v>
+      </c>
+      <c r="Q67">
+        <v>-30.79842507999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.365567255203625</v>
+      </c>
+      <c r="T67">
+        <v>2.941885377178509</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03553993469244784</v>
+      </c>
+      <c r="W67">
+        <v>0.2303130635954435</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1316293877498068</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.279652030658307</v>
+      </c>
+      <c r="C68">
+        <v>-41.49471081433165</v>
+      </c>
+      <c r="D68">
+        <v>221.9932891856683</v>
+      </c>
+      <c r="E68">
+        <v>154.188</v>
+      </c>
+      <c r="F68">
+        <v>403.788</v>
+      </c>
+      <c r="G68">
+        <v>140.3</v>
+      </c>
+      <c r="H68">
+        <v>362.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>41.9</v>
+      </c>
+      <c r="K68">
+        <v>29.4</v>
+      </c>
+      <c r="L68">
+        <v>12.5</v>
+      </c>
+      <c r="M68">
+        <v>96.42457440000001</v>
+      </c>
+      <c r="N68">
+        <v>-83.92457440000001</v>
+      </c>
+      <c r="O68">
+        <v>-22.65963508800001</v>
+      </c>
+      <c r="P68">
+        <v>-61.26493931200001</v>
+      </c>
+      <c r="Q68">
+        <v>-31.86493931200001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3751780568272611</v>
+      </c>
+      <c r="T68">
+        <v>3.02841141768376</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03500145083347134</v>
+      </c>
+      <c r="W68">
+        <v>0.230441653540967</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1296350030869309</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.281652030658307</v>
+      </c>
+      <c r="C69">
+        <v>-49.4409293273406</v>
+      </c>
+      <c r="D69">
+        <v>220.1650706726594</v>
+      </c>
+      <c r="E69">
+        <v>160.306</v>
+      </c>
+      <c r="F69">
+        <v>409.906</v>
+      </c>
+      <c r="G69">
+        <v>140.3</v>
+      </c>
+      <c r="H69">
+        <v>362.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>41.9</v>
+      </c>
+      <c r="K69">
+        <v>29.4</v>
+      </c>
+      <c r="L69">
+        <v>12.5</v>
+      </c>
+      <c r="M69">
+        <v>97.88555280000001</v>
+      </c>
+      <c r="N69">
+        <v>-85.38555280000001</v>
+      </c>
+      <c r="O69">
+        <v>-23.054099256</v>
+      </c>
+      <c r="P69">
+        <v>-62.33145354400001</v>
+      </c>
+      <c r="Q69">
+        <v>-32.93145354400001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.385371331276572</v>
+      </c>
+      <c r="T69">
+        <v>3.120181460643874</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03447904111953894</v>
+      </c>
+      <c r="W69">
+        <v>0.2305664049806541</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1277001522945886</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.283652030658307</v>
+      </c>
+      <c r="C70">
+        <v>-57.35728133676218</v>
+      </c>
+      <c r="D70">
+        <v>218.3667186632378</v>
+      </c>
+      <c r="E70">
+        <v>166.424</v>
+      </c>
+      <c r="F70">
+        <v>416.024</v>
+      </c>
+      <c r="G70">
+        <v>140.3</v>
+      </c>
+      <c r="H70">
+        <v>362.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>41.9</v>
+      </c>
+      <c r="K70">
+        <v>29.4</v>
+      </c>
+      <c r="L70">
+        <v>12.5</v>
+      </c>
+      <c r="M70">
+        <v>99.3465312</v>
+      </c>
+      <c r="N70">
+        <v>-86.8465312</v>
+      </c>
+      <c r="O70">
+        <v>-23.448563424</v>
+      </c>
+      <c r="P70">
+        <v>-63.397967776</v>
+      </c>
+      <c r="Q70">
+        <v>-33.997967776</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.396201685378965</v>
+      </c>
+      <c r="T70">
+        <v>3.217687131288995</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03397199639719278</v>
+      </c>
+      <c r="W70">
+        <v>0.2306874872603504</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1258222088784918</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.285652030658307</v>
+      </c>
+      <c r="C71">
+        <v>-65.24449277959212</v>
+      </c>
+      <c r="D71">
+        <v>216.5975072204079</v>
+      </c>
+      <c r="E71">
+        <v>172.542</v>
+      </c>
+      <c r="F71">
+        <v>422.142</v>
+      </c>
+      <c r="G71">
+        <v>140.3</v>
+      </c>
+      <c r="H71">
+        <v>362.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>41.9</v>
+      </c>
+      <c r="K71">
+        <v>29.4</v>
+      </c>
+      <c r="L71">
+        <v>12.5</v>
+      </c>
+      <c r="M71">
+        <v>100.8075096</v>
+      </c>
+      <c r="N71">
+        <v>-88.3075096</v>
+      </c>
+      <c r="O71">
+        <v>-23.843027592</v>
+      </c>
+      <c r="P71">
+        <v>-64.464482008</v>
+      </c>
+      <c r="Q71">
+        <v>-35.06448200800001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4077307720040929</v>
+      </c>
+      <c r="T71">
+        <v>3.321483490362834</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03347964862332042</v>
+      </c>
+      <c r="W71">
+        <v>0.2308050599087511</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1239986986048904</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.287652030658307</v>
+      </c>
+      <c r="C72">
+        <v>-73.10326625568086</v>
+      </c>
+      <c r="D72">
+        <v>214.8567337443191</v>
+      </c>
+      <c r="E72">
+        <v>178.66</v>
+      </c>
+      <c r="F72">
+        <v>428.26</v>
+      </c>
+      <c r="G72">
+        <v>140.3</v>
+      </c>
+      <c r="H72">
+        <v>362.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>41.9</v>
+      </c>
+      <c r="K72">
+        <v>29.4</v>
+      </c>
+      <c r="L72">
+        <v>12.5</v>
+      </c>
+      <c r="M72">
+        <v>102.268488</v>
+      </c>
+      <c r="N72">
+        <v>-89.768488</v>
+      </c>
+      <c r="O72">
+        <v>-24.23749176</v>
+      </c>
+      <c r="P72">
+        <v>-65.53099624000001</v>
+      </c>
+      <c r="Q72">
+        <v>-36.13099624000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4200284644042293</v>
+      </c>
+      <c r="T72">
+        <v>3.432199606708262</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03300136792870156</v>
+      </c>
+      <c r="W72">
+        <v>0.2309192733386261</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1222272886248206</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.289652030658307</v>
+      </c>
+      <c r="C73">
+        <v>-80.93428195804904</v>
+      </c>
+      <c r="D73">
+        <v>213.1437180419509</v>
+      </c>
+      <c r="E73">
+        <v>184.7779999999999</v>
+      </c>
+      <c r="F73">
+        <v>434.3779999999999</v>
+      </c>
+      <c r="G73">
+        <v>140.3</v>
+      </c>
+      <c r="H73">
+        <v>362.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>41.9</v>
+      </c>
+      <c r="K73">
+        <v>29.4</v>
+      </c>
+      <c r="L73">
+        <v>12.5</v>
+      </c>
+      <c r="M73">
+        <v>103.7294664</v>
+      </c>
+      <c r="N73">
+        <v>-91.22946639999999</v>
+      </c>
+      <c r="O73">
+        <v>-24.631955928</v>
+      </c>
+      <c r="P73">
+        <v>-66.597510472</v>
+      </c>
+      <c r="Q73">
+        <v>-37.197510472</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4331742735216164</v>
+      </c>
+      <c r="T73">
+        <v>3.550551317284408</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03253655992970576</v>
+      </c>
+      <c r="W73">
+        <v>0.2310302694887863</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1205057775174287</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.291652030658307</v>
+      </c>
+      <c r="C74">
+        <v>-88.738198559051</v>
+      </c>
+      <c r="D74">
+        <v>211.4578014409489</v>
+      </c>
+      <c r="E74">
+        <v>190.8959999999999</v>
+      </c>
+      <c r="F74">
+        <v>440.4959999999999</v>
+      </c>
+      <c r="G74">
+        <v>140.3</v>
+      </c>
+      <c r="H74">
+        <v>362.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>41.9</v>
+      </c>
+      <c r="K74">
+        <v>29.4</v>
+      </c>
+      <c r="L74">
+        <v>12.5</v>
+      </c>
+      <c r="M74">
+        <v>105.1904448</v>
+      </c>
+      <c r="N74">
+        <v>-92.69044479999998</v>
+      </c>
+      <c r="O74">
+        <v>-25.026420096</v>
+      </c>
+      <c r="P74">
+        <v>-67.66402470399998</v>
+      </c>
+      <c r="Q74">
+        <v>-38.26402470399999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4472590690045313</v>
+      </c>
+      <c r="T74">
+        <v>3.677356721473137</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03208466326401541</v>
+      </c>
+      <c r="W74">
+        <v>0.2311381824125531</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.11883208616302</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.293652030658307</v>
+      </c>
+      <c r="C75">
+        <v>-96.5156540548125</v>
+      </c>
+      <c r="D75">
+        <v>209.7983459451874</v>
+      </c>
+      <c r="E75">
+        <v>197.014</v>
+      </c>
+      <c r="F75">
+        <v>446.614</v>
+      </c>
+      <c r="G75">
+        <v>140.3</v>
+      </c>
+      <c r="H75">
+        <v>362.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>41.9</v>
+      </c>
+      <c r="K75">
+        <v>29.4</v>
+      </c>
+      <c r="L75">
+        <v>12.5</v>
+      </c>
+      <c r="M75">
+        <v>106.6514232</v>
+      </c>
+      <c r="N75">
+        <v>-94.1514232</v>
+      </c>
+      <c r="O75">
+        <v>-25.420884264</v>
+      </c>
+      <c r="P75">
+        <v>-68.73053893599999</v>
+      </c>
+      <c r="Q75">
+        <v>-39.33053893599999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4623871826713657</v>
+      </c>
+      <c r="T75">
+        <v>3.813555118564734</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03164514732889191</v>
+      </c>
+      <c r="W75">
+        <v>0.2312431388178606</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1172042493662663</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.295652030658307</v>
+      </c>
+      <c r="C76">
+        <v>-104.2672665702166</v>
+      </c>
+      <c r="D76">
+        <v>208.1647334297833</v>
+      </c>
+      <c r="E76">
+        <v>203.132</v>
+      </c>
+      <c r="F76">
+        <v>452.732</v>
+      </c>
+      <c r="G76">
+        <v>140.3</v>
+      </c>
+      <c r="H76">
+        <v>362.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>41.9</v>
+      </c>
+      <c r="K76">
+        <v>29.4</v>
+      </c>
+      <c r="L76">
+        <v>12.5</v>
+      </c>
+      <c r="M76">
+        <v>108.1124016</v>
+      </c>
+      <c r="N76">
+        <v>-95.6124016</v>
+      </c>
+      <c r="O76">
+        <v>-25.815348432</v>
+      </c>
+      <c r="P76">
+        <v>-69.79705316799999</v>
+      </c>
+      <c r="Q76">
+        <v>-40.39705316799999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4786789973894952</v>
+      </c>
+      <c r="T76">
+        <v>3.960230315432609</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0312175102028258</v>
+      </c>
+      <c r="W76">
+        <v>0.2313452585635652</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1156204081586141</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.297652030658307</v>
+      </c>
+      <c r="C77">
+        <v>-111.9936351265721</v>
+      </c>
+      <c r="D77">
+        <v>206.5563648734279</v>
+      </c>
+      <c r="E77">
+        <v>209.25</v>
+      </c>
+      <c r="F77">
+        <v>458.85</v>
+      </c>
+      <c r="G77">
+        <v>140.3</v>
+      </c>
+      <c r="H77">
+        <v>362.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>41.9</v>
+      </c>
+      <c r="K77">
+        <v>29.4</v>
+      </c>
+      <c r="L77">
+        <v>12.5</v>
+      </c>
+      <c r="M77">
+        <v>109.57338</v>
+      </c>
+      <c r="N77">
+        <v>-97.07338</v>
+      </c>
+      <c r="O77">
+        <v>-26.2098126</v>
+      </c>
+      <c r="P77">
+        <v>-70.86356739999999</v>
+      </c>
+      <c r="Q77">
+        <v>-41.4635674</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4962741572850751</v>
+      </c>
+      <c r="T77">
+        <v>4.118639528049913</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03080127673345479</v>
+      </c>
+      <c r="W77">
+        <v>0.231444655116051</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1140788027164992</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.299652030658307</v>
+      </c>
+      <c r="C78">
+        <v>-119.6953403739657</v>
+      </c>
+      <c r="D78">
+        <v>204.9726596260342</v>
+      </c>
+      <c r="E78">
+        <v>215.368</v>
+      </c>
+      <c r="F78">
+        <v>464.968</v>
+      </c>
+      <c r="G78">
+        <v>140.3</v>
+      </c>
+      <c r="H78">
+        <v>362.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>41.9</v>
+      </c>
+      <c r="K78">
+        <v>29.4</v>
+      </c>
+      <c r="L78">
+        <v>12.5</v>
+      </c>
+      <c r="M78">
+        <v>111.0343584</v>
+      </c>
+      <c r="N78">
+        <v>-98.5343584</v>
+      </c>
+      <c r="O78">
+        <v>-26.604276768</v>
+      </c>
+      <c r="P78">
+        <v>-71.930081632</v>
+      </c>
+      <c r="Q78">
+        <v>-42.530081632</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5153355805052865</v>
+      </c>
+      <c r="T78">
+        <v>4.290249508385326</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03039599677643565</v>
+      </c>
+      <c r="W78">
+        <v>0.2315414359697872</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1125777658386505</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.301652030658307</v>
+      </c>
+      <c r="C79">
+        <v>-127.3729452901817</v>
+      </c>
+      <c r="D79">
+        <v>203.4130547098182</v>
+      </c>
+      <c r="E79">
+        <v>221.486</v>
+      </c>
+      <c r="F79">
+        <v>471.086</v>
+      </c>
+      <c r="G79">
+        <v>140.3</v>
+      </c>
+      <c r="H79">
+        <v>362.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>41.9</v>
+      </c>
+      <c r="K79">
+        <v>29.4</v>
+      </c>
+      <c r="L79">
+        <v>12.5</v>
+      </c>
+      <c r="M79">
+        <v>112.4953368</v>
+      </c>
+      <c r="N79">
+        <v>-99.99533679999999</v>
+      </c>
+      <c r="O79">
+        <v>-26.998740936</v>
+      </c>
+      <c r="P79">
+        <v>-72.996595864</v>
+      </c>
+      <c r="Q79">
+        <v>-43.596595864</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5360545187881252</v>
+      </c>
+      <c r="T79">
+        <v>4.476782095706428</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03000124357154688</v>
+      </c>
+      <c r="W79">
+        <v>0.2316357030351146</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1111157169316551</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.303652030658307</v>
+      </c>
+      <c r="C80">
+        <v>-135.0269958479534</v>
+      </c>
+      <c r="D80">
+        <v>201.8770041520466</v>
+      </c>
+      <c r="E80">
+        <v>227.604</v>
+      </c>
+      <c r="F80">
+        <v>477.204</v>
+      </c>
+      <c r="G80">
+        <v>140.3</v>
+      </c>
+      <c r="H80">
+        <v>362.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>41.9</v>
+      </c>
+      <c r="K80">
+        <v>29.4</v>
+      </c>
+      <c r="L80">
+        <v>12.5</v>
+      </c>
+      <c r="M80">
+        <v>113.9563152</v>
+      </c>
+      <c r="N80">
+        <v>-101.4563152</v>
+      </c>
+      <c r="O80">
+        <v>-27.393205104</v>
+      </c>
+      <c r="P80">
+        <v>-74.063110096</v>
+      </c>
+      <c r="Q80">
+        <v>-44.663110096</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.558656996914858</v>
+      </c>
+      <c r="T80">
+        <v>4.680272190965811</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02961661224370652</v>
+      </c>
+      <c r="W80">
+        <v>0.2317275529962029</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1096911564581723</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.305652030658307</v>
+      </c>
+      <c r="C81">
+        <v>-142.6580216522093</v>
+      </c>
+      <c r="D81">
+        <v>200.3639783477907</v>
+      </c>
+      <c r="E81">
+        <v>233.722</v>
+      </c>
+      <c r="F81">
+        <v>483.322</v>
+      </c>
+      <c r="G81">
+        <v>140.3</v>
+      </c>
+      <c r="H81">
+        <v>362.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>41.9</v>
+      </c>
+      <c r="K81">
+        <v>29.4</v>
+      </c>
+      <c r="L81">
+        <v>12.5</v>
+      </c>
+      <c r="M81">
+        <v>115.4172936</v>
+      </c>
+      <c r="N81">
+        <v>-102.9172936</v>
+      </c>
+      <c r="O81">
+        <v>-27.787669272</v>
+      </c>
+      <c r="P81">
+        <v>-75.12962432800001</v>
+      </c>
+      <c r="Q81">
+        <v>-45.72962432800001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5834120920060417</v>
+      </c>
+      <c r="T81">
+        <v>4.903142295297516</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02924171841783682</v>
+      </c>
+      <c r="W81">
+        <v>0.2318170776418206</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1083026608068031</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.307652030658307</v>
+      </c>
+      <c r="C82">
+        <v>-150.2665365488771</v>
+      </c>
+      <c r="D82">
+        <v>198.8734634511229</v>
+      </c>
+      <c r="E82">
+        <v>239.84</v>
+      </c>
+      <c r="F82">
+        <v>489.44</v>
+      </c>
+      <c r="G82">
+        <v>140.3</v>
+      </c>
+      <c r="H82">
+        <v>362.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>41.9</v>
+      </c>
+      <c r="K82">
+        <v>29.4</v>
+      </c>
+      <c r="L82">
+        <v>12.5</v>
+      </c>
+      <c r="M82">
+        <v>116.878272</v>
+      </c>
+      <c r="N82">
+        <v>-104.378272</v>
+      </c>
+      <c r="O82">
+        <v>-28.18213344</v>
+      </c>
+      <c r="P82">
+        <v>-76.19613856000001</v>
+      </c>
+      <c r="Q82">
+        <v>-46.79613856000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6106426966063438</v>
+      </c>
+      <c r="T82">
+        <v>5.148299410062393</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02887619693761386</v>
+      </c>
+      <c r="W82">
+        <v>0.2319043641712978</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.106948877546718</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.309652030658307</v>
+      </c>
+      <c r="C83">
+        <v>-157.8530392067139</v>
+      </c>
+      <c r="D83">
+        <v>197.4049607932861</v>
+      </c>
+      <c r="E83">
+        <v>245.958</v>
+      </c>
+      <c r="F83">
+        <v>495.558</v>
+      </c>
+      <c r="G83">
+        <v>140.3</v>
+      </c>
+      <c r="H83">
+        <v>362.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>41.9</v>
+      </c>
+      <c r="K83">
+        <v>29.4</v>
+      </c>
+      <c r="L83">
+        <v>12.5</v>
+      </c>
+      <c r="M83">
+        <v>118.3392504</v>
+      </c>
+      <c r="N83">
+        <v>-105.8392504</v>
+      </c>
+      <c r="O83">
+        <v>-28.576597608</v>
+      </c>
+      <c r="P83">
+        <v>-77.262652792</v>
+      </c>
+      <c r="Q83">
+        <v>-47.862652792</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6407396806382568</v>
+      </c>
+      <c r="T83">
+        <v>5.419262536907782</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0285197006791248</v>
+      </c>
+      <c r="W83">
+        <v>0.231989495477825</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1056285210337956</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.311652030658307</v>
+      </c>
+      <c r="C84">
+        <v>-165.4180136735486</v>
+      </c>
+      <c r="D84">
+        <v>195.9579863264513</v>
+      </c>
+      <c r="E84">
+        <v>252.076</v>
+      </c>
+      <c r="F84">
+        <v>501.676</v>
+      </c>
+      <c r="G84">
+        <v>140.3</v>
+      </c>
+      <c r="H84">
+        <v>362.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>41.9</v>
+      </c>
+      <c r="K84">
+        <v>29.4</v>
+      </c>
+      <c r="L84">
+        <v>12.5</v>
+      </c>
+      <c r="M84">
+        <v>119.8002288</v>
+      </c>
+      <c r="N84">
+        <v>-107.3002288</v>
+      </c>
+      <c r="O84">
+        <v>-28.971061776</v>
+      </c>
+      <c r="P84">
+        <v>-78.329167024</v>
+      </c>
+      <c r="Q84">
+        <v>-48.929167024</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6741807740070489</v>
+      </c>
+      <c r="T84">
+        <v>5.720332677847103</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0281718994513306</v>
+      </c>
+      <c r="W84">
+        <v>0.2320725504110223</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1043403683382614</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.313652030658307</v>
+      </c>
+      <c r="C85">
+        <v>-172.9619299082376</v>
+      </c>
+      <c r="D85">
+        <v>194.5320700917624</v>
+      </c>
+      <c r="E85">
+        <v>258.194</v>
+      </c>
+      <c r="F85">
+        <v>507.794</v>
+      </c>
+      <c r="G85">
+        <v>140.3</v>
+      </c>
+      <c r="H85">
+        <v>362.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>41.9</v>
+      </c>
+      <c r="K85">
+        <v>29.4</v>
+      </c>
+      <c r="L85">
+        <v>12.5</v>
+      </c>
+      <c r="M85">
+        <v>121.2612072</v>
+      </c>
+      <c r="N85">
+        <v>-108.7612072</v>
+      </c>
+      <c r="O85">
+        <v>-29.365525944</v>
+      </c>
+      <c r="P85">
+        <v>-79.395681256</v>
+      </c>
+      <c r="Q85">
+        <v>-49.995681256</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7115561136545225</v>
+      </c>
+      <c r="T85">
+        <v>6.056822835367522</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02783247897601336</v>
+      </c>
+      <c r="W85">
+        <v>0.232153604020528</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1030832554667162</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.315652030658307</v>
+      </c>
+      <c r="C86">
+        <v>-180.4852442895639</v>
+      </c>
+      <c r="D86">
+        <v>193.126755710436</v>
+      </c>
+      <c r="E86">
+        <v>264.3119999999999</v>
+      </c>
+      <c r="F86">
+        <v>513.9119999999999</v>
+      </c>
+      <c r="G86">
+        <v>140.3</v>
+      </c>
+      <c r="H86">
+        <v>362.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>41.9</v>
+      </c>
+      <c r="K86">
+        <v>29.4</v>
+      </c>
+      <c r="L86">
+        <v>12.5</v>
+      </c>
+      <c r="M86">
+        <v>122.7221856</v>
+      </c>
+      <c r="N86">
+        <v>-110.2221856</v>
+      </c>
+      <c r="O86">
+        <v>-29.759990112</v>
+      </c>
+      <c r="P86">
+        <v>-80.46219548799999</v>
+      </c>
+      <c r="Q86">
+        <v>-51.06219548799999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7536033707579297</v>
+      </c>
+      <c r="T86">
+        <v>6.435374262577988</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02750113994058463</v>
+      </c>
+      <c r="W86">
+        <v>0.2322327277821884</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1018560738540172</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.317652030658307</v>
+      </c>
+      <c r="C87">
+        <v>-187.9884001032369</v>
+      </c>
+      <c r="D87">
+        <v>191.741599896763</v>
+      </c>
+      <c r="E87">
+        <v>270.4299999999999</v>
+      </c>
+      <c r="F87">
+        <v>520.03</v>
+      </c>
+      <c r="G87">
+        <v>140.3</v>
+      </c>
+      <c r="H87">
+        <v>362.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>41.9</v>
+      </c>
+      <c r="K87">
+        <v>29.4</v>
+      </c>
+      <c r="L87">
+        <v>12.5</v>
+      </c>
+      <c r="M87">
+        <v>124.183164</v>
+      </c>
+      <c r="N87">
+        <v>-111.683164</v>
+      </c>
+      <c r="O87">
+        <v>-30.15445428</v>
+      </c>
+      <c r="P87">
+        <v>-81.52870971999999</v>
+      </c>
+      <c r="Q87">
+        <v>-52.12870972</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8012569288084583</v>
+      </c>
+      <c r="T87">
+        <v>6.864399213416521</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02717759711775422</v>
+      </c>
+      <c r="W87">
+        <v>0.2323099898082803</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1006577671027934</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3196520306583071</v>
+      </c>
+      <c r="C88">
+        <v>-195.4718280080829</v>
+      </c>
+      <c r="D88">
+        <v>190.376171991917</v>
+      </c>
+      <c r="E88">
+        <v>276.5479999999999</v>
+      </c>
+      <c r="F88">
+        <v>526.1479999999999</v>
+      </c>
+      <c r="G88">
+        <v>140.3</v>
+      </c>
+      <c r="H88">
+        <v>362.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>41.9</v>
+      </c>
+      <c r="K88">
+        <v>29.4</v>
+      </c>
+      <c r="L88">
+        <v>12.5</v>
+      </c>
+      <c r="M88">
+        <v>125.6441424</v>
+      </c>
+      <c r="N88">
+        <v>-113.1441424</v>
+      </c>
+      <c r="O88">
+        <v>-30.54891844799999</v>
+      </c>
+      <c r="P88">
+        <v>-82.59522395199998</v>
+      </c>
+      <c r="Q88">
+        <v>-53.19522395199998</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.8557181380090626</v>
+      </c>
+      <c r="T88">
+        <v>7.354713442946274</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02686157854661755</v>
+      </c>
+      <c r="W88">
+        <v>0.2323854550430677</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09948732795043536</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.321652030658307</v>
+      </c>
+      <c r="C89">
+        <v>-202.9359464824586</v>
+      </c>
+      <c r="D89">
+        <v>189.0300535175413</v>
+      </c>
+      <c r="E89">
+        <v>282.6659999999999</v>
+      </c>
+      <c r="F89">
+        <v>532.266</v>
+      </c>
+      <c r="G89">
+        <v>140.3</v>
+      </c>
+      <c r="H89">
+        <v>362.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>41.9</v>
+      </c>
+      <c r="K89">
+        <v>29.4</v>
+      </c>
+      <c r="L89">
+        <v>12.5</v>
+      </c>
+      <c r="M89">
+        <v>127.1051208</v>
+      </c>
+      <c r="N89">
+        <v>-114.6051208</v>
+      </c>
+      <c r="O89">
+        <v>-30.943382616</v>
+      </c>
+      <c r="P89">
+        <v>-83.661738184</v>
+      </c>
+      <c r="Q89">
+        <v>-54.261738184</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9185579947789904</v>
+      </c>
+      <c r="T89">
+        <v>7.920460630865217</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02655282477021964</v>
+      </c>
+      <c r="W89">
+        <v>0.2324591854448715</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09834379544525795</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3236520306583071</v>
+      </c>
+      <c r="C90">
+        <v>-210.3811622518579</v>
+      </c>
+      <c r="D90">
+        <v>187.7028377481421</v>
+      </c>
+      <c r="E90">
+        <v>288.784</v>
+      </c>
+      <c r="F90">
+        <v>538.384</v>
+      </c>
+      <c r="G90">
+        <v>140.3</v>
+      </c>
+      <c r="H90">
+        <v>362.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>41.9</v>
+      </c>
+      <c r="K90">
+        <v>29.4</v>
+      </c>
+      <c r="L90">
+        <v>12.5</v>
+      </c>
+      <c r="M90">
+        <v>128.5660992</v>
+      </c>
+      <c r="N90">
+        <v>-116.0660992</v>
+      </c>
+      <c r="O90">
+        <v>-31.337846784</v>
+      </c>
+      <c r="P90">
+        <v>-84.728252416</v>
+      </c>
+      <c r="Q90">
+        <v>-55.32825241600001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.9918711610105733</v>
+      </c>
+      <c r="T90">
+        <v>8.580499016770654</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02625108812510351</v>
+      </c>
+      <c r="W90">
+        <v>0.2325312401557253</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09722625231519821</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.325652030658307</v>
+      </c>
+      <c r="C91">
+        <v>-217.80787069863</v>
+      </c>
+      <c r="D91">
+        <v>186.39412930137</v>
+      </c>
+      <c r="E91">
+        <v>294.9019999999999</v>
+      </c>
+      <c r="F91">
+        <v>544.502</v>
+      </c>
+      <c r="G91">
+        <v>140.3</v>
+      </c>
+      <c r="H91">
+        <v>362.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>41.9</v>
+      </c>
+      <c r="K91">
+        <v>29.4</v>
+      </c>
+      <c r="L91">
+        <v>12.5</v>
+      </c>
+      <c r="M91">
+        <v>130.0270776</v>
+      </c>
+      <c r="N91">
+        <v>-117.5270776</v>
+      </c>
+      <c r="O91">
+        <v>-31.732310952</v>
+      </c>
+      <c r="P91">
+        <v>-85.79476664799998</v>
+      </c>
+      <c r="Q91">
+        <v>-56.39476664799998</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.078513993829716</v>
+      </c>
+      <c r="T91">
+        <v>9.360544381931621</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02595613207875404</v>
+      </c>
+      <c r="W91">
+        <v>0.2326016756595936</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09613382251390379</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3276520306583071</v>
+      </c>
+      <c r="C92">
+        <v>-225.2164562546781</v>
+      </c>
+      <c r="D92">
+        <v>185.1035437453219</v>
+      </c>
+      <c r="E92">
+        <v>301.02</v>
+      </c>
+      <c r="F92">
+        <v>550.62</v>
+      </c>
+      <c r="G92">
+        <v>140.3</v>
+      </c>
+      <c r="H92">
+        <v>362.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>41.9</v>
+      </c>
+      <c r="K92">
+        <v>29.4</v>
+      </c>
+      <c r="L92">
+        <v>12.5</v>
+      </c>
+      <c r="M92">
+        <v>131.488056</v>
+      </c>
+      <c r="N92">
+        <v>-118.988056</v>
+      </c>
+      <c r="O92">
+        <v>-32.12677512</v>
+      </c>
+      <c r="P92">
+        <v>-86.86128088</v>
+      </c>
+      <c r="Q92">
+        <v>-57.46128088</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.182485393212688</v>
+      </c>
+      <c r="T92">
+        <v>10.29659882012479</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02566773061121232</v>
+      </c>
+      <c r="W92">
+        <v>0.2326705459300425</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.09506566893041601</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3296520306583071</v>
+      </c>
+      <c r="C93">
+        <v>-232.6072927779531</v>
+      </c>
+      <c r="D93">
+        <v>183.8307072220468</v>
+      </c>
+      <c r="E93">
+        <v>307.1379999999999</v>
+      </c>
+      <c r="F93">
+        <v>556.7379999999999</v>
+      </c>
+      <c r="G93">
+        <v>140.3</v>
+      </c>
+      <c r="H93">
+        <v>362.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>41.9</v>
+      </c>
+      <c r="K93">
+        <v>29.4</v>
+      </c>
+      <c r="L93">
+        <v>12.5</v>
+      </c>
+      <c r="M93">
+        <v>132.9490344</v>
+      </c>
+      <c r="N93">
+        <v>-120.4490344</v>
+      </c>
+      <c r="O93">
+        <v>-32.521239288</v>
+      </c>
+      <c r="P93">
+        <v>-87.92779511199998</v>
+      </c>
+      <c r="Q93">
+        <v>-58.52779511199999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.309561548014098</v>
+      </c>
+      <c r="T93">
+        <v>11.44066535569421</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02538566763746274</v>
+      </c>
+      <c r="W93">
+        <v>0.2327379025681739</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.09402099124986196</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3316520306583071</v>
+      </c>
+      <c r="C94">
+        <v>-239.9807439135237</v>
+      </c>
+      <c r="D94">
+        <v>182.5752560864763</v>
+      </c>
+      <c r="E94">
+        <v>313.256</v>
+      </c>
+      <c r="F94">
+        <v>562.856</v>
+      </c>
+      <c r="G94">
+        <v>140.3</v>
+      </c>
+      <c r="H94">
+        <v>362.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>41.9</v>
+      </c>
+      <c r="K94">
+        <v>29.4</v>
+      </c>
+      <c r="L94">
+        <v>12.5</v>
+      </c>
+      <c r="M94">
+        <v>134.4100128</v>
+      </c>
+      <c r="N94">
+        <v>-121.9100128</v>
+      </c>
+      <c r="O94">
+        <v>-32.915703456</v>
+      </c>
+      <c r="P94">
+        <v>-88.994309344</v>
+      </c>
+      <c r="Q94">
+        <v>-59.594309344</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.46840674151586</v>
+      </c>
+      <c r="T94">
+        <v>12.87074852515599</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02510973646749031</v>
+      </c>
+      <c r="W94">
+        <v>0.2328037949315633</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09299902395366788</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3336520306583071</v>
+      </c>
+      <c r="C95">
+        <v>-247.3371634399475</v>
+      </c>
+      <c r="D95">
+        <v>181.3368365600525</v>
+      </c>
+      <c r="E95">
+        <v>319.3739999999999</v>
+      </c>
+      <c r="F95">
+        <v>568.9739999999999</v>
+      </c>
+      <c r="G95">
+        <v>140.3</v>
+      </c>
+      <c r="H95">
+        <v>362.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>41.9</v>
+      </c>
+      <c r="K95">
+        <v>29.4</v>
+      </c>
+      <c r="L95">
+        <v>12.5</v>
+      </c>
+      <c r="M95">
+        <v>135.8709912</v>
+      </c>
+      <c r="N95">
+        <v>-123.3709912</v>
+      </c>
+      <c r="O95">
+        <v>-33.310167624</v>
+      </c>
+      <c r="P95">
+        <v>-90.06082357599999</v>
+      </c>
+      <c r="Q95">
+        <v>-60.66082357599999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.672636276018126</v>
+      </c>
+      <c r="T95">
+        <v>14.70942688589256</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02483973930117322</v>
+      </c>
+      <c r="W95">
+        <v>0.2328682702548799</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.09199903444878965</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.335652030658307</v>
+      </c>
+      <c r="C96">
+        <v>-254.6768956016438</v>
+      </c>
+      <c r="D96">
+        <v>180.1151043983562</v>
+      </c>
+      <c r="E96">
+        <v>325.492</v>
+      </c>
+      <c r="F96">
+        <v>575.092</v>
+      </c>
+      <c r="G96">
+        <v>140.3</v>
+      </c>
+      <c r="H96">
+        <v>362.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>41.9</v>
+      </c>
+      <c r="K96">
+        <v>29.4</v>
+      </c>
+      <c r="L96">
+        <v>12.5</v>
+      </c>
+      <c r="M96">
+        <v>137.3319696</v>
+      </c>
+      <c r="N96">
+        <v>-124.8319696</v>
+      </c>
+      <c r="O96">
+        <v>-33.70463179200001</v>
+      </c>
+      <c r="P96">
+        <v>-91.12733780799999</v>
+      </c>
+      <c r="Q96">
+        <v>-61.72733780799999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.944942322021148</v>
+      </c>
+      <c r="T96">
+        <v>17.16099803354132</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02457548675541605</v>
+      </c>
+      <c r="W96">
+        <v>0.2329313737628066</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.09102032131635573</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3376520306583071</v>
+      </c>
+      <c r="C97">
+        <v>-262.0002754279184</v>
+      </c>
+      <c r="D97">
+        <v>178.9097245720816</v>
+      </c>
+      <c r="E97">
+        <v>331.61</v>
+      </c>
+      <c r="F97">
+        <v>581.21</v>
+      </c>
+      <c r="G97">
+        <v>140.3</v>
+      </c>
+      <c r="H97">
+        <v>362.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>41.9</v>
+      </c>
+      <c r="K97">
+        <v>29.4</v>
+      </c>
+      <c r="L97">
+        <v>12.5</v>
+      </c>
+      <c r="M97">
+        <v>138.792948</v>
+      </c>
+      <c r="N97">
+        <v>-126.292948</v>
+      </c>
+      <c r="O97">
+        <v>-34.09909596000001</v>
+      </c>
+      <c r="P97">
+        <v>-92.19385204000002</v>
+      </c>
+      <c r="Q97">
+        <v>-62.79385204000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.326170786425379</v>
+      </c>
+      <c r="T97">
+        <v>20.5931976402496</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02431679742114851</v>
+      </c>
+      <c r="W97">
+        <v>0.2329931487758297</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.09006221267092041</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3396520306583071</v>
+      </c>
+      <c r="C98">
+        <v>-269.3076290392641</v>
+      </c>
+      <c r="D98">
+        <v>177.7203709607359</v>
+      </c>
+      <c r="E98">
+        <v>337.728</v>
+      </c>
+      <c r="F98">
+        <v>587.328</v>
+      </c>
+      <c r="G98">
+        <v>140.3</v>
+      </c>
+      <c r="H98">
+        <v>362.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>41.9</v>
+      </c>
+      <c r="K98">
+        <v>29.4</v>
+      </c>
+      <c r="L98">
+        <v>12.5</v>
+      </c>
+      <c r="M98">
+        <v>140.2539264</v>
+      </c>
+      <c r="N98">
+        <v>-127.7539264</v>
+      </c>
+      <c r="O98">
+        <v>-34.49356012800001</v>
+      </c>
+      <c r="P98">
+        <v>-93.260366272</v>
+      </c>
+      <c r="Q98">
+        <v>-63.860366272</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.898013483031717</v>
+      </c>
+      <c r="T98">
+        <v>25.74149705031194</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02406349744801155</v>
+      </c>
+      <c r="W98">
+        <v>0.2330536368094149</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.08912406462226496</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3416520306583071</v>
+      </c>
+      <c r="C99">
+        <v>-276.5992739415249</v>
+      </c>
+      <c r="D99">
+        <v>176.546726058475</v>
+      </c>
+      <c r="E99">
+        <v>343.8459999999999</v>
+      </c>
+      <c r="F99">
+        <v>593.4459999999999</v>
+      </c>
+      <c r="G99">
+        <v>140.3</v>
+      </c>
+      <c r="H99">
+        <v>362.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>41.9</v>
+      </c>
+      <c r="K99">
+        <v>29.4</v>
+      </c>
+      <c r="L99">
+        <v>12.5</v>
+      </c>
+      <c r="M99">
+        <v>141.7149048</v>
+      </c>
+      <c r="N99">
+        <v>-129.2149048</v>
+      </c>
+      <c r="O99">
+        <v>-34.888024296</v>
+      </c>
+      <c r="P99">
+        <v>-94.326880504</v>
+      </c>
+      <c r="Q99">
+        <v>-64.926880504</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.85108464404229</v>
+      </c>
+      <c r="T99">
+        <v>34.32199606708259</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02381542015473308</v>
+      </c>
+      <c r="W99">
+        <v>0.2331128776670498</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08820525983234473</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3436520306583071</v>
+      </c>
+      <c r="C100">
+        <v>-283.8755193084804</v>
+      </c>
+      <c r="D100">
+        <v>175.3884806915195</v>
+      </c>
+      <c r="E100">
+        <v>349.9639999999999</v>
+      </c>
+      <c r="F100">
+        <v>599.564</v>
+      </c>
+      <c r="G100">
+        <v>140.3</v>
+      </c>
+      <c r="H100">
+        <v>362.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>41.9</v>
+      </c>
+      <c r="K100">
+        <v>29.4</v>
+      </c>
+      <c r="L100">
+        <v>12.5</v>
+      </c>
+      <c r="M100">
+        <v>143.1758832</v>
+      </c>
+      <c r="N100">
+        <v>-130.6758832</v>
+      </c>
+      <c r="O100">
+        <v>-35.282488464</v>
+      </c>
+      <c r="P100">
+        <v>-95.39339473599999</v>
+      </c>
+      <c r="Q100">
+        <v>-65.993394736</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.757226966063434</v>
+      </c>
+      <c r="T100">
+        <v>51.48299410062387</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02357240566335826</v>
+      </c>
+      <c r="W100">
+        <v>0.2331709095275901</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08730520616058612</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3456520306583071</v>
+      </c>
+      <c r="C101">
+        <v>-291.1366662533792</v>
+      </c>
+      <c r="D101">
+        <v>174.2453337466207</v>
+      </c>
+      <c r="E101">
+        <v>356.0819999999999</v>
+      </c>
+      <c r="F101">
+        <v>605.6819999999999</v>
+      </c>
+      <c r="G101">
+        <v>140.3</v>
+      </c>
+      <c r="H101">
+        <v>362.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>41.9</v>
+      </c>
+      <c r="K101">
+        <v>29.4</v>
+      </c>
+      <c r="L101">
+        <v>12.5</v>
+      </c>
+      <c r="M101">
+        <v>144.6368616</v>
+      </c>
+      <c r="N101">
+        <v>-132.1368616</v>
+      </c>
+      <c r="O101">
+        <v>-35.676952632</v>
+      </c>
+      <c r="P101">
+        <v>-96.45990896799998</v>
+      </c>
+      <c r="Q101">
+        <v>-67.05990896799997</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>11.47565393212687</v>
+      </c>
+      <c r="T101">
+        <v>102.9659882012478</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02333430055564757</v>
+      </c>
+      <c r="W101">
+        <v>0.2332277690273114</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08642333539128733</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1175429549195353</v>
+        <v>0.1172584389412526</v>
       </c>
       <c r="C2">
-        <v>572.3920378222572</v>
+        <v>568.3278735627924</v>
       </c>
       <c r="D2">
-        <v>440.9920378222572</v>
+        <v>442.7478735627925</v>
       </c>
       <c r="E2">
-        <v>-158.9</v>
+        <v>-153.08</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="G2">
         <v>131.4</v>
@@ -1451,28 +1451,28 @@
         <v>44.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.292746</v>
       </c>
       <c r="N2">
-        <v>44.75</v>
+        <v>44.457254</v>
       </c>
       <c r="O2">
-        <v>12.0825</v>
+        <v>12.00345858</v>
       </c>
       <c r="P2">
-        <v>32.6675</v>
+        <v>32.45379542</v>
       </c>
       <c r="Q2">
-        <v>53.6675</v>
+        <v>53.45379542</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1175429549195353</v>
+        <v>0.1180719686275278</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8657995614446363</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>152.8628913802409</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1172584389412526</v>
+        <v>0.1169739229629698</v>
       </c>
       <c r="C3">
-        <v>568.3278735627924</v>
+        <v>564.2777471223104</v>
       </c>
       <c r="D3">
-        <v>442.7478735627925</v>
+        <v>444.5177471223104</v>
       </c>
       <c r="E3">
-        <v>-153.08</v>
+        <v>-147.26</v>
       </c>
       <c r="F3">
-        <v>5.82</v>
+        <v>11.64</v>
       </c>
       <c r="G3">
         <v>131.4</v>
@@ -1533,28 +1533,28 @@
         <v>44.75</v>
       </c>
       <c r="M3">
-        <v>0.292746</v>
+        <v>0.585492</v>
       </c>
       <c r="N3">
-        <v>44.457254</v>
+        <v>44.164508</v>
       </c>
       <c r="O3">
-        <v>12.00345858</v>
+        <v>11.92441716</v>
       </c>
       <c r="P3">
-        <v>32.45379542</v>
+        <v>32.24009083999999</v>
       </c>
       <c r="Q3">
-        <v>53.45379542</v>
+        <v>53.24009083999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180719686275278</v>
+        <v>0.1186117785336427</v>
       </c>
       <c r="T3">
-        <v>0.8657995614446363</v>
+        <v>0.8722663450241231</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>152.8628913802409</v>
+        <v>76.43144569012044</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1169739229629698</v>
+        <v>0.1166894069846871</v>
       </c>
       <c r="C4">
-        <v>564.2777471223104</v>
+        <v>560.2418275239685</v>
       </c>
       <c r="D4">
-        <v>444.5177471223104</v>
+        <v>446.3018275239685</v>
       </c>
       <c r="E4">
-        <v>-147.26</v>
+        <v>-141.44</v>
       </c>
       <c r="F4">
-        <v>11.64</v>
+        <v>17.46</v>
       </c>
       <c r="G4">
         <v>131.4</v>
@@ -1615,28 +1615,28 @@
         <v>44.75</v>
       </c>
       <c r="M4">
-        <v>0.585492</v>
+        <v>0.878238</v>
       </c>
       <c r="N4">
-        <v>44.164508</v>
+        <v>43.871762</v>
       </c>
       <c r="O4">
-        <v>11.92441716</v>
+        <v>11.84537574</v>
       </c>
       <c r="P4">
-        <v>32.24009083999999</v>
+        <v>32.02638626</v>
       </c>
       <c r="Q4">
-        <v>53.24009083999999</v>
+        <v>53.02638626</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1186117785336427</v>
+        <v>0.1191627185409145</v>
       </c>
       <c r="T4">
-        <v>0.8722663450241231</v>
+        <v>0.878866464347517</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.43144569012044</v>
+        <v>50.95429712674697</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1166894069846871</v>
+        <v>0.1164048910064043</v>
       </c>
       <c r="C5">
-        <v>560.2418275239685</v>
+        <v>556.2202865153695</v>
       </c>
       <c r="D5">
-        <v>446.3018275239685</v>
+        <v>448.1002865153694</v>
       </c>
       <c r="E5">
-        <v>-141.44</v>
+        <v>-135.62</v>
       </c>
       <c r="F5">
-        <v>17.46</v>
+        <v>23.28</v>
       </c>
       <c r="G5">
         <v>131.4</v>
@@ -1697,28 +1697,28 @@
         <v>44.75</v>
       </c>
       <c r="M5">
-        <v>0.878238</v>
+        <v>1.170984</v>
       </c>
       <c r="N5">
-        <v>43.871762</v>
+        <v>43.579016</v>
       </c>
       <c r="O5">
-        <v>11.84537574</v>
+        <v>11.76633432</v>
       </c>
       <c r="P5">
-        <v>32.02638626</v>
+        <v>31.81268168</v>
       </c>
       <c r="Q5">
-        <v>53.02638626</v>
+        <v>52.81268168</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1191627185409145</v>
+        <v>0.1197251364650045</v>
       </c>
       <c r="T5">
-        <v>0.878866464347517</v>
+        <v>0.885604086156815</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.95429712674697</v>
+        <v>38.21572284506023</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1164048910064043</v>
+        <v>0.1161203750281216</v>
       </c>
       <c r="C6">
-        <v>556.2202865153695</v>
+        <v>552.2132986236768</v>
       </c>
       <c r="D6">
-        <v>448.1002865153694</v>
+        <v>449.9132986236768</v>
       </c>
       <c r="E6">
-        <v>-135.62</v>
+        <v>-129.8</v>
       </c>
       <c r="F6">
-        <v>23.28</v>
+        <v>29.1</v>
       </c>
       <c r="G6">
         <v>131.4</v>
@@ -1779,28 +1779,28 @@
         <v>44.75</v>
       </c>
       <c r="M6">
-        <v>1.170984</v>
+        <v>1.46373</v>
       </c>
       <c r="N6">
-        <v>43.579016</v>
+        <v>43.28627</v>
       </c>
       <c r="O6">
-        <v>11.76633432</v>
+        <v>11.6872929</v>
       </c>
       <c r="P6">
-        <v>31.81268168</v>
+        <v>31.5989771</v>
       </c>
       <c r="Q6">
-        <v>52.81268168</v>
+        <v>52.5989771</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1197251364650045</v>
+        <v>0.1202993947664438</v>
       </c>
       <c r="T6">
-        <v>0.885604086156815</v>
+        <v>0.8924835526357822</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.21572284506023</v>
+        <v>30.57257827604818</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1161203750281216</v>
+        <v>0.1158358590498388</v>
       </c>
       <c r="C7">
-        <v>552.2132986236768</v>
+        <v>548.2210412120734</v>
       </c>
       <c r="D7">
-        <v>449.9132986236768</v>
+        <v>451.7410412120734</v>
       </c>
       <c r="E7">
-        <v>-129.8</v>
+        <v>-123.98</v>
       </c>
       <c r="F7">
-        <v>29.1</v>
+        <v>34.92</v>
       </c>
       <c r="G7">
         <v>131.4</v>
@@ -1861,28 +1861,28 @@
         <v>44.75</v>
       </c>
       <c r="M7">
-        <v>1.46373</v>
+        <v>1.756476</v>
       </c>
       <c r="N7">
-        <v>43.28627</v>
+        <v>42.993524</v>
       </c>
       <c r="O7">
-        <v>11.6872929</v>
+        <v>11.60825148</v>
       </c>
       <c r="P7">
-        <v>31.5989771</v>
+        <v>31.38527252</v>
       </c>
       <c r="Q7">
-        <v>52.5989771</v>
+        <v>52.38527252</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1202993947664438</v>
+        <v>0.1208858713296158</v>
       </c>
       <c r="T7">
-        <v>0.8924835526357822</v>
+        <v>0.8995093907419617</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.57257827604818</v>
+        <v>25.47714856337348</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1158358590498388</v>
+        <v>0.1155513430715561</v>
       </c>
       <c r="C8">
-        <v>548.2210412120734</v>
+        <v>544.2436945376026</v>
       </c>
       <c r="D8">
-        <v>451.7410412120734</v>
+        <v>453.5836945376026</v>
       </c>
       <c r="E8">
-        <v>-123.98</v>
+        <v>-118.16</v>
       </c>
       <c r="F8">
-        <v>34.92</v>
+        <v>40.73999999999999</v>
       </c>
       <c r="G8">
         <v>131.4</v>
@@ -1943,28 +1943,28 @@
         <v>44.75</v>
       </c>
       <c r="M8">
-        <v>1.756476</v>
+        <v>2.049221999999999</v>
       </c>
       <c r="N8">
-        <v>42.993524</v>
+        <v>42.700778</v>
       </c>
       <c r="O8">
-        <v>11.60825148</v>
+        <v>11.52921006</v>
       </c>
       <c r="P8">
-        <v>31.38527252</v>
+        <v>31.17156794</v>
       </c>
       <c r="Q8">
-        <v>52.38527252</v>
+        <v>52.17156794</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1208858713296158</v>
+        <v>0.1214849602919958</v>
       </c>
       <c r="T8">
-        <v>0.8995093907419617</v>
+        <v>0.906686322140747</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.47714856337348</v>
+        <v>21.83755591146299</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1155513430715561</v>
+        <v>0.1152668270932733</v>
       </c>
       <c r="C9">
-        <v>544.2436945376026</v>
+        <v>540.2814418104294</v>
       </c>
       <c r="D9">
-        <v>453.5836945376026</v>
+        <v>455.4414418104295</v>
       </c>
       <c r="E9">
-        <v>-118.16</v>
+        <v>-112.34</v>
       </c>
       <c r="F9">
-        <v>40.74</v>
+        <v>46.56</v>
       </c>
       <c r="G9">
         <v>131.4</v>
@@ -2025,28 +2025,28 @@
         <v>44.75</v>
       </c>
       <c r="M9">
-        <v>2.049222</v>
+        <v>2.341968</v>
       </c>
       <c r="N9">
-        <v>42.700778</v>
+        <v>42.408032</v>
       </c>
       <c r="O9">
-        <v>11.52921006</v>
+        <v>11.45016864</v>
       </c>
       <c r="P9">
-        <v>31.17156794</v>
+        <v>30.95786336</v>
       </c>
       <c r="Q9">
-        <v>52.17156794</v>
+        <v>51.95786336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1214849602919958</v>
+        <v>0.122097072927471</v>
       </c>
       <c r="T9">
-        <v>0.906686322140747</v>
+        <v>0.9140192737873321</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.83755591146299</v>
+        <v>19.10786142253011</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1152668270932733</v>
+        <v>0.1149823111149906</v>
       </c>
       <c r="C10">
-        <v>540.2814418104294</v>
+        <v>536.3344692545663</v>
       </c>
       <c r="D10">
-        <v>455.4414418104295</v>
+        <v>457.3144692545663</v>
       </c>
       <c r="E10">
-        <v>-112.34</v>
+        <v>-106.52</v>
       </c>
       <c r="F10">
-        <v>46.56</v>
+        <v>52.38</v>
       </c>
       <c r="G10">
         <v>131.4</v>
@@ -2107,28 +2107,28 @@
         <v>44.75</v>
       </c>
       <c r="M10">
-        <v>2.341968</v>
+        <v>2.634714</v>
       </c>
       <c r="N10">
-        <v>42.408032</v>
+        <v>42.115286</v>
       </c>
       <c r="O10">
-        <v>11.45016864</v>
+        <v>11.37112722</v>
       </c>
       <c r="P10">
-        <v>30.95786336</v>
+        <v>30.74415878</v>
       </c>
       <c r="Q10">
-        <v>51.95786336</v>
+        <v>51.74415878</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.122097072927471</v>
+        <v>0.1227226385879018</v>
       </c>
       <c r="T10">
-        <v>0.9140192737873321</v>
+        <v>0.9215133892063696</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.10786142253011</v>
+        <v>16.98476570891565</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1149823111149906</v>
+        <v>0.1146977951367079</v>
       </c>
       <c r="C11">
-        <v>536.3344692545663</v>
+        <v>532.402966170101</v>
       </c>
       <c r="D11">
-        <v>457.3144692545663</v>
+        <v>459.202966170101</v>
       </c>
       <c r="E11">
-        <v>-106.52</v>
+        <v>-100.7</v>
       </c>
       <c r="F11">
-        <v>52.38</v>
+        <v>58.2</v>
       </c>
       <c r="G11">
         <v>131.4</v>
@@ -2189,28 +2189,28 @@
         <v>44.75</v>
       </c>
       <c r="M11">
-        <v>2.634714</v>
+        <v>2.92746</v>
       </c>
       <c r="N11">
-        <v>42.115286</v>
+        <v>41.82254</v>
       </c>
       <c r="O11">
-        <v>11.37112722</v>
+        <v>11.2920858</v>
       </c>
       <c r="P11">
-        <v>30.74415878</v>
+        <v>30.5304542</v>
       </c>
       <c r="Q11">
-        <v>51.74415878</v>
+        <v>51.5304542</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1227226385879018</v>
+        <v>0.1233621057074532</v>
       </c>
       <c r="T11">
-        <v>0.9215133892063696</v>
+        <v>0.929174040523608</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.98476570891565</v>
+        <v>15.28628913802409</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1146977951367079</v>
+        <v>0.1144132791584251</v>
       </c>
       <c r="C12">
-        <v>532.402966170101</v>
+        <v>528.4871249969742</v>
       </c>
       <c r="D12">
-        <v>459.202966170101</v>
+        <v>461.1071249969742</v>
       </c>
       <c r="E12">
-        <v>-100.7</v>
+        <v>-94.88000000000001</v>
       </c>
       <c r="F12">
-        <v>58.2</v>
+        <v>64.02</v>
       </c>
       <c r="G12">
         <v>131.4</v>
@@ -2271,28 +2271,28 @@
         <v>44.75</v>
       </c>
       <c r="M12">
-        <v>2.92746</v>
+        <v>3.220206</v>
       </c>
       <c r="N12">
-        <v>41.82254</v>
+        <v>41.529794</v>
       </c>
       <c r="O12">
-        <v>11.2920858</v>
+        <v>11.21304438</v>
       </c>
       <c r="P12">
-        <v>30.5304542</v>
+        <v>30.31674962</v>
       </c>
       <c r="Q12">
-        <v>51.5304542</v>
+        <v>51.31674962</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1233621057074532</v>
+        <v>0.124015942874635</v>
       </c>
       <c r="T12">
-        <v>0.929174040523608</v>
+        <v>0.9370068413086494</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.28628913802409</v>
+        <v>13.89662648911281</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1144132791584251</v>
+        <v>0.1142601631801424</v>
       </c>
       <c r="C13">
-        <v>528.4871249969742</v>
+        <v>523.6984235691274</v>
       </c>
       <c r="D13">
-        <v>461.1071249969742</v>
+        <v>462.1384235691274</v>
       </c>
       <c r="E13">
-        <v>-94.88000000000001</v>
+        <v>-89.06</v>
       </c>
       <c r="F13">
-        <v>64.02</v>
+        <v>69.84</v>
       </c>
       <c r="G13">
         <v>131.4</v>
@@ -2353,45 +2353,45 @@
         <v>44.75</v>
       </c>
       <c r="M13">
-        <v>3.220206</v>
+        <v>3.617712</v>
       </c>
       <c r="N13">
-        <v>41.529794</v>
+        <v>41.132288</v>
       </c>
       <c r="O13">
-        <v>11.21304438</v>
+        <v>11.10571776</v>
       </c>
       <c r="P13">
-        <v>30.31674962</v>
+        <v>30.02657024</v>
       </c>
       <c r="Q13">
-        <v>51.31674962</v>
+        <v>51.02657024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.124015942874635</v>
+        <v>0.1246846399774345</v>
       </c>
       <c r="T13">
-        <v>0.9370068413086494</v>
+        <v>0.9450176602933509</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.89662648911281</v>
+        <v>12.36969664804716</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1142601631801424</v>
+        <v>0.1139865972018596</v>
       </c>
       <c r="C14">
-        <v>523.6984235691274</v>
+        <v>519.7325320762798</v>
       </c>
       <c r="D14">
-        <v>462.1384235691274</v>
+        <v>463.9925320762798</v>
       </c>
       <c r="E14">
-        <v>-89.06</v>
+        <v>-83.24000000000001</v>
       </c>
       <c r="F14">
-        <v>69.84</v>
+        <v>75.66</v>
       </c>
       <c r="G14">
         <v>131.4</v>
@@ -2435,28 +2435,28 @@
         <v>44.75</v>
       </c>
       <c r="M14">
-        <v>3.617712</v>
+        <v>3.919188</v>
       </c>
       <c r="N14">
-        <v>41.132288</v>
+        <v>40.830812</v>
       </c>
       <c r="O14">
-        <v>11.10571776</v>
+        <v>11.02431924</v>
       </c>
       <c r="P14">
-        <v>30.02657024</v>
+        <v>29.80649276</v>
       </c>
       <c r="Q14">
-        <v>51.02657024</v>
+        <v>50.80649276</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1246846399774345</v>
+        <v>0.1253687094274248</v>
       </c>
       <c r="T14">
-        <v>0.9450176602933509</v>
+        <v>0.9532126360363213</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.36969664804716</v>
+        <v>11.41818152127431</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1139865972018596</v>
+        <v>0.1137130312235769</v>
       </c>
       <c r="C15">
-        <v>519.7325320762798</v>
+        <v>515.7815779525484</v>
       </c>
       <c r="D15">
-        <v>463.9925320762798</v>
+        <v>465.8615779525484</v>
       </c>
       <c r="E15">
-        <v>-83.24000000000001</v>
+        <v>-77.42</v>
       </c>
       <c r="F15">
-        <v>75.66</v>
+        <v>81.48</v>
       </c>
       <c r="G15">
         <v>131.4</v>
@@ -2517,28 +2517,28 @@
         <v>44.75</v>
       </c>
       <c r="M15">
-        <v>3.919188</v>
+        <v>4.220664</v>
       </c>
       <c r="N15">
-        <v>40.830812</v>
+        <v>40.529336</v>
       </c>
       <c r="O15">
-        <v>11.02431924</v>
+        <v>10.94292072</v>
       </c>
       <c r="P15">
-        <v>29.80649276</v>
+        <v>29.58641528</v>
       </c>
       <c r="Q15">
-        <v>50.80649276</v>
+        <v>50.58641528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1253687094274248</v>
+        <v>0.1260686874692754</v>
       </c>
       <c r="T15">
-        <v>0.9532126360363213</v>
+        <v>0.9615981926105236</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.41818152127431</v>
+        <v>10.60259712689757</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1137130312235769</v>
+        <v>0.1134394652452941</v>
       </c>
       <c r="C16">
-        <v>515.7815779525484</v>
+        <v>511.8457424392835</v>
       </c>
       <c r="D16">
-        <v>465.8615779525484</v>
+        <v>467.7457424392835</v>
       </c>
       <c r="E16">
-        <v>-77.42</v>
+        <v>-71.59999999999999</v>
       </c>
       <c r="F16">
-        <v>81.48</v>
+        <v>87.30000000000001</v>
       </c>
       <c r="G16">
         <v>131.4</v>
@@ -2599,28 +2599,28 @@
         <v>44.75</v>
       </c>
       <c r="M16">
-        <v>4.220664</v>
+        <v>4.52214</v>
       </c>
       <c r="N16">
-        <v>40.529336</v>
+        <v>40.22786</v>
       </c>
       <c r="O16">
-        <v>10.94292072</v>
+        <v>10.8615222</v>
       </c>
       <c r="P16">
-        <v>29.58641528</v>
+        <v>29.3663378</v>
       </c>
       <c r="Q16">
-        <v>50.58641528</v>
+        <v>50.3663378</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1260686874692754</v>
+        <v>0.126785135582699</v>
       </c>
       <c r="T16">
-        <v>0.9615981926105236</v>
+        <v>0.9701810563982367</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.60259712689757</v>
+        <v>9.895757318437731</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1134394652452941</v>
+        <v>0.1133644592670114</v>
       </c>
       <c r="C17">
-        <v>511.8457424392835</v>
+        <v>506.5450054864515</v>
       </c>
       <c r="D17">
-        <v>467.7457424392835</v>
+        <v>468.2650054864515</v>
       </c>
       <c r="E17">
-        <v>-71.60000000000001</v>
+        <v>-65.78</v>
       </c>
       <c r="F17">
-        <v>87.3</v>
+        <v>93.12</v>
       </c>
       <c r="G17">
         <v>131.4</v>
@@ -2681,45 +2681,45 @@
         <v>44.75</v>
       </c>
       <c r="M17">
-        <v>4.522139999999999</v>
+        <v>4.981920000000001</v>
       </c>
       <c r="N17">
-        <v>40.22786</v>
+        <v>39.76808</v>
       </c>
       <c r="O17">
-        <v>10.8615222</v>
+        <v>10.7373816</v>
       </c>
       <c r="P17">
-        <v>29.3663378</v>
+        <v>29.0306984</v>
       </c>
       <c r="Q17">
-        <v>50.3663378</v>
+        <v>50.0306984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.126785135582699</v>
+        <v>0.1275186419845374</v>
       </c>
       <c r="T17">
-        <v>0.9701810563982367</v>
+        <v>0.9789682740856571</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.895757318437733</v>
+        <v>8.98248065003051</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1133644592670114</v>
+        <v>0.1131033032887286</v>
       </c>
       <c r="C18">
-        <v>506.5450054864515</v>
+        <v>502.5420070246786</v>
       </c>
       <c r="D18">
-        <v>468.2650054864515</v>
+        <v>470.0820070246787</v>
       </c>
       <c r="E18">
-        <v>-65.78</v>
+        <v>-59.95999999999999</v>
       </c>
       <c r="F18">
-        <v>93.12</v>
+        <v>98.94000000000001</v>
       </c>
       <c r="G18">
         <v>131.4</v>
@@ -2763,28 +2763,28 @@
         <v>44.75</v>
       </c>
       <c r="M18">
-        <v>4.981920000000001</v>
+        <v>5.293290000000001</v>
       </c>
       <c r="N18">
-        <v>39.76808</v>
+        <v>39.45671</v>
       </c>
       <c r="O18">
-        <v>10.7373816</v>
+        <v>10.6533117</v>
       </c>
       <c r="P18">
-        <v>29.0306984</v>
+        <v>28.8033983</v>
       </c>
       <c r="Q18">
-        <v>50.0306984</v>
+        <v>49.8033983</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1275186419845374</v>
+        <v>0.1282698232394321</v>
       </c>
       <c r="T18">
-        <v>0.9789682740856571</v>
+        <v>0.9879672319583166</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.98248065003051</v>
+        <v>8.454099435322831</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1131033032887286</v>
+        <v>0.1128421473104459</v>
       </c>
       <c r="C19">
-        <v>502.5420070246786</v>
+        <v>498.5531644583625</v>
       </c>
       <c r="D19">
-        <v>470.0820070246787</v>
+        <v>471.9131644583625</v>
       </c>
       <c r="E19">
-        <v>-59.95999999999999</v>
+        <v>-54.13999999999999</v>
       </c>
       <c r="F19">
-        <v>98.94000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="G19">
         <v>131.4</v>
@@ -2845,28 +2845,28 @@
         <v>44.75</v>
       </c>
       <c r="M19">
-        <v>5.293290000000001</v>
+        <v>5.604660000000001</v>
       </c>
       <c r="N19">
-        <v>39.45671</v>
+        <v>39.14534</v>
       </c>
       <c r="O19">
-        <v>10.6533117</v>
+        <v>10.5692418</v>
       </c>
       <c r="P19">
-        <v>28.8033983</v>
+        <v>28.5760982</v>
       </c>
       <c r="Q19">
-        <v>49.8033983</v>
+        <v>49.5760982</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1282698232394321</v>
+        <v>0.1290393259883486</v>
       </c>
       <c r="T19">
-        <v>0.9879672319583166</v>
+        <v>0.9971856766083579</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.454099435322831</v>
+        <v>7.984427244471563</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1128421473104459</v>
+        <v>0.1126919513321632</v>
       </c>
       <c r="C20">
-        <v>498.5531644583624</v>
+        <v>493.7927756371179</v>
       </c>
       <c r="D20">
-        <v>471.9131644583624</v>
+        <v>472.9727756371179</v>
       </c>
       <c r="E20">
-        <v>-54.14000000000001</v>
+        <v>-48.32000000000001</v>
       </c>
       <c r="F20">
-        <v>104.76</v>
+        <v>110.58</v>
       </c>
       <c r="G20">
         <v>131.4</v>
@@ -2927,45 +2927,45 @@
         <v>44.75</v>
       </c>
       <c r="M20">
-        <v>5.604659999999999</v>
+        <v>6.004494</v>
       </c>
       <c r="N20">
-        <v>39.14534</v>
+        <v>38.745506</v>
       </c>
       <c r="O20">
-        <v>10.5692418</v>
+        <v>10.46128662</v>
       </c>
       <c r="P20">
-        <v>28.5760982</v>
+        <v>28.28421938</v>
       </c>
       <c r="Q20">
-        <v>49.5760982</v>
+        <v>49.28421938</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1290393259883486</v>
+        <v>0.1298278288051397</v>
       </c>
       <c r="T20">
-        <v>0.9971856766083579</v>
+        <v>1.006631737175684</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.984427244471567</v>
+        <v>7.452751222667555</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1126919513321632</v>
+        <v>0.1124366353538804</v>
       </c>
       <c r="C21">
-        <v>493.7927756371179</v>
+        <v>489.7849545724979</v>
       </c>
       <c r="D21">
-        <v>472.9727756371179</v>
+        <v>474.7849545724979</v>
       </c>
       <c r="E21">
-        <v>-48.32000000000001</v>
+        <v>-42.5</v>
       </c>
       <c r="F21">
-        <v>110.58</v>
+        <v>116.4</v>
       </c>
       <c r="G21">
         <v>131.4</v>
@@ -3009,28 +3009,28 @@
         <v>44.75</v>
       </c>
       <c r="M21">
-        <v>6.004494</v>
+        <v>6.32052</v>
       </c>
       <c r="N21">
-        <v>38.745506</v>
+        <v>38.42948</v>
       </c>
       <c r="O21">
-        <v>10.46128662</v>
+        <v>10.3759596</v>
       </c>
       <c r="P21">
-        <v>28.28421938</v>
+        <v>28.0535204</v>
       </c>
       <c r="Q21">
-        <v>49.28421938</v>
+        <v>49.0535204</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1298278288051397</v>
+        <v>0.1306360441923505</v>
       </c>
       <c r="T21">
-        <v>1.006631737175684</v>
+        <v>1.016313949257194</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.452751222667555</v>
+        <v>7.080113661534178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1124366353538804</v>
+        <v>0.1121813193755977</v>
       </c>
       <c r="C22">
-        <v>489.7849545724979</v>
+        <v>485.7910735211847</v>
       </c>
       <c r="D22">
-        <v>474.7849545724979</v>
+        <v>476.6110735211847</v>
       </c>
       <c r="E22">
-        <v>-42.5</v>
+        <v>-36.67999999999999</v>
       </c>
       <c r="F22">
-        <v>116.4</v>
+        <v>122.22</v>
       </c>
       <c r="G22">
         <v>131.4</v>
@@ -3091,28 +3091,28 @@
         <v>44.75</v>
       </c>
       <c r="M22">
-        <v>6.32052</v>
+        <v>6.636546000000001</v>
       </c>
       <c r="N22">
-        <v>38.42948</v>
+        <v>38.113454</v>
       </c>
       <c r="O22">
-        <v>10.3759596</v>
+        <v>10.29063258</v>
       </c>
       <c r="P22">
-        <v>28.0535204</v>
+        <v>27.82282142</v>
       </c>
       <c r="Q22">
-        <v>49.0535204</v>
+        <v>48.82282142</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1306360441923505</v>
+        <v>0.1314647207286046</v>
       </c>
       <c r="T22">
-        <v>1.016313949257194</v>
+        <v>1.026241280631906</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.080113661534178</v>
+        <v>6.742965391937311</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1121813193755977</v>
+        <v>0.1119260033973149</v>
       </c>
       <c r="C23">
-        <v>485.7910735211847</v>
+        <v>481.8112939525527</v>
       </c>
       <c r="D23">
-        <v>476.6110735211847</v>
+        <v>478.4512939525526</v>
       </c>
       <c r="E23">
-        <v>-36.68000000000001</v>
+        <v>-30.86000000000001</v>
       </c>
       <c r="F23">
-        <v>122.22</v>
+        <v>128.04</v>
       </c>
       <c r="G23">
         <v>131.4</v>
@@ -3173,28 +3173,28 @@
         <v>44.75</v>
       </c>
       <c r="M23">
-        <v>6.636546</v>
+        <v>6.952572</v>
       </c>
       <c r="N23">
-        <v>38.113454</v>
+        <v>37.797428</v>
       </c>
       <c r="O23">
-        <v>10.29063258</v>
+        <v>10.20530556</v>
       </c>
       <c r="P23">
-        <v>27.82282142</v>
+        <v>27.59212244</v>
       </c>
       <c r="Q23">
-        <v>48.82282142</v>
+        <v>48.59212244</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1314647207286046</v>
+        <v>0.132314645381173</v>
       </c>
       <c r="T23">
-        <v>1.026241280631906</v>
+        <v>1.036423158964945</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.742965391937312</v>
+        <v>6.43646696503107</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1119260033973149</v>
+        <v>0.1116706874190322</v>
       </c>
       <c r="C24">
-        <v>481.8112939525527</v>
+        <v>477.8457798394093</v>
       </c>
       <c r="D24">
-        <v>478.4512939525526</v>
+        <v>480.3057798394092</v>
       </c>
       <c r="E24">
-        <v>-30.86000000000001</v>
+        <v>-25.03999999999999</v>
       </c>
       <c r="F24">
-        <v>128.04</v>
+        <v>133.86</v>
       </c>
       <c r="G24">
         <v>131.4</v>
@@ -3255,28 +3255,28 @@
         <v>44.75</v>
       </c>
       <c r="M24">
-        <v>6.952572</v>
+        <v>7.268598000000001</v>
       </c>
       <c r="N24">
-        <v>37.797428</v>
+        <v>37.481402</v>
       </c>
       <c r="O24">
-        <v>10.20530556</v>
+        <v>10.11997854</v>
       </c>
       <c r="P24">
-        <v>27.59212244</v>
+        <v>27.36142346</v>
       </c>
       <c r="Q24">
-        <v>48.59212244</v>
+        <v>48.36142346</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.132314645381173</v>
+        <v>0.1331866459987431</v>
       </c>
       <c r="T24">
-        <v>1.036423158964945</v>
+        <v>1.04686950167027</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.43646696503107</v>
+        <v>6.156620575247111</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1116706874190322</v>
+        <v>0.1115905714407494</v>
       </c>
       <c r="C25">
-        <v>477.8457798394093</v>
+        <v>472.6106686248997</v>
       </c>
       <c r="D25">
-        <v>480.3057798394092</v>
+        <v>480.8906686248997</v>
       </c>
       <c r="E25">
-        <v>-25.03999999999999</v>
+        <v>-19.22</v>
       </c>
       <c r="F25">
-        <v>133.86</v>
+        <v>139.68</v>
       </c>
       <c r="G25">
         <v>131.4</v>
@@ -3337,45 +3337,45 @@
         <v>44.75</v>
       </c>
       <c r="M25">
-        <v>7.268598000000001</v>
+        <v>7.724304000000001</v>
       </c>
       <c r="N25">
-        <v>37.481402</v>
+        <v>37.025696</v>
       </c>
       <c r="O25">
-        <v>10.11997854</v>
+        <v>9.996937919999999</v>
       </c>
       <c r="P25">
-        <v>27.36142346</v>
+        <v>27.02875808</v>
       </c>
       <c r="Q25">
-        <v>48.36142346</v>
+        <v>48.02875808</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1331866459987431</v>
+        <v>0.1340815940009861</v>
       </c>
       <c r="T25">
-        <v>1.04686950167027</v>
+        <v>1.057590748130998</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.156620575247111</v>
+        <v>5.793402227566392</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1115905714407494</v>
+        <v>0.1113425554624667</v>
       </c>
       <c r="C26">
-        <v>472.6106686248997</v>
+        <v>468.610380547703</v>
       </c>
       <c r="D26">
-        <v>480.8906686248997</v>
+        <v>482.710380547703</v>
       </c>
       <c r="E26">
-        <v>-19.22</v>
+        <v>-13.40000000000001</v>
       </c>
       <c r="F26">
-        <v>139.68</v>
+        <v>145.5</v>
       </c>
       <c r="G26">
         <v>131.4</v>
@@ -3419,28 +3419,28 @@
         <v>44.75</v>
       </c>
       <c r="M26">
-        <v>7.724304000000001</v>
+        <v>8.046150000000001</v>
       </c>
       <c r="N26">
-        <v>37.025696</v>
+        <v>36.70385</v>
       </c>
       <c r="O26">
-        <v>9.996937919999999</v>
+        <v>9.910039500000002</v>
       </c>
       <c r="P26">
-        <v>27.02875808</v>
+        <v>26.7938105</v>
       </c>
       <c r="Q26">
-        <v>48.02875808</v>
+        <v>47.7938105</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1340815940009861</v>
+        <v>0.1350004072832889</v>
       </c>
       <c r="T26">
-        <v>1.057590748130998</v>
+        <v>1.068597894497346</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.793402227566392</v>
+        <v>5.561666138463737</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1113425554624667</v>
+        <v>0.1110945394841839</v>
       </c>
       <c r="C27">
-        <v>468.610380547703</v>
+        <v>464.6239165249003</v>
       </c>
       <c r="D27">
-        <v>482.710380547703</v>
+        <v>484.5439165249003</v>
       </c>
       <c r="E27">
-        <v>-13.40000000000001</v>
+        <v>-7.580000000000013</v>
       </c>
       <c r="F27">
-        <v>145.5</v>
+        <v>151.32</v>
       </c>
       <c r="G27">
         <v>131.4</v>
@@ -3501,28 +3501,28 @@
         <v>44.75</v>
       </c>
       <c r="M27">
-        <v>8.046150000000001</v>
+        <v>8.367996</v>
       </c>
       <c r="N27">
-        <v>36.70385</v>
+        <v>36.382004</v>
       </c>
       <c r="O27">
-        <v>9.910039500000002</v>
+        <v>9.823141080000001</v>
       </c>
       <c r="P27">
-        <v>26.7938105</v>
+        <v>26.55886292</v>
       </c>
       <c r="Q27">
-        <v>47.7938105</v>
+        <v>47.55886292</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1350004072832889</v>
+        <v>0.1359440533570053</v>
       </c>
       <c r="T27">
-        <v>1.068597894497346</v>
+        <v>1.079902531306027</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.561666138463737</v>
+        <v>5.347755902368979</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1110945394841839</v>
+        <v>0.1108465235059012</v>
       </c>
       <c r="C28">
-        <v>464.6239165249003</v>
+        <v>460.6514346857588</v>
       </c>
       <c r="D28">
-        <v>484.5439165249003</v>
+        <v>486.3914346857588</v>
       </c>
       <c r="E28">
-        <v>-7.580000000000013</v>
+        <v>-1.759999999999991</v>
       </c>
       <c r="F28">
-        <v>151.32</v>
+        <v>157.14</v>
       </c>
       <c r="G28">
         <v>131.4</v>
@@ -3583,28 +3583,28 @@
         <v>44.75</v>
       </c>
       <c r="M28">
-        <v>8.367996</v>
+        <v>8.689842000000001</v>
       </c>
       <c r="N28">
-        <v>36.382004</v>
+        <v>36.060158</v>
       </c>
       <c r="O28">
-        <v>9.823141080000001</v>
+        <v>9.73624266</v>
       </c>
       <c r="P28">
-        <v>26.55886292</v>
+        <v>26.32391534</v>
       </c>
       <c r="Q28">
-        <v>47.55886292</v>
+        <v>47.32391534</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1359440533570053</v>
+        <v>0.1369135527478098</v>
       </c>
       <c r="T28">
-        <v>1.079902531306027</v>
+        <v>1.091516884191659</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.347755902368979</v>
+        <v>5.149690868947904</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1108465235059012</v>
+        <v>0.1105985075276184</v>
       </c>
       <c r="C29">
-        <v>460.6514346857588</v>
+        <v>456.6930955805028</v>
       </c>
       <c r="D29">
-        <v>486.3914346857588</v>
+        <v>488.2530955805028</v>
       </c>
       <c r="E29">
-        <v>-1.759999999999991</v>
+        <v>4.060000000000002</v>
       </c>
       <c r="F29">
-        <v>157.14</v>
+        <v>162.96</v>
       </c>
       <c r="G29">
         <v>131.4</v>
@@ -3665,28 +3665,28 @@
         <v>44.75</v>
       </c>
       <c r="M29">
-        <v>8.689842000000001</v>
+        <v>9.011688000000001</v>
       </c>
       <c r="N29">
-        <v>36.060158</v>
+        <v>35.738312</v>
       </c>
       <c r="O29">
-        <v>9.73624266</v>
+        <v>9.649344240000001</v>
       </c>
       <c r="P29">
-        <v>26.32391534</v>
+        <v>26.08896776</v>
       </c>
       <c r="Q29">
-        <v>47.32391534</v>
+        <v>47.08896776</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1369135527478098</v>
+        <v>0.1379099826772478</v>
       </c>
       <c r="T29">
-        <v>1.091516884191659</v>
+        <v>1.10345385799078</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.149690868947904</v>
+        <v>4.965773337914051</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1105985075276184</v>
+        <v>0.1103504915493357</v>
       </c>
       <c r="C30">
-        <v>456.6930955805028</v>
+        <v>452.7490622268207</v>
       </c>
       <c r="D30">
-        <v>488.2530955805028</v>
+        <v>490.1290622268207</v>
       </c>
       <c r="E30">
-        <v>4.060000000000002</v>
+        <v>9.880000000000024</v>
       </c>
       <c r="F30">
-        <v>162.96</v>
+        <v>168.78</v>
       </c>
       <c r="G30">
         <v>131.4</v>
@@ -3747,28 +3747,28 @@
         <v>44.75</v>
       </c>
       <c r="M30">
-        <v>9.011688000000001</v>
+        <v>9.333534000000002</v>
       </c>
       <c r="N30">
-        <v>35.738312</v>
+        <v>35.416466</v>
       </c>
       <c r="O30">
-        <v>9.649344240000001</v>
+        <v>9.562445820000001</v>
       </c>
       <c r="P30">
-        <v>26.08896776</v>
+        <v>25.85402018</v>
       </c>
       <c r="Q30">
-        <v>47.08896776</v>
+        <v>46.85402018</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1379099826772478</v>
+        <v>0.1389344810554024</v>
       </c>
       <c r="T30">
-        <v>1.10345385799078</v>
+        <v>1.115727084572975</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.965773337914051</v>
+        <v>4.794539774537704</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1103504915493357</v>
+        <v>0.1101024755710529</v>
       </c>
       <c r="C31">
-        <v>452.7490622268208</v>
+        <v>448.8195001574517</v>
       </c>
       <c r="D31">
-        <v>490.1290622268207</v>
+        <v>492.0195001574517</v>
       </c>
       <c r="E31">
-        <v>9.879999999999995</v>
+        <v>15.69999999999999</v>
       </c>
       <c r="F31">
-        <v>168.78</v>
+        <v>174.6</v>
       </c>
       <c r="G31">
         <v>131.4</v>
@@ -3829,28 +3829,28 @@
         <v>44.75</v>
       </c>
       <c r="M31">
-        <v>9.333534</v>
+        <v>9.655379999999999</v>
       </c>
       <c r="N31">
-        <v>35.416466</v>
+        <v>35.09462</v>
       </c>
       <c r="O31">
-        <v>9.562445820000001</v>
+        <v>9.4755474</v>
       </c>
       <c r="P31">
-        <v>25.85402018</v>
+        <v>25.6190726</v>
       </c>
       <c r="Q31">
-        <v>46.85402018</v>
+        <v>46.6190726</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1389344810554024</v>
+        <v>0.1399882508157899</v>
       </c>
       <c r="T31">
-        <v>1.115727084572975</v>
+        <v>1.128350974771805</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.794539774537705</v>
+        <v>4.634721782053115</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1101024755710529</v>
+        <v>0.1104202095927702</v>
       </c>
       <c r="C32">
-        <v>448.8195001574517</v>
+        <v>440.5802672961917</v>
       </c>
       <c r="D32">
-        <v>492.0195001574517</v>
+        <v>489.6002672961916</v>
       </c>
       <c r="E32">
-        <v>15.69999999999999</v>
+        <v>21.51999999999998</v>
       </c>
       <c r="F32">
-        <v>174.6</v>
+        <v>180.42</v>
       </c>
       <c r="G32">
         <v>131.4</v>
@@ -3911,45 +3911,45 @@
         <v>44.75</v>
       </c>
       <c r="M32">
-        <v>9.655379999999999</v>
+        <v>10.428276</v>
       </c>
       <c r="N32">
-        <v>35.09462</v>
+        <v>34.321724</v>
       </c>
       <c r="O32">
-        <v>9.4755474</v>
+        <v>9.266865480000002</v>
       </c>
       <c r="P32">
-        <v>25.6190726</v>
+        <v>25.05485852</v>
       </c>
       <c r="Q32">
-        <v>46.6190726</v>
+        <v>46.05485852</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1399882508157899</v>
+        <v>0.1410725646272032</v>
       </c>
       <c r="T32">
-        <v>1.128350974771805</v>
+        <v>1.14134077483147</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.634721782053115</v>
+        <v>4.291217455310926</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1104202095927702</v>
+        <v>0.1101904436144874</v>
       </c>
       <c r="C33">
-        <v>440.5802672961917</v>
+        <v>436.5073197789532</v>
       </c>
       <c r="D33">
-        <v>489.6002672961916</v>
+        <v>491.3473197789532</v>
       </c>
       <c r="E33">
-        <v>21.51999999999998</v>
+        <v>27.34</v>
       </c>
       <c r="F33">
-        <v>180.42</v>
+        <v>186.24</v>
       </c>
       <c r="G33">
         <v>131.4</v>
@@ -3993,28 +3993,28 @@
         <v>44.75</v>
       </c>
       <c r="M33">
-        <v>10.428276</v>
+        <v>10.764672</v>
       </c>
       <c r="N33">
-        <v>34.321724</v>
+        <v>33.985328</v>
       </c>
       <c r="O33">
-        <v>9.266865480000002</v>
+        <v>9.176038559999999</v>
       </c>
       <c r="P33">
-        <v>25.05485852</v>
+        <v>24.80928944</v>
       </c>
       <c r="Q33">
-        <v>46.05485852</v>
+        <v>45.80928944</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1410725646272032</v>
+        <v>0.1421887700213051</v>
       </c>
       <c r="T33">
-        <v>1.14134077483147</v>
+        <v>1.154712627834066</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.291217455310926</v>
+        <v>4.157116909832459</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1101904436144874</v>
+        <v>0.1099606776362047</v>
       </c>
       <c r="C34">
-        <v>436.5073197789532</v>
+        <v>432.4468850105696</v>
       </c>
       <c r="D34">
-        <v>491.3473197789532</v>
+        <v>493.1068850105696</v>
       </c>
       <c r="E34">
-        <v>27.34</v>
+        <v>33.16</v>
       </c>
       <c r="F34">
-        <v>186.24</v>
+        <v>192.06</v>
       </c>
       <c r="G34">
         <v>131.4</v>
@@ -4075,28 +4075,28 @@
         <v>44.75</v>
       </c>
       <c r="M34">
-        <v>10.764672</v>
+        <v>11.101068</v>
       </c>
       <c r="N34">
-        <v>33.985328</v>
+        <v>33.648932</v>
       </c>
       <c r="O34">
-        <v>9.176038559999999</v>
+        <v>9.085211640000001</v>
       </c>
       <c r="P34">
-        <v>24.80928944</v>
+        <v>24.56372036</v>
       </c>
       <c r="Q34">
-        <v>45.80928944</v>
+        <v>45.56372036</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1421887700213051</v>
+        <v>0.14333829497941</v>
       </c>
       <c r="T34">
-        <v>1.154712627834066</v>
+        <v>1.168483640627785</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.157116909832459</v>
+        <v>4.031143670140566</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1099606776362047</v>
+        <v>0.1105996116579219</v>
       </c>
       <c r="C35">
-        <v>432.4468850105696</v>
+        <v>421.7647761627653</v>
       </c>
       <c r="D35">
-        <v>493.1068850105696</v>
+        <v>488.2447761627653</v>
       </c>
       <c r="E35">
-        <v>33.16</v>
+        <v>38.98000000000002</v>
       </c>
       <c r="F35">
-        <v>192.06</v>
+        <v>197.88</v>
       </c>
       <c r="G35">
         <v>131.4</v>
@@ -4157,45 +4157,45 @@
         <v>44.75</v>
       </c>
       <c r="M35">
-        <v>11.101068</v>
+        <v>12.130044</v>
       </c>
       <c r="N35">
-        <v>33.648932</v>
+        <v>32.619956</v>
       </c>
       <c r="O35">
-        <v>9.085211640000001</v>
+        <v>8.807388120000001</v>
       </c>
       <c r="P35">
-        <v>24.56372036</v>
+        <v>23.81256788</v>
       </c>
       <c r="Q35">
-        <v>45.56372036</v>
+        <v>44.81256788</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.14333829497941</v>
+        <v>0.1445226540271545</v>
       </c>
       <c r="T35">
-        <v>1.168483640627785</v>
+        <v>1.182671956839495</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.031143670140566</v>
+        <v>3.689186947714287</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1105996116579219</v>
+        <v>0.1103953956796392</v>
       </c>
       <c r="C36">
-        <v>421.7647761627653</v>
+        <v>417.4883441455362</v>
       </c>
       <c r="D36">
-        <v>488.2447761627653</v>
+        <v>489.7883441455363</v>
       </c>
       <c r="E36">
-        <v>38.98000000000002</v>
+        <v>44.80000000000001</v>
       </c>
       <c r="F36">
-        <v>197.88</v>
+        <v>203.7</v>
       </c>
       <c r="G36">
         <v>131.4</v>
@@ -4239,28 +4239,28 @@
         <v>44.75</v>
       </c>
       <c r="M36">
-        <v>12.130044</v>
+        <v>12.48681</v>
       </c>
       <c r="N36">
-        <v>32.619956</v>
+        <v>32.26318999999999</v>
       </c>
       <c r="O36">
-        <v>8.807388120000001</v>
+        <v>8.711061299999999</v>
       </c>
       <c r="P36">
-        <v>23.81256788</v>
+        <v>23.5521287</v>
       </c>
       <c r="Q36">
-        <v>44.81256788</v>
+        <v>44.5521287</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1445226540271545</v>
+        <v>0.1457434548917526</v>
       </c>
       <c r="T36">
-        <v>1.182671956839495</v>
+        <v>1.19729683662695</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.689186947714287</v>
+        <v>3.583781606351021</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1103953956796392</v>
+        <v>0.1109270197013565</v>
       </c>
       <c r="C37">
-        <v>417.4883441455362</v>
+        <v>407.6702608538566</v>
       </c>
       <c r="D37">
-        <v>489.7883441455363</v>
+        <v>485.7902608538566</v>
       </c>
       <c r="E37">
-        <v>44.80000000000001</v>
+        <v>50.62000000000003</v>
       </c>
       <c r="F37">
-        <v>203.7</v>
+        <v>209.52</v>
       </c>
       <c r="G37">
         <v>131.4</v>
@@ -4321,45 +4321,45 @@
         <v>44.75</v>
       </c>
       <c r="M37">
-        <v>12.48681</v>
+        <v>13.430232</v>
       </c>
       <c r="N37">
-        <v>32.26318999999999</v>
+        <v>31.319768</v>
       </c>
       <c r="O37">
-        <v>8.711061299999999</v>
+        <v>8.456337359999999</v>
       </c>
       <c r="P37">
-        <v>23.5521287</v>
+        <v>22.86343064</v>
       </c>
       <c r="Q37">
-        <v>44.5521287</v>
+        <v>43.86343064</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1457434548917526</v>
+        <v>0.1470024057833695</v>
       </c>
       <c r="T37">
-        <v>1.19729683662695</v>
+        <v>1.212378743907762</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.583781606351021</v>
+        <v>3.332034770508804</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1109270197013565</v>
+        <v>0.1107432437230737</v>
       </c>
       <c r="C38">
-        <v>407.6702608538567</v>
+        <v>403.2249470461467</v>
       </c>
       <c r="D38">
-        <v>485.7902608538566</v>
+        <v>487.1649470461467</v>
       </c>
       <c r="E38">
-        <v>50.61999999999998</v>
+        <v>56.44</v>
       </c>
       <c r="F38">
-        <v>209.52</v>
+        <v>215.34</v>
       </c>
       <c r="G38">
         <v>131.4</v>
@@ -4403,28 +4403,28 @@
         <v>44.75</v>
       </c>
       <c r="M38">
-        <v>13.430232</v>
+        <v>13.803294</v>
       </c>
       <c r="N38">
-        <v>31.319768</v>
+        <v>30.946706</v>
       </c>
       <c r="O38">
-        <v>8.456337360000001</v>
+        <v>8.35561062</v>
       </c>
       <c r="P38">
-        <v>22.86343064</v>
+        <v>22.59109538</v>
       </c>
       <c r="Q38">
-        <v>43.86343064</v>
+        <v>43.59109538</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1470024057833695</v>
+        <v>0.1483013233699583</v>
       </c>
       <c r="T38">
-        <v>1.212378743907762</v>
+        <v>1.227939441895903</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.332034770508804</v>
+        <v>3.241979776711269</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1107432437230737</v>
+        <v>0.110559467744791</v>
       </c>
       <c r="C39">
-        <v>403.2249470461467</v>
+        <v>398.7874354736505</v>
       </c>
       <c r="D39">
-        <v>487.1649470461467</v>
+        <v>488.5474354736504</v>
       </c>
       <c r="E39">
-        <v>56.44</v>
+        <v>62.25999999999999</v>
       </c>
       <c r="F39">
-        <v>215.34</v>
+        <v>221.16</v>
       </c>
       <c r="G39">
         <v>131.4</v>
@@ -4485,28 +4485,28 @@
         <v>44.75</v>
       </c>
       <c r="M39">
-        <v>13.803294</v>
+        <v>14.176356</v>
       </c>
       <c r="N39">
-        <v>30.946706</v>
+        <v>30.573644</v>
       </c>
       <c r="O39">
-        <v>8.35561062</v>
+        <v>8.254883880000001</v>
       </c>
       <c r="P39">
-        <v>22.59109538</v>
+        <v>22.31876012</v>
       </c>
       <c r="Q39">
-        <v>43.59109538</v>
+        <v>43.31876012</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1483013233699583</v>
+        <v>0.1496421415238564</v>
       </c>
       <c r="T39">
-        <v>1.227939441895903</v>
+        <v>1.244002097883661</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.241979776711269</v>
+        <v>3.156664519429394</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.110559467744791</v>
+        <v>0.1103756917665082</v>
       </c>
       <c r="C40">
-        <v>398.7874354736505</v>
+        <v>394.3577927495172</v>
       </c>
       <c r="D40">
-        <v>488.5474354736504</v>
+        <v>489.9377927495172</v>
       </c>
       <c r="E40">
-        <v>62.25999999999999</v>
+        <v>68.08000000000001</v>
       </c>
       <c r="F40">
-        <v>221.16</v>
+        <v>226.98</v>
       </c>
       <c r="G40">
         <v>131.4</v>
@@ -4567,28 +4567,28 @@
         <v>44.75</v>
       </c>
       <c r="M40">
-        <v>14.176356</v>
+        <v>14.549418</v>
       </c>
       <c r="N40">
-        <v>30.573644</v>
+        <v>30.200582</v>
       </c>
       <c r="O40">
-        <v>8.254883880000001</v>
+        <v>8.154157140000001</v>
       </c>
       <c r="P40">
-        <v>22.31876012</v>
+        <v>22.04642485999999</v>
       </c>
       <c r="Q40">
-        <v>43.31876012</v>
+        <v>43.04642485999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1496421415238564</v>
+        <v>0.151026920928702</v>
       </c>
       <c r="T40">
-        <v>1.244002097883661</v>
+        <v>1.260591398330033</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.156664519429394</v>
+        <v>3.075724403546588</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1103756917665082</v>
+        <v>0.1124695157882255</v>
       </c>
       <c r="C41">
-        <v>394.3577927495172</v>
+        <v>373.1507975467223</v>
       </c>
       <c r="D41">
-        <v>489.9377927495172</v>
+        <v>474.5507975467223</v>
       </c>
       <c r="E41">
-        <v>68.08000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F41">
-        <v>226.98</v>
+        <v>232.8</v>
       </c>
       <c r="G41">
         <v>131.4</v>
@@ -4649,45 +4649,45 @@
         <v>44.75</v>
       </c>
       <c r="M41">
-        <v>14.549418</v>
+        <v>16.73832</v>
       </c>
       <c r="N41">
-        <v>30.200582</v>
+        <v>28.01168</v>
       </c>
       <c r="O41">
-        <v>8.154157140000001</v>
+        <v>7.5631536</v>
       </c>
       <c r="P41">
-        <v>22.04642485999999</v>
+        <v>20.4485264</v>
       </c>
       <c r="Q41">
-        <v>43.04642485999999</v>
+        <v>41.4485264</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.151026920928702</v>
+        <v>0.1524578596470425</v>
       </c>
       <c r="T41">
-        <v>1.260591398330033</v>
+        <v>1.277733675457952</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.075724403546588</v>
+        <v>2.673506062735089</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1124695157882255</v>
+        <v>0.1123426798099428</v>
       </c>
       <c r="C42">
-        <v>373.1507975467223</v>
+        <v>368.2353315213626</v>
       </c>
       <c r="D42">
-        <v>474.5507975467223</v>
+        <v>475.4553315213626</v>
       </c>
       <c r="E42">
-        <v>73.90000000000001</v>
+        <v>79.72</v>
       </c>
       <c r="F42">
-        <v>232.8</v>
+        <v>238.62</v>
       </c>
       <c r="G42">
         <v>131.4</v>
@@ -4731,28 +4731,28 @@
         <v>44.75</v>
       </c>
       <c r="M42">
-        <v>16.73832</v>
+        <v>17.156778</v>
       </c>
       <c r="N42">
-        <v>28.01168</v>
+        <v>27.593222</v>
       </c>
       <c r="O42">
-        <v>7.5631536</v>
+        <v>7.450169939999999</v>
       </c>
       <c r="P42">
-        <v>20.4485264</v>
+        <v>20.14305206</v>
       </c>
       <c r="Q42">
-        <v>41.4485264</v>
+        <v>41.14305206</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1524578596470425</v>
+        <v>0.1539373047626148</v>
       </c>
       <c r="T42">
-        <v>1.277733675457952</v>
+        <v>1.2954570467258</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.673506062735089</v>
+        <v>2.608298597790331</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1123426798099428</v>
+        <v>0.11221584383166</v>
       </c>
       <c r="C43">
-        <v>368.2353315213626</v>
+        <v>363.3233203177725</v>
       </c>
       <c r="D43">
-        <v>475.4553315213626</v>
+        <v>476.3633203177725</v>
       </c>
       <c r="E43">
-        <v>79.72</v>
+        <v>85.54000000000002</v>
       </c>
       <c r="F43">
-        <v>238.62</v>
+        <v>244.44</v>
       </c>
       <c r="G43">
         <v>131.4</v>
@@ -4813,28 +4813,28 @@
         <v>44.75</v>
       </c>
       <c r="M43">
-        <v>17.156778</v>
+        <v>17.575236</v>
       </c>
       <c r="N43">
-        <v>27.593222</v>
+        <v>27.174764</v>
       </c>
       <c r="O43">
-        <v>7.450169939999999</v>
+        <v>7.337186279999999</v>
       </c>
       <c r="P43">
-        <v>20.14305206</v>
+        <v>19.83757772</v>
       </c>
       <c r="Q43">
-        <v>41.14305206</v>
+        <v>40.83757772</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1539373047626148</v>
+        <v>0.155467765227</v>
       </c>
       <c r="T43">
-        <v>1.2954570467258</v>
+        <v>1.313791568727022</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.608298597790331</v>
+        <v>2.546196250223894</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.11221584383166</v>
+        <v>0.1133132178533773</v>
       </c>
       <c r="C44">
-        <v>363.3233203177726</v>
+        <v>349.760410866308</v>
       </c>
       <c r="D44">
-        <v>476.3633203177725</v>
+        <v>468.620410866308</v>
       </c>
       <c r="E44">
-        <v>85.53999999999999</v>
+        <v>91.35999999999999</v>
       </c>
       <c r="F44">
-        <v>244.44</v>
+        <v>250.26</v>
       </c>
       <c r="G44">
         <v>131.4</v>
@@ -4895,45 +4895,45 @@
         <v>44.75</v>
       </c>
       <c r="M44">
-        <v>17.575236</v>
+        <v>18.969708</v>
       </c>
       <c r="N44">
-        <v>27.174764</v>
+        <v>25.780292</v>
       </c>
       <c r="O44">
-        <v>7.33718628</v>
+        <v>6.96067884</v>
       </c>
       <c r="P44">
-        <v>19.83757772</v>
+        <v>18.81961316</v>
       </c>
       <c r="Q44">
-        <v>40.83757772</v>
+        <v>39.81961316</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.155467765227</v>
+        <v>0.1570519260585566</v>
       </c>
       <c r="T44">
-        <v>1.313791568727022</v>
+        <v>1.332769407289691</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.546196250223895</v>
+        <v>2.359024187404466</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1133132178533773</v>
+        <v>0.1132148518750945</v>
       </c>
       <c r="C45">
-        <v>349.760410866308</v>
+        <v>344.6241816360418</v>
       </c>
       <c r="D45">
-        <v>468.620410866308</v>
+        <v>469.3041816360418</v>
       </c>
       <c r="E45">
-        <v>91.35999999999999</v>
+        <v>97.17999999999998</v>
       </c>
       <c r="F45">
-        <v>250.26</v>
+        <v>256.08</v>
       </c>
       <c r="G45">
         <v>131.4</v>
@@ -4977,28 +4977,28 @@
         <v>44.75</v>
       </c>
       <c r="M45">
-        <v>18.969708</v>
+        <v>19.410864</v>
       </c>
       <c r="N45">
-        <v>25.780292</v>
+        <v>25.339136</v>
       </c>
       <c r="O45">
-        <v>6.96067884</v>
+        <v>6.84156672</v>
       </c>
       <c r="P45">
-        <v>18.81961316</v>
+        <v>18.49756928</v>
       </c>
       <c r="Q45">
-        <v>39.81961316</v>
+        <v>39.49756928</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1570519260585566</v>
+        <v>0.1586926640626688</v>
       </c>
       <c r="T45">
-        <v>1.332769407289691</v>
+        <v>1.352425025801026</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.359024187404466</v>
+        <v>2.305410001327092</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1132148518750945</v>
+        <v>0.1131164858968118</v>
       </c>
       <c r="C46">
-        <v>344.6241816360418</v>
+        <v>339.489950721041</v>
       </c>
       <c r="D46">
-        <v>469.3041816360418</v>
+        <v>469.989950721041</v>
       </c>
       <c r="E46">
-        <v>97.17999999999998</v>
+        <v>103</v>
       </c>
       <c r="F46">
-        <v>256.08</v>
+        <v>261.9</v>
       </c>
       <c r="G46">
         <v>131.4</v>
@@ -5059,28 +5059,28 @@
         <v>44.75</v>
       </c>
       <c r="M46">
-        <v>19.410864</v>
+        <v>19.85202</v>
       </c>
       <c r="N46">
-        <v>25.339136</v>
+        <v>24.89798</v>
       </c>
       <c r="O46">
-        <v>6.84156672</v>
+        <v>6.7224546</v>
       </c>
       <c r="P46">
-        <v>18.49756928</v>
+        <v>18.1755254</v>
       </c>
       <c r="Q46">
-        <v>39.49756928</v>
+        <v>39.1755254</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1586926640626688</v>
+        <v>0.1603930652669305</v>
       </c>
       <c r="T46">
-        <v>1.352425025801026</v>
+        <v>1.372795394076409</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.305410001327092</v>
+        <v>2.254178667964267</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1131164858968118</v>
+        <v>0.113018119918529</v>
       </c>
       <c r="C47">
-        <v>339.489950721041</v>
+        <v>334.3577268942181</v>
       </c>
       <c r="D47">
-        <v>469.989950721041</v>
+        <v>470.6777268942181</v>
       </c>
       <c r="E47">
-        <v>103</v>
+        <v>108.82</v>
       </c>
       <c r="F47">
-        <v>261.9</v>
+        <v>267.72</v>
       </c>
       <c r="G47">
         <v>131.4</v>
@@ -5141,28 +5141,28 @@
         <v>44.75</v>
       </c>
       <c r="M47">
-        <v>19.85202</v>
+        <v>20.293176</v>
       </c>
       <c r="N47">
-        <v>24.89798</v>
+        <v>24.456824</v>
       </c>
       <c r="O47">
-        <v>6.7224546</v>
+        <v>6.603342479999999</v>
       </c>
       <c r="P47">
-        <v>18.1755254</v>
+        <v>17.85348152</v>
       </c>
       <c r="Q47">
-        <v>39.1755254</v>
+        <v>38.85348152</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1603930652669305</v>
+        <v>0.1621564442935723</v>
       </c>
       <c r="T47">
-        <v>1.372795394076409</v>
+        <v>1.393920220436067</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.254178667964267</v>
+        <v>2.205174783878087</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.113018119918529</v>
+        <v>0.1129197539402463</v>
       </c>
       <c r="C48">
-        <v>334.3577268942181</v>
+        <v>329.2275189799142</v>
       </c>
       <c r="D48">
-        <v>470.6777268942181</v>
+        <v>471.3675189799143</v>
       </c>
       <c r="E48">
-        <v>108.82</v>
+        <v>114.64</v>
       </c>
       <c r="F48">
-        <v>267.72</v>
+        <v>273.54</v>
       </c>
       <c r="G48">
         <v>131.4</v>
@@ -5223,28 +5223,28 @@
         <v>44.75</v>
       </c>
       <c r="M48">
-        <v>20.293176</v>
+        <v>20.734332</v>
       </c>
       <c r="N48">
-        <v>24.456824</v>
+        <v>24.015668</v>
       </c>
       <c r="O48">
-        <v>6.603342479999999</v>
+        <v>6.48423036</v>
       </c>
       <c r="P48">
-        <v>17.85348152</v>
+        <v>17.53143764</v>
       </c>
       <c r="Q48">
-        <v>38.85348152</v>
+        <v>38.53143764</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1621564442935723</v>
+        <v>0.163986365924993</v>
       </c>
       <c r="T48">
-        <v>1.393920220436067</v>
+        <v>1.415842210054579</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.205174783878087</v>
+        <v>2.158256171455149</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1129197539402463</v>
+        <v>0.1128213879619635</v>
       </c>
       <c r="C49">
-        <v>329.2275189799142</v>
+        <v>324.0993358542752</v>
       </c>
       <c r="D49">
-        <v>471.3675189799143</v>
+        <v>472.0593358542752</v>
       </c>
       <c r="E49">
-        <v>114.64</v>
+        <v>120.46</v>
       </c>
       <c r="F49">
-        <v>273.54</v>
+        <v>279.36</v>
       </c>
       <c r="G49">
         <v>131.4</v>
@@ -5305,28 +5305,28 @@
         <v>44.75</v>
       </c>
       <c r="M49">
-        <v>20.734332</v>
+        <v>21.175488</v>
       </c>
       <c r="N49">
-        <v>24.015668</v>
+        <v>23.574512</v>
       </c>
       <c r="O49">
-        <v>6.48423036</v>
+        <v>6.36511824</v>
       </c>
       <c r="P49">
-        <v>17.53143764</v>
+        <v>17.20939376</v>
       </c>
       <c r="Q49">
-        <v>38.53143764</v>
+        <v>38.20939376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.163986365924993</v>
+        <v>0.1658866691576222</v>
       </c>
       <c r="T49">
-        <v>1.415842210054579</v>
+        <v>1.438607353119957</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.158256171455149</v>
+        <v>2.113292501216501</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1128213879619635</v>
+        <v>0.1127230219836808</v>
       </c>
       <c r="C50">
-        <v>324.0993358542752</v>
+        <v>318.9731864456327</v>
       </c>
       <c r="D50">
-        <v>472.0593358542752</v>
+        <v>472.7531864456328</v>
       </c>
       <c r="E50">
-        <v>120.46</v>
+        <v>126.28</v>
       </c>
       <c r="F50">
-        <v>279.36</v>
+        <v>285.18</v>
       </c>
       <c r="G50">
         <v>131.4</v>
@@ -5387,28 +5387,28 @@
         <v>44.75</v>
       </c>
       <c r="M50">
-        <v>21.175488</v>
+        <v>21.616644</v>
       </c>
       <c r="N50">
-        <v>23.574512</v>
+        <v>23.133356</v>
       </c>
       <c r="O50">
-        <v>6.36511824</v>
+        <v>6.246006120000001</v>
       </c>
       <c r="P50">
-        <v>17.20939376</v>
+        <v>16.88734988</v>
       </c>
       <c r="Q50">
-        <v>38.20939376</v>
+        <v>37.88734988</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1658866691576222</v>
+        <v>0.1678614940856486</v>
       </c>
       <c r="T50">
-        <v>1.438607353119957</v>
+        <v>1.462265246893781</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.113292501216501</v>
+        <v>2.070164082824327</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1127230219836808</v>
+        <v>0.112624656005398</v>
       </c>
       <c r="C51">
-        <v>318.9731864456327</v>
+        <v>313.8490797348888</v>
       </c>
       <c r="D51">
-        <v>472.7531864456328</v>
+        <v>473.4490797348889</v>
       </c>
       <c r="E51">
-        <v>126.28</v>
+        <v>132.1</v>
       </c>
       <c r="F51">
-        <v>285.18</v>
+        <v>291</v>
       </c>
       <c r="G51">
         <v>131.4</v>
@@ -5469,28 +5469,28 @@
         <v>44.75</v>
       </c>
       <c r="M51">
-        <v>21.616644</v>
+        <v>22.0578</v>
       </c>
       <c r="N51">
-        <v>23.133356</v>
+        <v>22.6922</v>
       </c>
       <c r="O51">
-        <v>6.246006120000001</v>
+        <v>6.126894</v>
       </c>
       <c r="P51">
-        <v>16.88734988</v>
+        <v>16.565306</v>
       </c>
       <c r="Q51">
-        <v>37.88734988</v>
+        <v>37.565306</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1678614940856486</v>
+        <v>0.1699153120107961</v>
       </c>
       <c r="T51">
-        <v>1.462265246893781</v>
+        <v>1.486869456418558</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.070164082824327</v>
+        <v>2.028760801167841</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.112624656005398</v>
+        <v>0.1178129500271153</v>
       </c>
       <c r="C52">
-        <v>313.8490797348888</v>
+        <v>273.9186450276432</v>
       </c>
       <c r="D52">
-        <v>473.4490797348889</v>
+        <v>439.3386450276432</v>
       </c>
       <c r="E52">
-        <v>132.1</v>
+        <v>137.92</v>
       </c>
       <c r="F52">
-        <v>291</v>
+        <v>296.82</v>
       </c>
       <c r="G52">
         <v>131.4</v>
@@ -5551,45 +5551,45 @@
         <v>44.75</v>
       </c>
       <c r="M52">
-        <v>22.0578</v>
+        <v>26.7138</v>
       </c>
       <c r="N52">
-        <v>22.6922</v>
+        <v>18.0362</v>
       </c>
       <c r="O52">
-        <v>6.126894</v>
+        <v>4.869774</v>
       </c>
       <c r="P52">
-        <v>16.565306</v>
+        <v>13.166426</v>
       </c>
       <c r="Q52">
-        <v>37.565306</v>
+        <v>34.166426</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1699153120107961</v>
+        <v>0.1720529592390108</v>
       </c>
       <c r="T52">
-        <v>1.486869456418558</v>
+        <v>1.512477919393327</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.028760801167841</v>
+        <v>1.675164147369524</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1178129500271153</v>
+        <v>0.1178182440488326</v>
       </c>
       <c r="C53">
-        <v>273.9186450276432</v>
+        <v>268.0663494842191</v>
       </c>
       <c r="D53">
-        <v>439.3386450276432</v>
+        <v>439.3063494842191</v>
       </c>
       <c r="E53">
-        <v>137.92</v>
+        <v>143.74</v>
       </c>
       <c r="F53">
-        <v>296.82</v>
+        <v>302.64</v>
       </c>
       <c r="G53">
         <v>131.4</v>
@@ -5633,28 +5633,28 @@
         <v>44.75</v>
       </c>
       <c r="M53">
-        <v>26.7138</v>
+        <v>27.2376</v>
       </c>
       <c r="N53">
-        <v>18.0362</v>
+        <v>17.5124</v>
       </c>
       <c r="O53">
-        <v>4.869774</v>
+        <v>4.728348000000001</v>
       </c>
       <c r="P53">
-        <v>13.166426</v>
+        <v>12.784052</v>
       </c>
       <c r="Q53">
-        <v>34.166426</v>
+        <v>33.784052</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1720529592390108</v>
+        <v>0.1742796751017345</v>
       </c>
       <c r="T53">
-        <v>1.512477919393327</v>
+        <v>1.53915340165871</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.675164147369524</v>
+        <v>1.642949452227803</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1178182440488326</v>
+        <v>0.1178235380705498</v>
       </c>
       <c r="C54">
-        <v>268.0663494842191</v>
+        <v>262.2140586885015</v>
       </c>
       <c r="D54">
-        <v>439.3063494842191</v>
+        <v>439.2740586885015</v>
       </c>
       <c r="E54">
-        <v>143.74</v>
+        <v>149.56</v>
       </c>
       <c r="F54">
-        <v>302.64</v>
+        <v>308.46</v>
       </c>
       <c r="G54">
         <v>131.4</v>
@@ -5715,28 +5715,28 @@
         <v>44.75</v>
       </c>
       <c r="M54">
-        <v>27.2376</v>
+        <v>27.7614</v>
       </c>
       <c r="N54">
-        <v>17.5124</v>
+        <v>16.9886</v>
       </c>
       <c r="O54">
-        <v>4.728348000000001</v>
+        <v>4.586921999999999</v>
       </c>
       <c r="P54">
-        <v>12.784052</v>
+        <v>12.401678</v>
       </c>
       <c r="Q54">
-        <v>33.784052</v>
+        <v>33.401678</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1742796751017345</v>
+        <v>0.176601144830957</v>
       </c>
       <c r="T54">
-        <v>1.53915340165871</v>
+        <v>1.566964010829004</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.642949452227803</v>
+        <v>1.611950405959353</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1178235380705498</v>
+        <v>0.117828832092267</v>
       </c>
       <c r="C55">
-        <v>262.2140586885015</v>
+        <v>256.3617726394435</v>
       </c>
       <c r="D55">
-        <v>439.2740586885015</v>
+        <v>439.2417726394435</v>
       </c>
       <c r="E55">
-        <v>149.56</v>
+        <v>155.38</v>
       </c>
       <c r="F55">
-        <v>308.46</v>
+        <v>314.28</v>
       </c>
       <c r="G55">
         <v>131.4</v>
@@ -5797,28 +5797,28 @@
         <v>44.75</v>
       </c>
       <c r="M55">
-        <v>27.7614</v>
+        <v>28.2852</v>
       </c>
       <c r="N55">
-        <v>16.9886</v>
+        <v>16.4648</v>
       </c>
       <c r="O55">
-        <v>4.586921999999999</v>
+        <v>4.445495999999999</v>
       </c>
       <c r="P55">
-        <v>12.401678</v>
+        <v>12.019304</v>
       </c>
       <c r="Q55">
-        <v>33.401678</v>
+        <v>33.019304</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.176601144830957</v>
+        <v>0.1790235480266675</v>
       </c>
       <c r="T55">
-        <v>1.566964010829004</v>
+        <v>1.595983776919744</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.611950405959353</v>
+        <v>1.582099472515662</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.117828832092267</v>
+        <v>0.1178341261139843</v>
       </c>
       <c r="C56">
-        <v>256.3617726394435</v>
+        <v>250.5094913359984</v>
       </c>
       <c r="D56">
-        <v>439.2417726394435</v>
+        <v>439.2094913359984</v>
       </c>
       <c r="E56">
-        <v>155.38</v>
+        <v>161.2</v>
       </c>
       <c r="F56">
-        <v>314.28</v>
+        <v>320.1</v>
       </c>
       <c r="G56">
         <v>131.4</v>
@@ -5879,28 +5879,28 @@
         <v>44.75</v>
       </c>
       <c r="M56">
-        <v>28.2852</v>
+        <v>28.809</v>
       </c>
       <c r="N56">
-        <v>16.4648</v>
+        <v>15.941</v>
       </c>
       <c r="O56">
-        <v>4.445495999999999</v>
+        <v>4.30407</v>
       </c>
       <c r="P56">
-        <v>12.019304</v>
+        <v>11.63693</v>
       </c>
       <c r="Q56">
-        <v>33.019304</v>
+        <v>32.63693</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1790235480266675</v>
+        <v>0.1815536135866318</v>
       </c>
       <c r="T56">
-        <v>1.595983776919744</v>
+        <v>1.626293310392297</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.582099472515662</v>
+        <v>1.553334027560832</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1178341261139843</v>
+        <v>0.1178394201357016</v>
       </c>
       <c r="C57">
-        <v>250.5094913359984</v>
+        <v>244.6572147771204</v>
       </c>
       <c r="D57">
-        <v>439.2094913359984</v>
+        <v>439.1772147771204</v>
       </c>
       <c r="E57">
-        <v>161.2</v>
+        <v>167.02</v>
       </c>
       <c r="F57">
-        <v>320.1</v>
+        <v>325.92</v>
       </c>
       <c r="G57">
         <v>131.4</v>
@@ -5961,28 +5961,28 @@
         <v>44.75</v>
       </c>
       <c r="M57">
-        <v>28.809</v>
+        <v>29.3328</v>
       </c>
       <c r="N57">
-        <v>15.941</v>
+        <v>15.4172</v>
       </c>
       <c r="O57">
-        <v>4.30407</v>
+        <v>4.162644</v>
       </c>
       <c r="P57">
-        <v>11.63693</v>
+        <v>11.254556</v>
       </c>
       <c r="Q57">
-        <v>32.63693</v>
+        <v>32.254556</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1815536135866318</v>
+        <v>0.1841986821265945</v>
       </c>
       <c r="T57">
-        <v>1.626293310392297</v>
+        <v>1.657980549931782</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.553334027560832</v>
+        <v>1.525595919925817</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1178394201357016</v>
+        <v>0.1442068286611282</v>
       </c>
       <c r="C58">
-        <v>244.6572147771204</v>
+        <v>121.1628095083163</v>
       </c>
       <c r="D58">
-        <v>439.1772147771204</v>
+        <v>321.5028095083163</v>
       </c>
       <c r="E58">
-        <v>167.02</v>
+        <v>172.84</v>
       </c>
       <c r="F58">
-        <v>325.92</v>
+        <v>331.74</v>
       </c>
       <c r="G58">
         <v>131.4</v>
@@ -6043,45 +6043,45 @@
         <v>44.75</v>
       </c>
       <c r="M58">
-        <v>29.3328</v>
+        <v>48.69943200000001</v>
       </c>
       <c r="N58">
-        <v>15.4172</v>
+        <v>-3.949432000000009</v>
       </c>
       <c r="O58">
-        <v>4.162644</v>
+        <v>-1.066346640000002</v>
       </c>
       <c r="P58">
-        <v>11.254556</v>
+        <v>-2.883085360000006</v>
       </c>
       <c r="Q58">
-        <v>32.254556</v>
+        <v>18.11691463999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1841986821265945</v>
+        <v>0.1890491579987877</v>
       </c>
       <c r="T58">
-        <v>1.657980549931782</v>
+        <v>1.716088001032029</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.27</v>
+        <v>0.2481035097082857</v>
       </c>
       <c r="W58">
-        <v>0.06569999999999999</v>
+        <v>0.1103784047748237</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.525595919925817</v>
+        <v>0.9189018878084655</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1442068286611282</v>
+        <v>0.1452168286611282</v>
       </c>
       <c r="C59">
-        <v>121.1628095083163</v>
+        <v>112.0765834379772</v>
       </c>
       <c r="D59">
-        <v>321.5028095083163</v>
+        <v>318.2365834379773</v>
       </c>
       <c r="E59">
-        <v>172.84</v>
+        <v>178.6600000000001</v>
       </c>
       <c r="F59">
-        <v>331.74</v>
+        <v>337.5600000000001</v>
       </c>
       <c r="G59">
         <v>131.4</v>
@@ -6125,37 +6125,37 @@
         <v>44.75</v>
       </c>
       <c r="M59">
-        <v>48.69943200000001</v>
+        <v>49.55380800000001</v>
       </c>
       <c r="N59">
-        <v>-3.949432000000009</v>
+        <v>-4.803808000000011</v>
       </c>
       <c r="O59">
-        <v>-1.066346640000002</v>
+        <v>-1.297028160000003</v>
       </c>
       <c r="P59">
-        <v>-2.883085360000006</v>
+        <v>-3.506779840000008</v>
       </c>
       <c r="Q59">
-        <v>18.11691463999999</v>
+        <v>17.49322015999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1890491579987877</v>
+        <v>0.1924598522368541</v>
       </c>
       <c r="T59">
-        <v>1.716088001032029</v>
+        <v>1.756947239151839</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2481035097082857</v>
+        <v>0.2438258629891773</v>
       </c>
       <c r="W59">
-        <v>0.1103784047748237</v>
+        <v>0.1110063633131888</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9189018878084655</v>
+        <v>0.9030587518117678</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1452168286611282</v>
+        <v>0.1462268286611282</v>
       </c>
       <c r="C60">
-        <v>112.0765834379773</v>
+        <v>103.0560547191334</v>
       </c>
       <c r="D60">
-        <v>318.2365834379773</v>
+        <v>315.0360547191334</v>
       </c>
       <c r="E60">
-        <v>178.66</v>
+        <v>184.48</v>
       </c>
       <c r="F60">
-        <v>337.56</v>
+        <v>343.38</v>
       </c>
       <c r="G60">
         <v>131.4</v>
@@ -6207,37 +6207,37 @@
         <v>44.75</v>
       </c>
       <c r="M60">
-        <v>49.553808</v>
+        <v>50.40818400000001</v>
       </c>
       <c r="N60">
-        <v>-4.803808000000004</v>
+        <v>-5.658184000000006</v>
       </c>
       <c r="O60">
-        <v>-1.297028160000001</v>
+        <v>-1.527709680000002</v>
       </c>
       <c r="P60">
-        <v>-3.506779840000003</v>
+        <v>-4.130474320000004</v>
       </c>
       <c r="Q60">
-        <v>17.49322016</v>
+        <v>16.86952568</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.192459852236854</v>
+        <v>0.1960369218036066</v>
       </c>
       <c r="T60">
-        <v>1.756947239151839</v>
+        <v>1.799799610838469</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2438258629891773</v>
+        <v>0.239693221243598</v>
       </c>
       <c r="W60">
-        <v>0.1110063633131888</v>
+        <v>0.1116130351214398</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9030587518117679</v>
+        <v>0.8877526712725853</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1462268286611282</v>
+        <v>0.1472368286611282</v>
       </c>
       <c r="C61">
-        <v>103.0560547191334</v>
+        <v>94.09926091883329</v>
       </c>
       <c r="D61">
-        <v>315.0360547191334</v>
+        <v>311.8992609188333</v>
       </c>
       <c r="E61">
-        <v>184.48</v>
+        <v>190.3</v>
       </c>
       <c r="F61">
-        <v>343.38</v>
+        <v>349.2</v>
       </c>
       <c r="G61">
         <v>131.4</v>
@@ -6289,37 +6289,37 @@
         <v>44.75</v>
       </c>
       <c r="M61">
-        <v>50.40818400000001</v>
+        <v>51.26256</v>
       </c>
       <c r="N61">
-        <v>-5.658184000000006</v>
+        <v>-6.512560000000001</v>
       </c>
       <c r="O61">
-        <v>-1.527709680000002</v>
+        <v>-1.7583912</v>
       </c>
       <c r="P61">
-        <v>-4.130474320000004</v>
+        <v>-4.7541688</v>
       </c>
       <c r="Q61">
-        <v>16.86952568</v>
+        <v>16.2458312</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1960369218036066</v>
+        <v>0.1997928448486967</v>
       </c>
       <c r="T61">
-        <v>1.799799610838469</v>
+        <v>1.844794601109431</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.239693221243598</v>
+        <v>0.2356983342228715</v>
       </c>
       <c r="W61">
-        <v>0.1116130351214398</v>
+        <v>0.1121994845360825</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8877526712725853</v>
+        <v>0.8729567934180423</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1472368286611282</v>
+        <v>0.1482468286611282</v>
       </c>
       <c r="C62">
-        <v>94.09926091883329</v>
+        <v>85.20431699284768</v>
       </c>
       <c r="D62">
-        <v>311.8992609188333</v>
+        <v>308.8243169928477</v>
       </c>
       <c r="E62">
-        <v>190.3</v>
+        <v>196.12</v>
       </c>
       <c r="F62">
-        <v>349.2</v>
+        <v>355.02</v>
       </c>
       <c r="G62">
         <v>131.4</v>
@@ -6371,37 +6371,37 @@
         <v>44.75</v>
       </c>
       <c r="M62">
-        <v>51.26256</v>
+        <v>52.116936</v>
       </c>
       <c r="N62">
-        <v>-6.512560000000001</v>
+        <v>-7.366936000000003</v>
       </c>
       <c r="O62">
-        <v>-1.7583912</v>
+        <v>-1.989072720000001</v>
       </c>
       <c r="P62">
-        <v>-4.7541688</v>
+        <v>-5.377863280000001</v>
       </c>
       <c r="Q62">
-        <v>16.2458312</v>
+        <v>15.62213672</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1997928448486967</v>
+        <v>0.2037413793319967</v>
       </c>
       <c r="T62">
-        <v>1.844794601109431</v>
+        <v>1.892097026778904</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2356983342228715</v>
+        <v>0.2318344271044637</v>
       </c>
       <c r="W62">
-        <v>0.1121994845360825</v>
+        <v>0.1127667061010647</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8729567934180423</v>
+        <v>0.8586460263128285</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1482468286611282</v>
+        <v>0.1492568286611282</v>
       </c>
       <c r="C63">
-        <v>85.20431699284768</v>
+        <v>76.36941150812203</v>
       </c>
       <c r="D63">
-        <v>308.8243169928477</v>
+        <v>305.809411508122</v>
       </c>
       <c r="E63">
-        <v>196.12</v>
+        <v>201.94</v>
       </c>
       <c r="F63">
-        <v>355.02</v>
+        <v>360.84</v>
       </c>
       <c r="G63">
         <v>131.4</v>
@@ -6453,37 +6453,37 @@
         <v>44.75</v>
       </c>
       <c r="M63">
-        <v>52.116936</v>
+        <v>52.971312</v>
       </c>
       <c r="N63">
-        <v>-7.366936000000003</v>
+        <v>-8.221312000000005</v>
       </c>
       <c r="O63">
-        <v>-1.989072720000001</v>
+        <v>-2.219754240000001</v>
       </c>
       <c r="P63">
-        <v>-5.377863280000001</v>
+        <v>-6.001557760000003</v>
       </c>
       <c r="Q63">
-        <v>15.62213672</v>
+        <v>14.99844224</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2037413793319967</v>
+        <v>0.2078977314196808</v>
       </c>
       <c r="T63">
-        <v>1.892097026778904</v>
+        <v>1.941889053799401</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2318344271044637</v>
+        <v>0.2280951621511659</v>
       </c>
       <c r="W63">
-        <v>0.1127667061010647</v>
+        <v>0.1133156301962089</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8586460263128285</v>
+        <v>0.8447968968561699</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1492568286611282</v>
+        <v>0.1502668286611282</v>
       </c>
       <c r="C64">
-        <v>76.36941150812203</v>
+        <v>67.5928030843599</v>
       </c>
       <c r="D64">
-        <v>305.809411508122</v>
+        <v>302.8528030843599</v>
       </c>
       <c r="E64">
-        <v>201.94</v>
+        <v>207.76</v>
       </c>
       <c r="F64">
-        <v>360.84</v>
+        <v>366.66</v>
       </c>
       <c r="G64">
         <v>131.4</v>
@@ -6535,37 +6535,37 @@
         <v>44.75</v>
       </c>
       <c r="M64">
-        <v>52.971312</v>
+        <v>53.82568800000001</v>
       </c>
       <c r="N64">
-        <v>-8.221312000000005</v>
+        <v>-9.075688000000007</v>
       </c>
       <c r="O64">
-        <v>-2.219754240000001</v>
+        <v>-2.450435760000002</v>
       </c>
       <c r="P64">
-        <v>-6.001557760000003</v>
+        <v>-6.625252240000005</v>
       </c>
       <c r="Q64">
-        <v>14.99844224</v>
+        <v>14.37474775999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2078977314196808</v>
+        <v>0.2122787511877803</v>
       </c>
       <c r="T64">
-        <v>1.941889053799401</v>
+        <v>1.994372541739925</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2280951621511659</v>
+        <v>0.2244746040217823</v>
       </c>
       <c r="W64">
-        <v>0.1133156301962089</v>
+        <v>0.1138471281296024</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8447968968561699</v>
+        <v>0.8313874223028974</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1502668286611282</v>
+        <v>0.1512768286611282</v>
       </c>
       <c r="C65">
-        <v>67.5928030843599</v>
+        <v>58.87281704005113</v>
       </c>
       <c r="D65">
-        <v>302.8528030843599</v>
+        <v>299.9528170400512</v>
       </c>
       <c r="E65">
-        <v>207.76</v>
+        <v>213.58</v>
       </c>
       <c r="F65">
-        <v>366.66</v>
+        <v>372.48</v>
       </c>
       <c r="G65">
         <v>131.4</v>
@@ -6617,37 +6617,37 @@
         <v>44.75</v>
       </c>
       <c r="M65">
-        <v>53.82568800000001</v>
+        <v>54.68006400000001</v>
       </c>
       <c r="N65">
-        <v>-9.075688000000007</v>
+        <v>-9.930064000000009</v>
       </c>
       <c r="O65">
-        <v>-2.450435760000002</v>
+        <v>-2.681117280000003</v>
       </c>
       <c r="P65">
-        <v>-6.625252240000005</v>
+        <v>-7.248946720000006</v>
       </c>
       <c r="Q65">
-        <v>14.37474775999999</v>
+        <v>13.75105327999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2122787511877803</v>
+        <v>0.2169031609429964</v>
       </c>
       <c r="T65">
-        <v>1.994372541739925</v>
+        <v>2.049771779010479</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2244746040217823</v>
+        <v>0.2209671883339419</v>
       </c>
       <c r="W65">
-        <v>0.1138471281296024</v>
+        <v>0.1143620167525773</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8313874223028974</v>
+        <v>0.8183969938294146</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1512768286611282</v>
+        <v>0.1522868286611282</v>
       </c>
       <c r="C66">
-        <v>58.87281704005113</v>
+        <v>50.20784222936794</v>
       </c>
       <c r="D66">
-        <v>299.9528170400512</v>
+        <v>297.107842229368</v>
       </c>
       <c r="E66">
-        <v>213.58</v>
+        <v>219.4</v>
       </c>
       <c r="F66">
-        <v>372.48</v>
+        <v>378.3</v>
       </c>
       <c r="G66">
         <v>131.4</v>
@@ -6699,37 +6699,37 @@
         <v>44.75</v>
       </c>
       <c r="M66">
-        <v>54.68006400000001</v>
+        <v>55.53444</v>
       </c>
       <c r="N66">
-        <v>-9.930064000000009</v>
+        <v>-10.78444</v>
       </c>
       <c r="O66">
-        <v>-2.681117280000003</v>
+        <v>-2.911798800000001</v>
       </c>
       <c r="P66">
-        <v>-7.248946720000006</v>
+        <v>-7.872641200000002</v>
       </c>
       <c r="Q66">
-        <v>13.75105327999999</v>
+        <v>13.1273588</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2169031609429964</v>
+        <v>0.2217918226842248</v>
       </c>
       <c r="T66">
-        <v>2.049771779010479</v>
+        <v>2.108336686982207</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2209671883339419</v>
+        <v>0.2175676931288044</v>
       </c>
       <c r="W66">
-        <v>0.1143620167525773</v>
+        <v>0.1148610626486915</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8183969938294146</v>
+        <v>0.8058062708474236</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1522868286611282</v>
+        <v>0.1916652854187131</v>
       </c>
       <c r="C67">
-        <v>50.20784222936794</v>
+        <v>-35.82074396017083</v>
       </c>
       <c r="D67">
-        <v>297.107842229368</v>
+        <v>216.8992560398292</v>
       </c>
       <c r="E67">
-        <v>219.4</v>
+        <v>225.22</v>
       </c>
       <c r="F67">
-        <v>378.3</v>
+        <v>384.12</v>
       </c>
       <c r="G67">
         <v>131.4</v>
@@ -6781,45 +6781,45 @@
         <v>44.75</v>
       </c>
       <c r="M67">
-        <v>55.53444</v>
+        <v>77.13129600000001</v>
       </c>
       <c r="N67">
-        <v>-10.78444</v>
+        <v>-32.38129600000001</v>
       </c>
       <c r="O67">
-        <v>-2.911798800000001</v>
+        <v>-8.742949920000003</v>
       </c>
       <c r="P67">
-        <v>-7.872641200000002</v>
+        <v>-23.63834608000001</v>
       </c>
       <c r="Q67">
-        <v>13.1273588</v>
+        <v>-2.638346080000005</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2217918226842248</v>
+        <v>0.2349929255795989</v>
       </c>
       <c r="T67">
-        <v>2.108336686982207</v>
+        <v>2.266482498068457</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.2175676931288044</v>
+        <v>0.1566484763849942</v>
       </c>
       <c r="W67">
-        <v>0.1148610626486915</v>
+        <v>0.1693449859418932</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8058062708474236</v>
+        <v>0.5801795421666452</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1916652854187131</v>
+        <v>0.1932152854187131</v>
       </c>
       <c r="C68">
-        <v>-35.82074396017083</v>
+        <v>-43.92133410322703</v>
       </c>
       <c r="D68">
-        <v>216.8992560398292</v>
+        <v>214.6186658967729</v>
       </c>
       <c r="E68">
-        <v>225.22</v>
+        <v>231.04</v>
       </c>
       <c r="F68">
-        <v>384.12</v>
+        <v>389.94</v>
       </c>
       <c r="G68">
         <v>131.4</v>
@@ -6863,37 +6863,37 @@
         <v>44.75</v>
       </c>
       <c r="M68">
-        <v>77.13129600000001</v>
+        <v>78.299952</v>
       </c>
       <c r="N68">
-        <v>-32.38129600000001</v>
+        <v>-33.549952</v>
       </c>
       <c r="O68">
-        <v>-8.742949920000003</v>
+        <v>-9.058487040000001</v>
       </c>
       <c r="P68">
-        <v>-23.63834608000001</v>
+        <v>-24.49146496</v>
       </c>
       <c r="Q68">
-        <v>-2.638346080000005</v>
+        <v>-3.491464960000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2349929255795989</v>
+        <v>0.2407260445365565</v>
       </c>
       <c r="T68">
-        <v>2.266482498068457</v>
+        <v>2.335163785888713</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1566484763849942</v>
+        <v>0.1543104394240242</v>
       </c>
       <c r="W68">
-        <v>0.1693449859418932</v>
+        <v>0.1698144637636559</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5801795421666452</v>
+        <v>0.5715201460149043</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1932152854187131</v>
+        <v>0.1947652854187131</v>
       </c>
       <c r="C69">
-        <v>-43.92133410322703</v>
+        <v>-51.97446466921747</v>
       </c>
       <c r="D69">
-        <v>214.6186658967729</v>
+        <v>212.3855353307826</v>
       </c>
       <c r="E69">
-        <v>231.04</v>
+        <v>236.86</v>
       </c>
       <c r="F69">
-        <v>389.94</v>
+        <v>395.76</v>
       </c>
       <c r="G69">
         <v>131.4</v>
@@ -6945,37 +6945,37 @@
         <v>44.75</v>
       </c>
       <c r="M69">
-        <v>78.299952</v>
+        <v>79.46860800000002</v>
       </c>
       <c r="N69">
-        <v>-33.549952</v>
+        <v>-34.71860800000002</v>
       </c>
       <c r="O69">
-        <v>-9.058487040000001</v>
+        <v>-9.374024160000005</v>
       </c>
       <c r="P69">
-        <v>-24.49146496</v>
+        <v>-25.34458384000001</v>
       </c>
       <c r="Q69">
-        <v>-3.491464960000002</v>
+        <v>-4.344583840000013</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2407260445365565</v>
+        <v>0.2468174834283239</v>
       </c>
       <c r="T69">
-        <v>2.335163785888713</v>
+        <v>2.408137654197736</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1543104394240242</v>
+        <v>0.1520411682560238</v>
       </c>
       <c r="W69">
-        <v>0.1698144637636559</v>
+        <v>0.1702701334141904</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5715201460149043</v>
+        <v>0.5631154379852732</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1947652854187131</v>
+        <v>0.1963152854187131</v>
       </c>
       <c r="C70">
-        <v>-51.97446466921747</v>
+        <v>-59.98160186825294</v>
       </c>
       <c r="D70">
-        <v>212.3855353307826</v>
+        <v>210.1983981317471</v>
       </c>
       <c r="E70">
-        <v>236.86</v>
+        <v>242.68</v>
       </c>
       <c r="F70">
-        <v>395.76</v>
+        <v>401.58</v>
       </c>
       <c r="G70">
         <v>131.4</v>
@@ -7027,37 +7027,37 @@
         <v>44.75</v>
       </c>
       <c r="M70">
-        <v>79.46860800000002</v>
+        <v>80.63726400000002</v>
       </c>
       <c r="N70">
-        <v>-34.71860800000002</v>
+        <v>-35.88726400000002</v>
       </c>
       <c r="O70">
-        <v>-9.374024160000005</v>
+        <v>-9.689561280000005</v>
       </c>
       <c r="P70">
-        <v>-25.34458384000001</v>
+        <v>-26.19770272000001</v>
       </c>
       <c r="Q70">
-        <v>-4.344583840000013</v>
+        <v>-5.197702720000009</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2468174834283239</v>
+        <v>0.2533019183776246</v>
       </c>
       <c r="T70">
-        <v>2.408137654197736</v>
+        <v>2.485819514010566</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1520411682560238</v>
+        <v>0.1498376730639075</v>
       </c>
       <c r="W70">
-        <v>0.1702701334141904</v>
+        <v>0.1707125952487674</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5631154379852732</v>
+        <v>0.5549543446811389</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1963152854187131</v>
+        <v>0.1978652854187131</v>
       </c>
       <c r="C71">
-        <v>-59.98160186825294</v>
+        <v>-67.94415213018215</v>
       </c>
       <c r="D71">
-        <v>210.1983981317471</v>
+        <v>208.0558478698179</v>
       </c>
       <c r="E71">
-        <v>242.68</v>
+        <v>248.5</v>
       </c>
       <c r="F71">
-        <v>401.58</v>
+        <v>407.4</v>
       </c>
       <c r="G71">
         <v>131.4</v>
@@ -7109,37 +7109,37 @@
         <v>44.75</v>
       </c>
       <c r="M71">
-        <v>80.63726400000002</v>
+        <v>81.80592000000001</v>
       </c>
       <c r="N71">
-        <v>-35.88726400000002</v>
+        <v>-37.05592000000001</v>
       </c>
       <c r="O71">
-        <v>-9.689561280000005</v>
+        <v>-10.0050984</v>
       </c>
       <c r="P71">
-        <v>-26.19770272000001</v>
+        <v>-27.05082160000001</v>
       </c>
       <c r="Q71">
-        <v>-5.197702720000009</v>
+        <v>-6.05082160000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2533019183776246</v>
+        <v>0.2602186489902121</v>
       </c>
       <c r="T71">
-        <v>2.485819514010566</v>
+        <v>2.568680164477585</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1498376730639075</v>
+        <v>0.1476971348772803</v>
       </c>
       <c r="W71">
-        <v>0.1707125952487674</v>
+        <v>0.1711424153166421</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5549543446811389</v>
+        <v>0.5470264254714083</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1978652854187131</v>
+        <v>0.1994152854187131</v>
       </c>
       <c r="C72">
-        <v>-67.94415213018215</v>
+        <v>-75.86346512054774</v>
       </c>
       <c r="D72">
-        <v>208.0558478698179</v>
+        <v>205.9565348794523</v>
       </c>
       <c r="E72">
-        <v>248.5</v>
+        <v>254.32</v>
       </c>
       <c r="F72">
-        <v>407.4</v>
+        <v>413.22</v>
       </c>
       <c r="G72">
         <v>131.4</v>
@@ -7191,37 +7191,37 @@
         <v>44.75</v>
       </c>
       <c r="M72">
-        <v>81.80592000000001</v>
+        <v>82.97457600000001</v>
       </c>
       <c r="N72">
-        <v>-37.05592000000001</v>
+        <v>-38.22457600000001</v>
       </c>
       <c r="O72">
-        <v>-10.0050984</v>
+        <v>-10.32063552000001</v>
       </c>
       <c r="P72">
-        <v>-27.05082160000001</v>
+        <v>-27.90394048000001</v>
       </c>
       <c r="Q72">
-        <v>-6.05082160000001</v>
+        <v>-6.90394048000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2602186489902121</v>
+        <v>0.267612395507116</v>
       </c>
       <c r="T72">
-        <v>2.568680164477585</v>
+        <v>2.657255342563019</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1476971348772803</v>
+        <v>0.1456168935409805</v>
       </c>
       <c r="W72">
-        <v>0.1711424153166421</v>
+        <v>0.1715601277769711</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5470264254714083</v>
+        <v>0.5393218279295575</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1994152854187131</v>
+        <v>0.2009652854187131</v>
       </c>
       <c r="C73">
-        <v>-75.86346512054769</v>
+        <v>-83.74083657577813</v>
       </c>
       <c r="D73">
-        <v>205.9565348794523</v>
+        <v>203.8991634242218</v>
       </c>
       <c r="E73">
-        <v>254.32</v>
+        <v>260.14</v>
       </c>
       <c r="F73">
-        <v>413.22</v>
+        <v>419.04</v>
       </c>
       <c r="G73">
         <v>131.4</v>
@@ -7273,37 +7273,37 @@
         <v>44.75</v>
       </c>
       <c r="M73">
-        <v>82.974576</v>
+        <v>84.143232</v>
       </c>
       <c r="N73">
-        <v>-38.224576</v>
+        <v>-39.393232</v>
       </c>
       <c r="O73">
-        <v>-10.32063552</v>
+        <v>-10.63617264</v>
       </c>
       <c r="P73">
-        <v>-27.90394048</v>
+        <v>-28.75705936</v>
       </c>
       <c r="Q73">
-        <v>-6.903940479999999</v>
+        <v>-7.75705936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.267612395507116</v>
+        <v>0.2755342667752272</v>
       </c>
       <c r="T73">
-        <v>2.657255342563019</v>
+        <v>2.752157319083126</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1456168935409806</v>
+        <v>0.1435944366862447</v>
       </c>
       <c r="W73">
-        <v>0.1715601277769711</v>
+        <v>0.1719662371134021</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5393218279295576</v>
+        <v>0.5318312469860915</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2009652854187131</v>
+        <v>0.2025152854187131</v>
       </c>
       <c r="C74">
-        <v>-83.74083657577813</v>
+        <v>-91.57751097013056</v>
       </c>
       <c r="D74">
-        <v>203.8991634242218</v>
+        <v>201.8824890298694</v>
       </c>
       <c r="E74">
-        <v>260.14</v>
+        <v>265.96</v>
       </c>
       <c r="F74">
-        <v>419.04</v>
+        <v>424.86</v>
       </c>
       <c r="G74">
         <v>131.4</v>
@@ -7355,37 +7355,37 @@
         <v>44.75</v>
       </c>
       <c r="M74">
-        <v>84.143232</v>
+        <v>85.31188800000001</v>
       </c>
       <c r="N74">
-        <v>-39.393232</v>
+        <v>-40.56188800000001</v>
       </c>
       <c r="O74">
-        <v>-10.63617264</v>
+        <v>-10.95170976</v>
       </c>
       <c r="P74">
-        <v>-28.75705936</v>
+        <v>-29.61017824000001</v>
       </c>
       <c r="Q74">
-        <v>-7.75705936</v>
+        <v>-8.610178240000007</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2755342667752272</v>
+        <v>0.2840429433224579</v>
       </c>
       <c r="T74">
-        <v>2.752157319083126</v>
+        <v>2.854089071641761</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1435944366862447</v>
+        <v>0.1416273896083509</v>
       </c>
       <c r="W74">
-        <v>0.1719662371134021</v>
+        <v>0.1723612201666432</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5318312469860915</v>
+        <v>0.5245458874383369</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2025152854187131</v>
+        <v>0.2040652854187131</v>
       </c>
       <c r="C75">
-        <v>-91.57751097013056</v>
+        <v>-99.37468402591736</v>
       </c>
       <c r="D75">
-        <v>201.8824890298694</v>
+        <v>199.9053159740826</v>
       </c>
       <c r="E75">
-        <v>265.96</v>
+        <v>271.78</v>
       </c>
       <c r="F75">
-        <v>424.86</v>
+        <v>430.68</v>
       </c>
       <c r="G75">
         <v>131.4</v>
@@ -7437,37 +7437,37 @@
         <v>44.75</v>
       </c>
       <c r="M75">
-        <v>85.31188800000001</v>
+        <v>86.48054400000001</v>
       </c>
       <c r="N75">
-        <v>-40.56188800000001</v>
+        <v>-41.73054400000001</v>
       </c>
       <c r="O75">
-        <v>-10.95170976</v>
+        <v>-11.26724688</v>
       </c>
       <c r="P75">
-        <v>-29.61017824000001</v>
+        <v>-30.46329712000001</v>
       </c>
       <c r="Q75">
-        <v>-8.610178240000007</v>
+        <v>-9.463297120000007</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2840429433224579</v>
+        <v>0.2932061334502447</v>
       </c>
       <c r="T75">
-        <v>2.854089071641761</v>
+        <v>2.963861728243367</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1416273896083509</v>
+        <v>0.1397135059649948</v>
       </c>
       <c r="W75">
-        <v>0.1723612201666432</v>
+        <v>0.172745528002229</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5245458874383369</v>
+        <v>0.517457429499981</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2040652854187131</v>
+        <v>0.2056152854187131</v>
       </c>
       <c r="C76">
-        <v>-99.37468402591736</v>
+        <v>-107.1335050776586</v>
       </c>
       <c r="D76">
-        <v>199.9053159740826</v>
+        <v>197.9664949223414</v>
       </c>
       <c r="E76">
-        <v>271.78</v>
+        <v>277.6</v>
       </c>
       <c r="F76">
-        <v>430.68</v>
+        <v>436.5</v>
       </c>
       <c r="G76">
         <v>131.4</v>
@@ -7519,37 +7519,37 @@
         <v>44.75</v>
       </c>
       <c r="M76">
-        <v>86.48054400000001</v>
+        <v>87.64920000000001</v>
       </c>
       <c r="N76">
-        <v>-41.73054400000001</v>
+        <v>-42.89920000000001</v>
       </c>
       <c r="O76">
-        <v>-11.26724688</v>
+        <v>-11.582784</v>
       </c>
       <c r="P76">
-        <v>-30.46329712000001</v>
+        <v>-31.316416</v>
       </c>
       <c r="Q76">
-        <v>-9.463297120000007</v>
+        <v>-10.316416</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2932061334502447</v>
+        <v>0.3031023787882545</v>
       </c>
       <c r="T76">
-        <v>2.963861728243367</v>
+        <v>3.082416197373102</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1397135059649948</v>
+        <v>0.1378506592187949</v>
       </c>
       <c r="W76">
-        <v>0.172745528002229</v>
+        <v>0.173119587628866</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.517457429499981</v>
+        <v>0.5105579971066478</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2056152854187131</v>
+        <v>0.2071652854187132</v>
       </c>
       <c r="C77">
-        <v>-107.1335050776586</v>
+        <v>-114.8550792999792</v>
       </c>
       <c r="D77">
-        <v>197.9664949223414</v>
+        <v>196.0649207000208</v>
       </c>
       <c r="E77">
-        <v>277.6</v>
+        <v>283.42</v>
       </c>
       <c r="F77">
-        <v>436.5</v>
+        <v>442.32</v>
       </c>
       <c r="G77">
         <v>131.4</v>
@@ -7601,37 +7601,37 @@
         <v>44.75</v>
       </c>
       <c r="M77">
-        <v>87.64920000000001</v>
+        <v>88.81785600000001</v>
       </c>
       <c r="N77">
-        <v>-42.89920000000001</v>
+        <v>-44.06785600000001</v>
       </c>
       <c r="O77">
-        <v>-11.582784</v>
+        <v>-11.89832112</v>
       </c>
       <c r="P77">
-        <v>-31.316416</v>
+        <v>-32.16953488</v>
       </c>
       <c r="Q77">
-        <v>-10.316416</v>
+        <v>-11.16953488</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3031023787882545</v>
+        <v>0.3138233112377651</v>
       </c>
       <c r="T77">
-        <v>3.082416197373102</v>
+        <v>3.210850205596981</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1378506592187949</v>
+        <v>0.1360368347553897</v>
       </c>
       <c r="W77">
-        <v>0.173119587628866</v>
+        <v>0.1734838035811178</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5105579971066478</v>
+        <v>0.5038401287236656</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2071652854187132</v>
+        <v>0.2367662506765015</v>
       </c>
       <c r="C78">
-        <v>-114.8550792999792</v>
+        <v>-151.066370354564</v>
       </c>
       <c r="D78">
-        <v>196.0649207000208</v>
+        <v>165.673629645436</v>
       </c>
       <c r="E78">
-        <v>283.42</v>
+        <v>289.24</v>
       </c>
       <c r="F78">
-        <v>442.32</v>
+        <v>448.14</v>
       </c>
       <c r="G78">
         <v>131.4</v>
@@ -7683,45 +7683,45 @@
         <v>44.75</v>
       </c>
       <c r="M78">
-        <v>88.81785600000001</v>
+        <v>105.671412</v>
       </c>
       <c r="N78">
-        <v>-44.06785600000001</v>
+        <v>-60.921412</v>
       </c>
       <c r="O78">
-        <v>-11.89832112</v>
+        <v>-16.44878124</v>
       </c>
       <c r="P78">
-        <v>-32.16953488</v>
+        <v>-44.47263076</v>
       </c>
       <c r="Q78">
-        <v>-11.16953488</v>
+        <v>-23.47263076</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3138233112377651</v>
+        <v>0.3302633041515307</v>
       </c>
       <c r="T78">
-        <v>3.210850205596981</v>
+        <v>3.407797084521067</v>
       </c>
       <c r="U78">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1360368347553897</v>
+        <v>0.114340291014565</v>
       </c>
       <c r="W78">
-        <v>0.1734838035811178</v>
+        <v>0.2088385593787656</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5038401287236656</v>
+        <v>0.4234825593132038</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2367662506765015</v>
+        <v>0.2386662506765015</v>
       </c>
       <c r="C79">
-        <v>-151.066370354564</v>
+        <v>-158.5184853317681</v>
       </c>
       <c r="D79">
-        <v>165.673629645436</v>
+        <v>164.0415146682319</v>
       </c>
       <c r="E79">
-        <v>289.24</v>
+        <v>295.0600000000001</v>
       </c>
       <c r="F79">
-        <v>448.14</v>
+        <v>453.96</v>
       </c>
       <c r="G79">
         <v>131.4</v>
@@ -7765,37 +7765,37 @@
         <v>44.75</v>
       </c>
       <c r="M79">
-        <v>105.671412</v>
+        <v>107.043768</v>
       </c>
       <c r="N79">
-        <v>-60.921412</v>
+        <v>-62.29376800000001</v>
       </c>
       <c r="O79">
-        <v>-16.44878124</v>
+        <v>-16.81931736000001</v>
       </c>
       <c r="P79">
-        <v>-44.47263076</v>
+        <v>-45.47445064000001</v>
       </c>
       <c r="Q79">
-        <v>-23.47263076</v>
+        <v>-24.47445064000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3302633041515307</v>
+        <v>0.3431934543402366</v>
       </c>
       <c r="T79">
-        <v>3.407797084521067</v>
+        <v>3.562696951999297</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.114340291014565</v>
+        <v>0.1128743898477116</v>
       </c>
       <c r="W79">
-        <v>0.2088385593787656</v>
+        <v>0.2091842188739096</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4234825593132038</v>
+        <v>0.4180532957322652</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2386662506765015</v>
+        <v>0.2405662506765016</v>
       </c>
       <c r="C80">
-        <v>-158.5184853317681</v>
+        <v>-165.9387568202168</v>
       </c>
       <c r="D80">
-        <v>164.0415146682319</v>
+        <v>162.4412431797832</v>
       </c>
       <c r="E80">
-        <v>295.0600000000001</v>
+        <v>300.88</v>
       </c>
       <c r="F80">
-        <v>453.96</v>
+        <v>459.78</v>
       </c>
       <c r="G80">
         <v>131.4</v>
@@ -7847,37 +7847,37 @@
         <v>44.75</v>
       </c>
       <c r="M80">
-        <v>107.043768</v>
+        <v>108.416124</v>
       </c>
       <c r="N80">
-        <v>-62.29376800000001</v>
+        <v>-63.66612400000001</v>
       </c>
       <c r="O80">
-        <v>-16.81931736000001</v>
+        <v>-17.18985348</v>
       </c>
       <c r="P80">
-        <v>-45.47445064000001</v>
+        <v>-46.47627052000001</v>
       </c>
       <c r="Q80">
-        <v>-24.47445064000001</v>
+        <v>-25.47627052000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3431934543402366</v>
+        <v>0.3573550474040574</v>
       </c>
       <c r="T80">
-        <v>3.562696951999297</v>
+        <v>3.732349187808789</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1128743898477116</v>
+        <v>0.1114456001028039</v>
       </c>
       <c r="W80">
-        <v>0.2091842188739096</v>
+        <v>0.2095211274957589</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4180532957322652</v>
+        <v>0.4127614818622366</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2405662506765016</v>
+        <v>0.2424662506765015</v>
       </c>
       <c r="C81">
-        <v>-165.9387568202168</v>
+        <v>-173.3281077433159</v>
       </c>
       <c r="D81">
-        <v>162.4412431797832</v>
+        <v>160.8718922566842</v>
       </c>
       <c r="E81">
-        <v>300.88</v>
+        <v>306.7</v>
       </c>
       <c r="F81">
-        <v>459.78</v>
+        <v>465.6</v>
       </c>
       <c r="G81">
         <v>131.4</v>
@@ -7929,37 +7929,37 @@
         <v>44.75</v>
       </c>
       <c r="M81">
-        <v>108.416124</v>
+        <v>109.78848</v>
       </c>
       <c r="N81">
-        <v>-63.66612400000001</v>
+        <v>-65.03848000000001</v>
       </c>
       <c r="O81">
-        <v>-17.18985348</v>
+        <v>-17.5603896</v>
       </c>
       <c r="P81">
-        <v>-46.47627052000001</v>
+        <v>-47.4780904</v>
       </c>
       <c r="Q81">
-        <v>-25.47627052000001</v>
+        <v>-26.4780904</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3573550474040574</v>
+        <v>0.3729327997742602</v>
       </c>
       <c r="T81">
-        <v>3.732349187808789</v>
+        <v>3.918966647199228</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1114456001028039</v>
+        <v>0.1100525301015188</v>
       </c>
       <c r="W81">
-        <v>0.2095211274957589</v>
+        <v>0.2098496134020619</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4127614818622366</v>
+        <v>0.4076019633389587</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2424662506765015</v>
+        <v>0.2443662506765015</v>
       </c>
       <c r="C82">
-        <v>-173.3281077433159</v>
+        <v>-180.6874257001505</v>
       </c>
       <c r="D82">
-        <v>160.8718922566842</v>
+        <v>159.3325742998495</v>
       </c>
       <c r="E82">
-        <v>306.7</v>
+        <v>312.52</v>
       </c>
       <c r="F82">
-        <v>465.6</v>
+        <v>471.42</v>
       </c>
       <c r="G82">
         <v>131.4</v>
@@ -8011,37 +8011,37 @@
         <v>44.75</v>
       </c>
       <c r="M82">
-        <v>109.78848</v>
+        <v>111.160836</v>
       </c>
       <c r="N82">
-        <v>-65.03848000000001</v>
+        <v>-66.410836</v>
       </c>
       <c r="O82">
-        <v>-17.5603896</v>
+        <v>-17.93092572</v>
       </c>
       <c r="P82">
-        <v>-47.4780904</v>
+        <v>-48.47991028</v>
       </c>
       <c r="Q82">
-        <v>-26.4780904</v>
+        <v>-27.47991028</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3729327997742602</v>
+        <v>0.3901503155518529</v>
       </c>
       <c r="T82">
-        <v>3.918966647199228</v>
+        <v>4.125228049683398</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1100525301015188</v>
+        <v>0.108693856890389</v>
       </c>
       <c r="W82">
-        <v>0.2098496134020619</v>
+        <v>0.2101699885452463</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4076019633389587</v>
+        <v>0.4025698403347741</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2443662506765015</v>
+        <v>0.2462662506765015</v>
       </c>
       <c r="C83">
-        <v>-180.6874257001505</v>
+        <v>-188.0175646394887</v>
       </c>
       <c r="D83">
-        <v>159.3325742998495</v>
+        <v>157.8224353605113</v>
       </c>
       <c r="E83">
-        <v>312.52</v>
+        <v>318.34</v>
       </c>
       <c r="F83">
-        <v>471.42</v>
+        <v>477.24</v>
       </c>
       <c r="G83">
         <v>131.4</v>
@@ -8093,37 +8093,37 @@
         <v>44.75</v>
       </c>
       <c r="M83">
-        <v>111.160836</v>
+        <v>112.533192</v>
       </c>
       <c r="N83">
-        <v>-66.410836</v>
+        <v>-67.783192</v>
       </c>
       <c r="O83">
-        <v>-17.93092572</v>
+        <v>-18.30146184</v>
       </c>
       <c r="P83">
-        <v>-48.47991028</v>
+        <v>-49.48173016</v>
       </c>
       <c r="Q83">
-        <v>-27.47991028</v>
+        <v>-28.48173016</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3901503155518529</v>
+        <v>0.4092808886380671</v>
       </c>
       <c r="T83">
-        <v>4.125228049683398</v>
+        <v>4.354407385776921</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.108693856890389</v>
+        <v>0.1073683220502623</v>
       </c>
       <c r="W83">
-        <v>0.2101699885452463</v>
+        <v>0.2104825496605482</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4025698403347741</v>
+        <v>0.3976604520380085</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2462662506765015</v>
+        <v>0.2481662506765016</v>
       </c>
       <c r="C84">
-        <v>-188.0175646394887</v>
+        <v>-195.3193464394803</v>
       </c>
       <c r="D84">
-        <v>157.8224353605113</v>
+        <v>156.3406535605197</v>
       </c>
       <c r="E84">
-        <v>318.34</v>
+        <v>324.1600000000001</v>
       </c>
       <c r="F84">
-        <v>477.24</v>
+        <v>483.0600000000001</v>
       </c>
       <c r="G84">
         <v>131.4</v>
@@ -8175,37 +8175,37 @@
         <v>44.75</v>
       </c>
       <c r="M84">
-        <v>112.533192</v>
+        <v>113.905548</v>
       </c>
       <c r="N84">
-        <v>-67.783192</v>
+        <v>-69.15554800000002</v>
       </c>
       <c r="O84">
-        <v>-18.30146184</v>
+        <v>-18.67199796000001</v>
       </c>
       <c r="P84">
-        <v>-49.48173016</v>
+        <v>-50.48355004000001</v>
       </c>
       <c r="Q84">
-        <v>-28.48173016</v>
+        <v>-29.48355004000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4092808886380671</v>
+        <v>0.4306621173814828</v>
       </c>
       <c r="T84">
-        <v>4.354407385776921</v>
+        <v>4.610548996704975</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1073683220502623</v>
+        <v>0.1060747278086928</v>
       </c>
       <c r="W84">
-        <v>0.2104825496605482</v>
+        <v>0.2107875791827102</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3976604520380085</v>
+        <v>0.3928693622544179</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2481662506765016</v>
+        <v>0.2500662506765016</v>
       </c>
       <c r="C85">
-        <v>-195.3193464394803</v>
+        <v>-202.5935623991957</v>
       </c>
       <c r="D85">
-        <v>156.3406535605197</v>
+        <v>154.8864376008043</v>
       </c>
       <c r="E85">
-        <v>324.1600000000001</v>
+        <v>329.98</v>
       </c>
       <c r="F85">
-        <v>483.0600000000001</v>
+        <v>488.8800000000001</v>
       </c>
       <c r="G85">
         <v>131.4</v>
@@ -8257,37 +8257,37 @@
         <v>44.75</v>
       </c>
       <c r="M85">
-        <v>113.905548</v>
+        <v>115.277904</v>
       </c>
       <c r="N85">
-        <v>-69.15554800000002</v>
+        <v>-70.52790400000002</v>
       </c>
       <c r="O85">
-        <v>-18.67199796000001</v>
+        <v>-19.04253408000001</v>
       </c>
       <c r="P85">
-        <v>-50.48355004000001</v>
+        <v>-51.48536992000001</v>
       </c>
       <c r="Q85">
-        <v>-29.48355004000001</v>
+        <v>-30.48536992000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4306621173814828</v>
+        <v>0.4547159997178256</v>
       </c>
       <c r="T85">
-        <v>4.610548996704975</v>
+        <v>4.898708308999037</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1060747278086928</v>
+        <v>0.1048119334300179</v>
       </c>
       <c r="W85">
-        <v>0.2107875791827102</v>
+        <v>0.2110853460972018</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3928693622544179</v>
+        <v>0.3881923460371034</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2500662506765016</v>
+        <v>0.2519662506765015</v>
       </c>
       <c r="C86">
-        <v>-202.5935623991957</v>
+        <v>-209.8409746476887</v>
       </c>
       <c r="D86">
-        <v>154.8864376008043</v>
+        <v>153.4590253523113</v>
       </c>
       <c r="E86">
-        <v>329.98</v>
+        <v>335.8</v>
       </c>
       <c r="F86">
-        <v>488.88</v>
+        <v>494.7</v>
       </c>
       <c r="G86">
         <v>131.4</v>
@@ -8339,37 +8339,37 @@
         <v>44.75</v>
       </c>
       <c r="M86">
-        <v>115.277904</v>
+        <v>116.65026</v>
       </c>
       <c r="N86">
-        <v>-70.52790400000001</v>
+        <v>-71.90026</v>
       </c>
       <c r="O86">
-        <v>-19.04253408</v>
+        <v>-19.4130702</v>
       </c>
       <c r="P86">
-        <v>-51.48536992</v>
+        <v>-52.4871898</v>
       </c>
       <c r="Q86">
-        <v>-30.48536992</v>
+        <v>-31.4871898</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4547159997178252</v>
+        <v>0.4819770663656803</v>
       </c>
       <c r="T86">
-        <v>4.898708308999034</v>
+        <v>5.225288862932302</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1048119334300179</v>
+        <v>0.103578851860253</v>
       </c>
       <c r="W86">
-        <v>0.2110853460972018</v>
+        <v>0.2113761067313523</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3881923460371035</v>
+        <v>0.3836253772601964</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2519662506765015</v>
+        <v>0.2538662506765015</v>
       </c>
       <c r="C87">
-        <v>-209.8409746476887</v>
+        <v>-217.0623174758571</v>
       </c>
       <c r="D87">
-        <v>153.4590253523113</v>
+        <v>152.0576825241429</v>
       </c>
       <c r="E87">
-        <v>335.8</v>
+        <v>341.62</v>
       </c>
       <c r="F87">
-        <v>494.7</v>
+        <v>500.52</v>
       </c>
       <c r="G87">
         <v>131.4</v>
@@ -8421,37 +8421,37 @@
         <v>44.75</v>
       </c>
       <c r="M87">
-        <v>116.65026</v>
+        <v>118.022616</v>
       </c>
       <c r="N87">
-        <v>-71.90026</v>
+        <v>-73.272616</v>
       </c>
       <c r="O87">
-        <v>-19.4130702</v>
+        <v>-19.78360632</v>
       </c>
       <c r="P87">
-        <v>-52.4871898</v>
+        <v>-53.48900968</v>
       </c>
       <c r="Q87">
-        <v>-31.4871898</v>
+        <v>-32.48900968</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4819770663656803</v>
+        <v>0.513132571106086</v>
       </c>
       <c r="T87">
-        <v>5.225288862932302</v>
+        <v>5.598523781713181</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.103578851860253</v>
+        <v>0.102374446606064</v>
       </c>
       <c r="W87">
-        <v>0.2113761067313523</v>
+        <v>0.2116601054902901</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3836253772601964</v>
+        <v>0.3791646170594964</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2538662506765015</v>
+        <v>0.2557662506765015</v>
       </c>
       <c r="C88">
-        <v>-217.0623174758571</v>
+        <v>-224.2582985959895</v>
       </c>
       <c r="D88">
-        <v>152.0576825241429</v>
+        <v>150.6817014040105</v>
       </c>
       <c r="E88">
-        <v>341.62</v>
+        <v>347.4399999999999</v>
       </c>
       <c r="F88">
-        <v>500.52</v>
+        <v>506.34</v>
       </c>
       <c r="G88">
         <v>131.4</v>
@@ -8503,37 +8503,37 @@
         <v>44.75</v>
       </c>
       <c r="M88">
-        <v>118.022616</v>
+        <v>119.394972</v>
       </c>
       <c r="N88">
-        <v>-73.272616</v>
+        <v>-74.644972</v>
       </c>
       <c r="O88">
-        <v>-19.78360632</v>
+        <v>-20.15414244</v>
       </c>
       <c r="P88">
-        <v>-53.48900968</v>
+        <v>-54.49082955999999</v>
       </c>
       <c r="Q88">
-        <v>-32.48900968</v>
+        <v>-33.49082955999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.513132571106086</v>
+        <v>0.5490812304219387</v>
       </c>
       <c r="T88">
-        <v>5.598523781713181</v>
+        <v>6.02917945722958</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.102374446606064</v>
+        <v>0.1011977288289829</v>
       </c>
       <c r="W88">
-        <v>0.2116601054902901</v>
+        <v>0.2119375755421258</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3791646170594964</v>
+        <v>0.3748064030703069</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2557662506765015</v>
+        <v>0.2576662506765016</v>
       </c>
       <c r="C89">
-        <v>-224.2582985959895</v>
+        <v>-231.4296003335407</v>
       </c>
       <c r="D89">
-        <v>150.6817014040105</v>
+        <v>149.3303996664592</v>
       </c>
       <c r="E89">
-        <v>347.4399999999999</v>
+        <v>353.26</v>
       </c>
       <c r="F89">
-        <v>506.34</v>
+        <v>512.16</v>
       </c>
       <c r="G89">
         <v>131.4</v>
@@ -8585,37 +8585,37 @@
         <v>44.75</v>
       </c>
       <c r="M89">
-        <v>119.394972</v>
+        <v>120.767328</v>
       </c>
       <c r="N89">
-        <v>-74.644972</v>
+        <v>-76.01732799999999</v>
       </c>
       <c r="O89">
-        <v>-20.15414244</v>
+        <v>-20.52467856</v>
       </c>
       <c r="P89">
-        <v>-54.49082955999999</v>
+        <v>-55.49264943999999</v>
       </c>
       <c r="Q89">
-        <v>-33.49082955999999</v>
+        <v>-34.49264943999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5490812304219387</v>
+        <v>0.5910213329571004</v>
       </c>
       <c r="T89">
-        <v>6.02917945722958</v>
+        <v>6.531611078665379</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1011977288289829</v>
+        <v>0.1000477546377444</v>
       </c>
       <c r="W89">
-        <v>0.2119375755421258</v>
+        <v>0.2122087394564199</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3748064030703069</v>
+        <v>0.3705472393990534</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2576662506765016</v>
+        <v>0.2595662506765015</v>
       </c>
       <c r="C90">
-        <v>-231.4296003335407</v>
+        <v>-238.576880755349</v>
       </c>
       <c r="D90">
-        <v>149.3303996664592</v>
+        <v>148.003119244651</v>
       </c>
       <c r="E90">
-        <v>353.26</v>
+        <v>359.08</v>
       </c>
       <c r="F90">
-        <v>512.16</v>
+        <v>517.98</v>
       </c>
       <c r="G90">
         <v>131.4</v>
@@ -8667,37 +8667,37 @@
         <v>44.75</v>
       </c>
       <c r="M90">
-        <v>120.767328</v>
+        <v>122.139684</v>
       </c>
       <c r="N90">
-        <v>-76.01732799999999</v>
+        <v>-77.389684</v>
       </c>
       <c r="O90">
-        <v>-20.52467856</v>
+        <v>-20.89521468</v>
       </c>
       <c r="P90">
-        <v>-55.49264943999999</v>
+        <v>-56.49446932</v>
       </c>
       <c r="Q90">
-        <v>-34.49264943999999</v>
+        <v>-35.49446932</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5910213329571004</v>
+        <v>0.6405869086804731</v>
       </c>
       <c r="T90">
-        <v>6.531611078665379</v>
+        <v>7.125393903998595</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1000477546377444</v>
+        <v>0.09892362256316301</v>
       </c>
       <c r="W90">
-        <v>0.2122087394564199</v>
+        <v>0.2124738097996062</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3705472393990534</v>
+        <v>0.3663837872709741</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2595662506765015</v>
+        <v>0.2614662506765015</v>
       </c>
       <c r="C91">
-        <v>-238.576880755349</v>
+        <v>-245.7007747382172</v>
       </c>
       <c r="D91">
-        <v>148.003119244651</v>
+        <v>146.6992252617828</v>
       </c>
       <c r="E91">
-        <v>359.08</v>
+        <v>364.9000000000001</v>
       </c>
       <c r="F91">
-        <v>517.98</v>
+        <v>523.8000000000001</v>
       </c>
       <c r="G91">
         <v>131.4</v>
@@ -8749,37 +8749,37 @@
         <v>44.75</v>
       </c>
       <c r="M91">
-        <v>122.139684</v>
+        <v>123.51204</v>
       </c>
       <c r="N91">
-        <v>-77.389684</v>
+        <v>-78.76204000000003</v>
       </c>
       <c r="O91">
-        <v>-20.89521468</v>
+        <v>-21.26575080000001</v>
       </c>
       <c r="P91">
-        <v>-56.49446932</v>
+        <v>-57.49628920000002</v>
       </c>
       <c r="Q91">
-        <v>-35.49446932</v>
+        <v>-36.49628920000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6405869086804731</v>
+        <v>0.7000655995485204</v>
       </c>
       <c r="T91">
-        <v>7.125393903998595</v>
+        <v>7.837933294398455</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09892362256316301</v>
+        <v>0.09782447120135007</v>
       </c>
       <c r="W91">
-        <v>0.2124738097996062</v>
+        <v>0.2127329896907217</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3663837872709741</v>
+        <v>0.3623128563012965</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2614662506765015</v>
+        <v>0.2633662506765015</v>
       </c>
       <c r="C92">
-        <v>-245.7007747382172</v>
+        <v>-252.8018949815026</v>
       </c>
       <c r="D92">
-        <v>146.6992252617828</v>
+        <v>145.4181050184973</v>
       </c>
       <c r="E92">
-        <v>364.9000000000001</v>
+        <v>370.72</v>
       </c>
       <c r="F92">
-        <v>523.8000000000001</v>
+        <v>529.62</v>
       </c>
       <c r="G92">
         <v>131.4</v>
@@ -8831,37 +8831,37 @@
         <v>44.75</v>
       </c>
       <c r="M92">
-        <v>123.51204</v>
+        <v>124.884396</v>
       </c>
       <c r="N92">
-        <v>-78.76204000000003</v>
+        <v>-80.13439600000001</v>
       </c>
       <c r="O92">
-        <v>-21.26575080000001</v>
+        <v>-21.63628692</v>
       </c>
       <c r="P92">
-        <v>-57.49628920000002</v>
+        <v>-58.49810908000001</v>
       </c>
       <c r="Q92">
-        <v>-36.49628920000002</v>
+        <v>-37.49810908000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7000655995485204</v>
+        <v>0.772761777276134</v>
       </c>
       <c r="T92">
-        <v>7.837933294398455</v>
+        <v>8.708814771553842</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09782447120135007</v>
+        <v>0.09674947701232425</v>
       </c>
       <c r="W92">
-        <v>0.2127329896907217</v>
+        <v>0.2129864733204939</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3623128563012965</v>
+        <v>0.3583313963419417</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2633662506765015</v>
+        <v>0.2652662506765016</v>
       </c>
       <c r="C93">
-        <v>-252.8018949815026</v>
+        <v>-259.8808329671086</v>
       </c>
       <c r="D93">
-        <v>145.4181050184973</v>
+        <v>144.1591670328915</v>
       </c>
       <c r="E93">
-        <v>370.72</v>
+        <v>376.5400000000001</v>
       </c>
       <c r="F93">
-        <v>529.62</v>
+        <v>535.4400000000001</v>
       </c>
       <c r="G93">
         <v>131.4</v>
@@ -8913,37 +8913,37 @@
         <v>44.75</v>
       </c>
       <c r="M93">
-        <v>124.884396</v>
+        <v>126.256752</v>
       </c>
       <c r="N93">
-        <v>-80.13439600000001</v>
+        <v>-81.50675200000002</v>
       </c>
       <c r="O93">
-        <v>-21.63628692</v>
+        <v>-22.00682304000001</v>
       </c>
       <c r="P93">
-        <v>-58.49810908000001</v>
+        <v>-59.49992896000001</v>
       </c>
       <c r="Q93">
-        <v>-37.49810908000001</v>
+        <v>-38.49992896000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.772761777276134</v>
+        <v>0.8636319994356511</v>
       </c>
       <c r="T93">
-        <v>8.708814771553842</v>
+        <v>9.797416617998074</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09674947701232425</v>
+        <v>0.09569785226219028</v>
       </c>
       <c r="W93">
-        <v>0.2129864733204939</v>
+        <v>0.2132344464365755</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3583313963419417</v>
+        <v>0.354436489859964</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2652662506765016</v>
+        <v>0.2671662506765016</v>
       </c>
       <c r="C94">
-        <v>-259.8808329671086</v>
+        <v>-266.9381598700372</v>
       </c>
       <c r="D94">
-        <v>144.1591670328915</v>
+        <v>142.9218401299628</v>
       </c>
       <c r="E94">
-        <v>376.5400000000001</v>
+        <v>382.36</v>
       </c>
       <c r="F94">
-        <v>535.4400000000001</v>
+        <v>541.26</v>
       </c>
       <c r="G94">
         <v>131.4</v>
@@ -8995,37 +8995,37 @@
         <v>44.75</v>
       </c>
       <c r="M94">
-        <v>126.256752</v>
+        <v>127.629108</v>
       </c>
       <c r="N94">
-        <v>-81.50675200000002</v>
+        <v>-82.879108</v>
       </c>
       <c r="O94">
-        <v>-22.00682304000001</v>
+        <v>-22.37735916</v>
       </c>
       <c r="P94">
-        <v>-59.49992896000001</v>
+        <v>-60.50174884</v>
       </c>
       <c r="Q94">
-        <v>-38.49992896000001</v>
+        <v>-39.50174884</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8636319994356511</v>
+        <v>0.9804651422121727</v>
       </c>
       <c r="T94">
-        <v>9.797416617998074</v>
+        <v>11.19704756342637</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09569785226219028</v>
+        <v>0.09466884309808074</v>
       </c>
       <c r="W94">
-        <v>0.2132344464365755</v>
+        <v>0.2134770867974726</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.354436489859964</v>
+        <v>0.3506253448077064</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2671662506765016</v>
+        <v>0.2690662506765016</v>
       </c>
       <c r="C95">
-        <v>-266.9381598700372</v>
+        <v>-273.9744274224511</v>
       </c>
       <c r="D95">
-        <v>142.9218401299628</v>
+        <v>141.7055725775489</v>
       </c>
       <c r="E95">
-        <v>382.36</v>
+        <v>388.1800000000001</v>
       </c>
       <c r="F95">
-        <v>541.26</v>
+        <v>547.08</v>
       </c>
       <c r="G95">
         <v>131.4</v>
@@ -9077,37 +9077,37 @@
         <v>44.75</v>
       </c>
       <c r="M95">
-        <v>127.629108</v>
+        <v>129.001464</v>
       </c>
       <c r="N95">
-        <v>-82.879108</v>
+        <v>-84.25146400000003</v>
       </c>
       <c r="O95">
-        <v>-22.37735916</v>
+        <v>-22.74789528000001</v>
       </c>
       <c r="P95">
-        <v>-60.50174884</v>
+        <v>-61.50356872000002</v>
       </c>
       <c r="Q95">
-        <v>-39.50174884</v>
+        <v>-40.50356872000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9804651422121727</v>
+        <v>1.136242665914202</v>
       </c>
       <c r="T95">
-        <v>11.19704756342637</v>
+        <v>13.06322215733077</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09466884309808074</v>
+        <v>0.09366172774597346</v>
       </c>
       <c r="W95">
-        <v>0.2134770867974726</v>
+        <v>0.2137145645974995</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3506253448077064</v>
+        <v>0.3468952879480499</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2690662506765016</v>
+        <v>0.2709662506765015</v>
       </c>
       <c r="C96">
-        <v>-273.9744274224511</v>
+        <v>-280.9901687339862</v>
       </c>
       <c r="D96">
-        <v>141.7055725775489</v>
+        <v>140.5098312660139</v>
       </c>
       <c r="E96">
-        <v>388.1800000000001</v>
+        <v>394.0000000000001</v>
       </c>
       <c r="F96">
-        <v>547.08</v>
+        <v>552.9000000000001</v>
       </c>
       <c r="G96">
         <v>131.4</v>
@@ -9159,37 +9159,37 @@
         <v>44.75</v>
       </c>
       <c r="M96">
-        <v>129.001464</v>
+        <v>130.37382</v>
       </c>
       <c r="N96">
-        <v>-84.25146400000003</v>
+        <v>-85.62382000000002</v>
       </c>
       <c r="O96">
-        <v>-22.74789528000001</v>
+        <v>-23.11843140000001</v>
       </c>
       <c r="P96">
-        <v>-61.50356872000002</v>
+        <v>-62.50538860000002</v>
       </c>
       <c r="Q96">
-        <v>-40.50356872000002</v>
+        <v>-41.50538860000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.136242665914202</v>
+        <v>1.354331199097043</v>
       </c>
       <c r="T96">
-        <v>13.06322215733077</v>
+        <v>15.67586658879693</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09366172774597346</v>
+        <v>0.09267581482233164</v>
       </c>
       <c r="W96">
-        <v>0.2137145645974995</v>
+        <v>0.2139470428648942</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3468952879480499</v>
+        <v>0.3432437586012284</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2709662506765015</v>
+        <v>0.2728662506765016</v>
       </c>
       <c r="C97">
-        <v>-280.9901687339862</v>
+        <v>-287.9858990708814</v>
       </c>
       <c r="D97">
-        <v>140.5098312660139</v>
+        <v>139.3341009291186</v>
       </c>
       <c r="E97">
-        <v>394.0000000000001</v>
+        <v>399.8200000000001</v>
       </c>
       <c r="F97">
-        <v>552.9000000000001</v>
+        <v>558.72</v>
       </c>
       <c r="G97">
         <v>131.4</v>
@@ -9241,37 +9241,37 @@
         <v>44.75</v>
       </c>
       <c r="M97">
-        <v>130.37382</v>
+        <v>131.746176</v>
       </c>
       <c r="N97">
-        <v>-85.62382000000002</v>
+        <v>-86.99617600000002</v>
       </c>
       <c r="O97">
-        <v>-23.11843140000001</v>
+        <v>-23.48896752000001</v>
       </c>
       <c r="P97">
-        <v>-62.50538860000002</v>
+        <v>-63.50720848000002</v>
       </c>
       <c r="Q97">
-        <v>-41.50538860000002</v>
+        <v>-42.50720848000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.354331199097043</v>
+        <v>1.681463998871304</v>
       </c>
       <c r="T97">
-        <v>15.67586658879693</v>
+        <v>19.59483323599617</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09267581482233164</v>
+        <v>0.09171044175126569</v>
       </c>
       <c r="W97">
-        <v>0.2139470428648942</v>
+        <v>0.2141746778350515</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3432437586012284</v>
+        <v>0.3396683027824655</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2728662506765015</v>
+        <v>0.2747662506765016</v>
       </c>
       <c r="C98">
-        <v>-287.9858990708814</v>
+        <v>-294.9621165963164</v>
       </c>
       <c r="D98">
-        <v>139.3341009291186</v>
+        <v>138.1778834036836</v>
       </c>
       <c r="E98">
-        <v>399.8200000000001</v>
+        <v>405.64</v>
       </c>
       <c r="F98">
-        <v>558.72</v>
+        <v>564.54</v>
       </c>
       <c r="G98">
         <v>131.4</v>
@@ -9323,37 +9323,37 @@
         <v>44.75</v>
       </c>
       <c r="M98">
-        <v>131.746176</v>
+        <v>133.118532</v>
       </c>
       <c r="N98">
-        <v>-86.99617600000002</v>
+        <v>-88.36853199999999</v>
       </c>
       <c r="O98">
-        <v>-23.48896752000001</v>
+        <v>-23.85950364</v>
       </c>
       <c r="P98">
-        <v>-63.50720848000002</v>
+        <v>-64.50902835999999</v>
       </c>
       <c r="Q98">
-        <v>-42.50720848000002</v>
+        <v>-43.50902835999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.6814639988713</v>
+        <v>2.2266853318284</v>
       </c>
       <c r="T98">
-        <v>19.59483323599612</v>
+        <v>26.12644431466149</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09171044175126569</v>
+        <v>0.09076497327960319</v>
       </c>
       <c r="W98">
-        <v>0.2141746778350515</v>
+        <v>0.2143976193006696</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3396683027824655</v>
+        <v>0.336166567702234</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2747662506765016</v>
+        <v>0.2766662506765015</v>
       </c>
       <c r="C99">
-        <v>-294.9621165963164</v>
+        <v>-301.9193030741913</v>
       </c>
       <c r="D99">
-        <v>138.1778834036836</v>
+        <v>137.0406969258087</v>
       </c>
       <c r="E99">
-        <v>405.64</v>
+        <v>411.46</v>
       </c>
       <c r="F99">
-        <v>564.54</v>
+        <v>570.36</v>
       </c>
       <c r="G99">
         <v>131.4</v>
@@ -9405,37 +9405,37 @@
         <v>44.75</v>
       </c>
       <c r="M99">
-        <v>133.118532</v>
+        <v>134.490888</v>
       </c>
       <c r="N99">
-        <v>-88.36853199999999</v>
+        <v>-89.74088800000001</v>
       </c>
       <c r="O99">
-        <v>-23.85950364</v>
+        <v>-24.23003976</v>
       </c>
       <c r="P99">
-        <v>-64.50902835999999</v>
+        <v>-65.51084824</v>
       </c>
       <c r="Q99">
-        <v>-43.50902835999999</v>
+        <v>-44.51084824</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.2266853318284</v>
+        <v>3.317127997742599</v>
       </c>
       <c r="T99">
-        <v>26.12644431466149</v>
+        <v>39.18966647199224</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09076497327960319</v>
+        <v>0.08983880008287252</v>
       </c>
       <c r="W99">
-        <v>0.2143976193006696</v>
+        <v>0.2146160109404587</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.336166567702234</v>
+        <v>0.3327362966032316</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2766662506765015</v>
+        <v>0.2785662506765015</v>
       </c>
       <c r="C100">
-        <v>-301.9193030741913</v>
+        <v>-308.8579245384383</v>
       </c>
       <c r="D100">
-        <v>137.0406969258087</v>
+        <v>135.9220754615616</v>
       </c>
       <c r="E100">
-        <v>411.46</v>
+        <v>417.28</v>
       </c>
       <c r="F100">
-        <v>570.36</v>
+        <v>576.1799999999999</v>
       </c>
       <c r="G100">
         <v>131.4</v>
@@ -9487,37 +9487,37 @@
         <v>44.75</v>
       </c>
       <c r="M100">
-        <v>134.490888</v>
+        <v>135.863244</v>
       </c>
       <c r="N100">
-        <v>-89.74088800000001</v>
+        <v>-91.11324399999998</v>
       </c>
       <c r="O100">
-        <v>-24.23003976</v>
+        <v>-24.60057588</v>
       </c>
       <c r="P100">
-        <v>-65.51084824</v>
+        <v>-66.51266811999999</v>
       </c>
       <c r="Q100">
-        <v>-44.51084824</v>
+        <v>-45.51266811999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.317127997742599</v>
+        <v>6.588455995485198</v>
       </c>
       <c r="T100">
-        <v>39.18966647199224</v>
+        <v>78.37933294398447</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08983880008287252</v>
+        <v>0.08893133745577282</v>
       </c>
       <c r="W100">
-        <v>0.2146160109404587</v>
+        <v>0.2148299906279288</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3327362966032316</v>
+        <v>0.3293753239102697</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2785662506765015</v>
-      </c>
-      <c r="C101">
-        <v>-308.8579245384383</v>
-      </c>
-      <c r="D101">
-        <v>135.9220754615616</v>
-      </c>
-      <c r="E101">
-        <v>417.28</v>
-      </c>
-      <c r="F101">
-        <v>576.1799999999999</v>
-      </c>
-      <c r="G101">
-        <v>131.4</v>
-      </c>
-      <c r="H101">
-        <v>423.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>65.75</v>
-      </c>
-      <c r="K101">
-        <v>21</v>
-      </c>
-      <c r="L101">
-        <v>44.75</v>
-      </c>
-      <c r="M101">
-        <v>135.863244</v>
-      </c>
-      <c r="N101">
-        <v>-91.11324399999998</v>
-      </c>
-      <c r="O101">
-        <v>-24.60057588</v>
-      </c>
-      <c r="P101">
-        <v>-66.51266811999999</v>
-      </c>
-      <c r="Q101">
-        <v>-45.51266811999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.588455995485198</v>
-      </c>
-      <c r="T101">
-        <v>78.37933294398447</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08893133745577282</v>
-      </c>
-      <c r="W101">
-        <v>0.2148299906279288</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3293753239102697</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
